--- a/OZET_tr.xlsx
+++ b/OZET_tr.xlsx
@@ -612,12 +612,12 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: Action=LOW_DATA | Trade_Action=LOW_DATA | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -10.1%, L -15.0%, H +22.6%, UD; Path=+24.2% → -19.6% | M Now=Now -18.7%, L -23.1%, H +0.0%, DU; Path=+2.6% → -11.0% | S Now=NA; Path=NA | WMA200=-10.5%, UP</t>
+          <t>NÖTR: Action=LOW_DATA | Trade_Action=LOW_DATA | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -10.0%, L -15.0%, H +22.6%, UD; Path=+24.2% → -19.6% | M Now=Now -18.6%, L -23.1%, H +0.0%, DU; Path=+2.6% → -11.0% | S Now=NA; Path=NA | WMA200=-10.4%, UP</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%10,1 / XU030 -%8,8 / Fark -%1,3 puan | M: Hisse -%18,7 / XU030 -%4,7 / Fark -%14,0 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%10,0 / XU030 -%8,7 / Fark -%1,3 puan | M: Hisse -%18,6 / XU030 -%4,6 / Fark -%14,0 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="I2" s="4" t="inlineStr">
@@ -627,7 +627,7 @@
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: Endeks=XU030 | Karar=AL_ADAYI | AL basari=66.66666666666667 n=3 | SAT basari=40 n=20</t>
+          <t>NÖTR: Endeks=XU030 | Karar=AL_ADAYI | AL basari=66.66666666666667 n=3 | SAT basari=42.85714285714285 n=21</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
@@ -692,12 +692,12 @@
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: Action=LONG_WATCH | Trade_Action=LONG_WATCH | Önerilen=EVET | Öneren sistem=3 | Q Now=Now -0.8%, L -9.5%, H +14.3%, UD; Path=+13.0% → -20.0% | M Now=Now -0.5%, L -4.9%, H +8.8%, UD; Path=+7.7% → -9.1% | S Now=NA; Path=NA | WMA200=-2.9%, DOWN</t>
+          <t>OLUMLU: Action=LONG_WATCH | Trade_Action=LONG_WATCH | Önerilen=EVET | Öneren sistem=3 | Q Now=Now -0.8%, L -9.5%, H +14.3%, UD; Path=+13.0% → -20.0% | M Now=Now -0.4%, L -4.9%, H +8.8%, UD; Path=+7.7% → -9.1% | S Now=NA; Path=NA | WMA200=-2.9%, DOWN</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%0,8 / XU030 -%8,8 / Fark +%8,0 puan | M: Hisse -%0,5 / XU030 -%4,7 / Fark +%4,2 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%0,8 / XU030 -%8,7 / Fark +%7,9 puan | M: Hisse -%0,4 / XU030 -%4,6 / Fark +%4,2 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="I3" s="5" t="inlineStr">
@@ -707,7 +707,7 @@
       </c>
       <c r="J3" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=AL_ADAYI | AL basari=65.38461538461539 n=26 | SAT basari=37.5 n=48</t>
+          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=AL_ADAYI | AL basari=66.66666666666667 n=27 | SAT basari=41.66666666666666 n=48</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
@@ -739,7 +739,7 @@
         <is>
           <t>LONG - 1 - 8/2
 LONG - 7 - 5/5
-LONG - 1 - 9/2</t>
+LONG - 1 - 8/2</t>
         </is>
       </c>
     </row>
@@ -772,12 +772,12 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: Action=LATE | Trade_Action=LATE | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -14.0%, L -17.3%, H +5.4%, DU; Path=+13.8% → -19.2% | M Now=Now +2.7%, L -0.5%, H +8.5%, UD; Path=+4.4% → -8.5% | S Now=NA; Path=NA | WMA200=-8.7%, UP</t>
+          <t>NÖTR: Action=LATE | Trade_Action=LATE | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -13.9%, L -17.3%, H +5.4%, DU; Path=+13.8% → -19.2% | M Now=Now +2.8%, L -0.5%, H +8.5%, UD; Path=+4.4% → -8.5% | S Now=NA; Path=NA | WMA200=-8.7%, UP</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%14,0 / XU030 -%8,8 / Fark -%5,2 puan | M: Hisse +%2,7 / XU030 -%4,7 / Fark +%7,4 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%13,9 / XU030 -%8,7 / Fark -%5,2 puan | M: Hisse +%2,8 / XU030 -%4,6 / Fark +%7,4 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: Action=LONG_WATCH | Trade_Action=LONG_WATCH | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -15.8%, L -23.0%, H +40.7%, UD; Path=-16.0% → +18.8% | M Now=Now -9.6%, L -17.3%, H +3.7%, UD; Path=+5.8% → -6.9% | S Now=NA; Path=NA | WMA200=-16.6%, UP</t>
+          <t>OLUMLU: Action=LONG_WATCH | Trade_Action=LONG_WATCH | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -15.7%, L -23.0%, H +40.7%, UD; Path=-16.0% → +18.8% | M Now=Now -9.5%, L -17.3%, H +3.7%, UD; Path=+5.8% → -6.9% | S Now=NA; Path=NA | WMA200=-16.6%, UP</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%15,8 / XU030 -%8,8 / Fark -%7,0 puan | M: Hisse -%9,6 / XU030 -%4,7 / Fark -%4,9 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%15,7 / XU030 -%8,7 / Fark -%7,0 puan | M: Hisse -%9,5 / XU030 -%4,6 / Fark -%4,9 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -932,12 +932,12 @@
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: Action=LONG_WATCH | Trade_Action=LONG_WATCH | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -12.7%, L -12.7%, H +6.2%, UD; Path=+8.2% → -13.3% | M Now=Now -8.8%, L -8.8%, H +0.0%, DU; Path=-3.3% → +10.4% | S Now=NA; Path=NA | WMA200=-14.4%, UP</t>
+          <t>OLUMLU: Action=LONG_WATCH | Trade_Action=LONG_WATCH | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -12.6%, L -12.6%, H +6.2%, UD; Path=+8.2% → -13.3% | M Now=Now -8.7%, L -8.7%, H +0.0%, DU; Path=-3.3% → +10.4% | S Now=NA; Path=NA | WMA200=-14.3%, UP</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%12,7 / XU030 -%8,8 / Fark -%3,9 puan | M: Hisse -%8,8 / XU030 -%4,7 / Fark -%4,1 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%12,6 / XU030 -%8,7 / Fark -%3,9 puan | M: Hisse -%8,7 / XU030 -%4,6 / Fark -%4,1 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: Endeks=XU030 | Karar=AL_BEKLE_EŞİK | AL basari=63.88888888888889 n=36 | SAT basari=nan n=0</t>
+          <t>NÖTR: Endeks=XU030 | Karar=AL_BEKLE_EŞİK | AL basari=62.16216216216216 n=37 | SAT basari=nan n=0</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
@@ -1012,12 +1012,12 @@
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: Action=LONG_WATCH | Trade_Action=LONG_WATCH | Önerilen=EVET | Öneren sistem=7 | Q Now=Now +11.0%, L -2.2%, H +14.5%, DU; Path=+17.9% → -12.9% | M Now=Now +2.6%, L -1.5%, H +5.8%, UD; Path=+6.0% → -6.5% | S Now=NA; Path=NA | WMA200=+5.4%, DOWN</t>
+          <t>OLUMLU: Action=LONG_WATCH | Trade_Action=LONG_WATCH | Önerilen=EVET | Öneren sistem=7 | Q Now=Now +11.1%, L -2.2%, H +14.5%, DU; Path=+17.9% → -12.9% | M Now=Now +2.7%, L -1.5%, H +5.8%, UD; Path=+6.0% → -6.5% | S Now=NA; Path=NA | WMA200=+5.5%, DOWN</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse +%11,0 / XU030 -%8,8 / Fark +%19,8 puan | M: Hisse +%2,6 / XU030 -%4,7 / Fark +%7,3 puan | S: VERİ YOK</t>
+          <t>Q: Hisse +%11,1 / XU030 -%8,7 / Fark +%19,8 puan | M: Hisse +%2,7 / XU030 -%4,6 / Fark +%7,3 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=SAT_ADAYI | AL basari=nan n=0 | SAT basari=44.44444444444444 n=27</t>
+          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=SAT_ADAYI | AL basari=nan n=0 | SAT basari=40.74074074074074 n=27</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
@@ -1059,7 +1059,7 @@
         <is>
           <t>SHORT - 2 - 2/9
 SHORT - 10 - 4/8
-SHORT - 2 - 2/7</t>
+SHORT - 2 - 2/8</t>
         </is>
       </c>
     </row>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: Action=LONG_WATCH | Trade_Action=LONG_WATCH | Önerilen=EVET | Öneren sistem=5 | Q Now=Now -23.2%, L -24.0%, H +1.2%, DU; Path=+13.9% → -20.1% | M Now=Now -9.9%, L -10.9%, H +3.2%, DU; Path=+6.0% → -9.1% | S Now=NA; Path=NA | WMA200=-24.6%, UP</t>
+          <t>OLUMLU: Action=LONG_WATCH | Trade_Action=LONG_WATCH | Önerilen=EVET | Öneren sistem=5 | Q Now=Now -23.1%, L -24.0%, H +1.2%, DU; Path=+13.9% → -20.1% | M Now=Now -9.9%, L -10.9%, H +3.2%, DU; Path=+6.0% → -9.1% | S Now=NA; Path=NA | WMA200=-24.5%, UP</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%23,2 / XU030 -%8,8 / Fark -%14,4 puan | M: Hisse -%9,9 / XU030 -%4,7 / Fark -%5,2 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%23,1 / XU030 -%8,7 / Fark -%14,4 puan | M: Hisse -%9,9 / XU030 -%4,6 / Fark -%5,3 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
@@ -1138,7 +1138,7 @@
       <c r="P8" s="2" t="inlineStr">
         <is>
           <t>ALT -  - 14/3
-ALT -  - 38/18
+ALT -  - 38/17
 LONG - 1 - 27/0</t>
         </is>
       </c>
@@ -1172,12 +1172,12 @@
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: Action=LONG_READY | Trade_Action=LONG_READY | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -18.3%, L -20.2%, H +0.3%, DU; Path=-3.6% → +58.5% | M Now=Now -13.5%, L -15.5%, H +3.4%, UD; Path=-6.5% → +7.6% | S Now=NA; Path=NA | WMA200=-24.8%, UP</t>
+          <t>OLUMLU: Action=LONG_READY | Trade_Action=LONG_READY | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -18.2%, L -20.2%, H +0.3%, DU; Path=-3.6% → +58.5% | M Now=Now -13.5%, L -15.5%, H +3.4%, UD; Path=-6.5% → +7.6% | S Now=NA; Path=NA | WMA200=-24.8%, UP</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%18,3 / XU030 -%8,8 / Fark -%9,5 puan | M: Hisse -%13,5 / XU030 -%4,7 / Fark -%8,8 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%18,2 / XU030 -%8,7 / Fark -%9,5 puan | M: Hisse -%13,5 / XU030 -%4,6 / Fark -%8,9 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: Endeks=XU030 | Karar=AL_BEKLE_EŞİK | AL basari=68.18181818181819 n=22 | SAT basari=nan n=0</t>
+          <t>NÖTR: Endeks=XU030 | Karar=AL_BEKLE_EŞİK | AL basari=66.66666666666667 n=21 | SAT basari=nan n=0</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: Action=RISK | Trade_Action=RISK | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -9.4%, L -11.3%, H +11.4%, UD; Path=+16.1% → -17.8% | M Now=Now +0.1%, L -1.1%, H +6.1%, UD; Path=+4.8% → -9.8% | S Now=NA; Path=NA | WMA200=-7.3%, DOWN</t>
+          <t>OLUMSUZ / RİSK: Action=RISK | Trade_Action=RISK | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -9.3%, L -11.3%, H +11.4%, UD; Path=+16.1% → -17.8% | M Now=Now +0.2%, L -1.1%, H +6.1%, UD; Path=+4.8% → -9.8% | S Now=NA; Path=NA | WMA200=-7.2%, DOWN</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%9,4 / XU030 -%8,8 / Fark -%0,6 puan | M: Hisse +%0,1 / XU030 -%4,7 / Fark +%4,8 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%9,3 / XU030 -%8,7 / Fark -%0,6 puan | M: Hisse +%0,2 / XU030 -%4,6 / Fark +%4,8 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: Endeks=XU030 | Karar=AL_BEKLE_EŞİK | AL basari=60.41666666666666 n=48 | SAT basari=nan n=0</t>
+          <t>NÖTR: Endeks=XU030 | Karar=AL_BEKLE_EŞİK | AL basari=61.22448979591837 n=49 | SAT basari=nan n=0</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: Action=LOW_DATA | Trade_Action=LOW_DATA | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -65.4%, L -67.5%, H +3.7%, UD; Path=-7.3% → +40.3% | M Now=Now -13.2%, L -18.6%, H +0.3%, DU; Path=-11.6% → +14.1% | S Now=NA; Path=NA | WMA200=-55.7%, UP</t>
+          <t>NÖTR: Action=LOW_DATA | Trade_Action=LOW_DATA | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -65.4%, L -67.5%, H +3.7%, UD; Path=-7.3% → +40.3% | M Now=Now -13.2%, L -18.6%, H +0.3%, DU; Path=-11.6% → +14.1% | S Now=NA; Path=NA | WMA200=-55.6%, UP</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%65,4 / XU030 -%8,8 / Fark -%56,6 puan | M: Hisse -%13,2 / XU030 -%4,7 / Fark -%8,5 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%65,4 / XU030 -%8,7 / Fark -%56,7 puan | M: Hisse -%13,2 / XU030 -%4,6 / Fark -%8,6 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=SAT_BEKLE_EŞİK | AL basari=nan n=1 | SAT basari=42.85714285714285 n=28</t>
+          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=SAT_BEKLE_EŞİK | AL basari=nan n=1 | SAT basari=44.82758620689656 n=29</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
@@ -1412,12 +1412,12 @@
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: Action=NO_CLEAR_EDGE | Trade_Action=NO_CLEAR_EDGE | Önerilen=EVET | Öneren sistem=1 | Q Now=Now -20.2%, L -20.2%, H +3.0%, DU; Path=+19.8% → -15.3% | M Now=Now -7.2%, L -7.2%, H +1.1%, DU; Path=-6.5% → +8.6% | S Now=NA; Path=NA | WMA200=-20.4%, UP</t>
+          <t>OLUMLU: Action=NO_CLEAR_EDGE | Trade_Action=NO_CLEAR_EDGE | Önerilen=EVET | Öneren sistem=1 | Q Now=Now -20.1%, L -20.1%, H +3.0%, DU; Path=+19.8% → -15.3% | M Now=Now -7.1%, L -7.1%, H +1.1%, DU; Path=-6.5% → +8.6% | S Now=NA; Path=NA | WMA200=-20.4%, UP</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%20,2 / XU030 -%8,8 / Fark -%11,4 puan | M: Hisse -%7,2 / XU030 -%4,7 / Fark -%2,5 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%20,1 / XU030 -%8,7 / Fark -%11,4 puan | M: Hisse -%7,1 / XU030 -%4,6 / Fark -%2,5 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: Endeks=XU030 | Karar=AL_BEKLE_EŞİK | AL basari=54.54545454545455 n=44 | SAT basari=nan n=0</t>
+          <t>NÖTR: Endeks=XU030 | Karar=AL_BEKLE_EŞİK | AL basari=50 n=42 | SAT basari=nan n=0</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
@@ -1457,8 +1457,8 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>LONG - 5 - 17/1
-LONG - 5 - 17/1
+          <t>LONG - 5 - 16/1
+LONG - 5 - 16/1
 ALT -  - 15/2</t>
         </is>
       </c>
@@ -1492,12 +1492,12 @@
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: Action=LONG_WATCH | Trade_Action=LONG_WATCH | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -12.8%, L -26.7%, H +2.9%, UD; Path=+17.0% → -14.4% | M Now=Now -10.0%, L -24.3%, H +0.0%, DU; Path=+9.0% → -5.1% | S Now=NA; Path=NA | WMA200=-22.0%, UP</t>
+          <t>OLUMLU: Action=LONG_WATCH | Trade_Action=LONG_WATCH | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -12.8%, L -26.7%, H +2.9%, UD; Path=+17.0% → -14.4% | M Now=Now -9.9%, L -24.3%, H +0.0%, DU; Path=+9.0% → -5.1% | S Now=NA; Path=NA | WMA200=-22.0%, UP</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%12,8 / XU030 -%8,8 / Fark -%4,0 puan | M: Hisse -%10,0 / XU030 -%4,7 / Fark -%5,3 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%12,8 / XU030 -%8,7 / Fark -%4,1 puan | M: Hisse -%9,9 / XU030 -%4,6 / Fark -%5,3 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
@@ -1507,7 +1507,7 @@
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=SAT_BEKLE_EŞİK | AL basari=nan n=0 | SAT basari=35.71428571428572 n=28</t>
+          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=SAT_BEKLE_EŞİK | AL basari=nan n=0 | SAT basari=33.33333333333334 n=27</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
@@ -1537,7 +1537,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>UST -  - 2/12
+          <t>UST -  - 3/12
 LONG - 1 - 19/3
 ALT -  - 20/2</t>
         </is>
@@ -1572,12 +1572,12 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: Action=LOW_DATA | Trade_Action=LOW_DATA | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now +13.9%, L -27.7%, H +13.9%, DU; Path=+70.0% → -20.5% | M Now=Now +31.0%, L +0.0%, H +31.0%, UD; Path=+11.3% → -20.5% | S Now=NA; Path=NA | WMA200=+32.9%, DOWN</t>
+          <t>NÖTR: Action=LOW_DATA | Trade_Action=LOW_DATA | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now +14.0%, L -27.7%, H +14.0%, DU; Path=+70.0% → -20.5% | M Now=Now +31.1%, L +0.0%, H +31.1%, UD; Path=+11.3% → -20.5% | S Now=NA; Path=NA | WMA200=+33.0%, DOWN</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse +%13,9 / XU030 -%8,8 / Fark +%22,7 puan | M: Hisse +%31,0 / XU030 -%4,7 / Fark +%35,7 puan | S: VERİ YOK</t>
+          <t>Q: Hisse +%14,0 / XU030 -%8,7 / Fark +%22,7 puan | M: Hisse +%31,1 / XU030 -%4,6 / Fark +%35,7 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="M14" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / GEÇ KALMA RİSKİ: Açık=EVET | Sayfa=USD | Güncel=%13,7 | Max_Aktif_Kar=%14,3 | Min=%0,0 | Grup/Etiket=USD/LAST_3_TOP3/T5_tek_sistem|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan|keltner_kirilim</t>
+          <t>OLUMSUZ / GEÇ KALMA RİSKİ: Açık=EVET | Sayfa=USD | Güncel=%13,8 | Max_Aktif_Kar=%14,4 | Min=%0,0 | Grup/Etiket=USD/LAST_3_TOP3/T5_tek_sistem|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan|keltner_kirilim</t>
         </is>
       </c>
       <c r="N14" s="4" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: Action=LATE | Trade_Action=LATE | Önerilen=EVET | Öneren sistem=2 | Q Now=Now -2.3%, L -12.4%, H +10.3%, UD; Path=-11.4% → +22.3% | M Now=Now -4.1%, L -12.6%, H +8.3%, UD; Path=-5.2% → +11.5% | S Now=NA; Path=NA | WMA200=-9.3%, UP</t>
+          <t>OLUMLU: Action=LATE | Trade_Action=LATE | Önerilen=EVET | Öneren sistem=2 | Q Now=Now -2.2%, L -12.4%, H +10.3%, UD; Path=-11.4% → +22.3% | M Now=Now -4.0%, L -12.6%, H +8.3%, UD; Path=-5.2% → +11.5% | S Now=NA; Path=NA | WMA200=-9.2%, UP</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%2,3 / XU030 -%8,8 / Fark +%6,5 puan | M: Hisse -%4,1 / XU030 -%4,7 / Fark +%0,6 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%2,2 / XU030 -%8,7 / Fark +%6,5 puan | M: Hisse -%4,0 / XU030 -%4,6 / Fark +%0,6 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
@@ -1667,7 +1667,7 @@
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=SAT_BEKLE_EŞİK | AL basari=nan n=0 | SAT basari=40 n=40</t>
+          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=SAT_BEKLE_EŞİK | AL basari=nan n=0 | SAT basari=38.46153846153846 n=39</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
@@ -1698,7 +1698,7 @@
       <c r="P15" s="2" t="inlineStr">
         <is>
           <t>LONG - 1 - 10/3
-LONG - 7 - 13/12
+LONG - 7 - 12/12
 LONG - 1 - 10/3</t>
         </is>
       </c>
@@ -1732,12 +1732,12 @@
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: Action=LONG_READY | Trade_Action=LONG_READY | Önerilen=EVET | Öneren sistem=2 | Q Now=Now -16.2%, L -16.2%, H +2.2%, DU; Path=-8.4% → +17.8% | M Now=Now -7.9%, L -7.9%, H +9.7%, UD; Path=-4.5% → +8.3% | S Now=NA; Path=NA | WMA200=-20.6%, UP</t>
+          <t>OLUMLU: Action=LONG_READY | Trade_Action=LONG_READY | Önerilen=EVET | Öneren sistem=2 | Q Now=Now -16.1%, L -16.1%, H +2.2%, DU; Path=-8.4% → +17.8% | M Now=Now -7.8%, L -7.8%, H +9.7%, UD; Path=-4.5% → +8.3% | S Now=NA; Path=NA | WMA200=-20.5%, UP</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%16,2 / XU030 -%8,8 / Fark -%7,4 puan | M: Hisse -%7,9 / XU030 -%4,7 / Fark -%3,2 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%16,1 / XU030 -%8,7 / Fark -%7,4 puan | M: Hisse -%7,8 / XU030 -%4,6 / Fark -%3,2 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
@@ -1747,7 +1747,7 @@
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=SAT_ADAYI | AL basari=56.81818181818182 n=44 | SAT basari=59.09090909090909 n=22</t>
+          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=SAT_ADAYI | AL basari=57.77777777777778 n=45 | SAT basari=56.52173913043478 n=23</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: Action=LONG_WATCH | Trade_Action=LONG_WATCH | Önerilen=EVET | Öneren sistem=3 | Q Now=Now -52.4%, L -56.6%, H +5.2%, UD; Path=-20.9% → +28.1% | M Now=Now -46.0%, L -50.8%, H +7.8%, UD; Path=+10.4% → -12.2% | S Now=NA; Path=NA | WMA200=-50.3%, UP</t>
+          <t>OLUMLU: Action=LONG_WATCH | Trade_Action=LONG_WATCH | Önerilen=EVET | Öneren sistem=3 | Q Now=Now -52.3%, L -56.6%, H +5.2%, UD; Path=-20.9% → +28.1% | M Now=Now -45.9%, L -50.8%, H +7.8%, UD; Path=+10.4% → -12.2% | S Now=NA; Path=NA | WMA200=-50.3%, UP</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%52,4 / XU030 -%8,8 / Fark -%43,6 puan | M: Hisse -%46,0 / XU030 -%4,7 / Fark -%41,3 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%52,3 / XU030 -%8,7 / Fark -%43,6 puan | M: Hisse -%45,9 / XU030 -%4,6 / Fark -%41,3 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
@@ -1857,8 +1857,8 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>ALT -  - 79/58
-ALT -  - 160/92
+          <t>ALT -  - 78/58
+ALT -  - 159/92
 ALT -  - 56/41</t>
         </is>
       </c>
@@ -1892,12 +1892,12 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: Action=NO_CLEAR_EDGE | Trade_Action=NO_CLEAR_EDGE | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -21.1%, L -25.8%, H +6.0%, DU; Path=-14.1% → +20.9% | M Now=Now -7.0%, L -12.4%, H +2.3%, DU; Path=-5.4% → +11.2% | S Now=NA; Path=NA | WMA200=-8.5%, UP</t>
+          <t>NÖTR: Action=NO_CLEAR_EDGE | Trade_Action=NO_CLEAR_EDGE | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -21.1%, L -25.8%, H +6.0%, DU; Path=-14.1% → +20.9% | M Now=Now -6.9%, L -12.4%, H +2.3%, DU; Path=-5.4% → +11.2% | S Now=NA; Path=NA | WMA200=-8.4%, UP</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%21,1 / XU030 -%8,8 / Fark -%12,3 puan | M: Hisse -%7,0 / XU030 -%4,7 / Fark -%2,3 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%21,1 / XU030 -%8,7 / Fark -%12,4 puan | M: Hisse -%6,9 / XU030 -%4,6 / Fark -%2,3 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=SAT_BEKLE_EŞİK | AL basari=72.72727272727273 n=11 | SAT basari=44.73684210526316 n=76</t>
+          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=SAT_BEKLE_EŞİK | AL basari=70 n=10 | SAT basari=45.33333333333334 n=75</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
@@ -1939,7 +1939,7 @@
         <is>
           <t>LONG - 3 - 4/6
 SHORT - 68 - 7/12
-LONG - 1 - 8/2</t>
+LONG - 1 - 8/3</t>
         </is>
       </c>
     </row>
@@ -1972,12 +1972,12 @@
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: Action=NO_CLEAR_EDGE | Trade_Action=NO_CLEAR_EDGE | Önerilen=EVET | Öneren sistem=7 | Q Now=Now -20.4%, L -26.4%, H +6.8%, UD; Path=+12.0% → -16.3% | M Now=Now -6.9%, L -7.1%, H +2.4%, DU; Path=-6.9% → +6.6% | S Now=NA; Path=NA | WMA200=-17.9%, UP</t>
+          <t>OLUMLU: Action=NO_CLEAR_EDGE | Trade_Action=NO_CLEAR_EDGE | Önerilen=EVET | Öneren sistem=7 | Q Now=Now -20.3%, L -26.4%, H +6.8%, UD; Path=+12.0% → -16.3% | M Now=Now -6.8%, L -7.1%, H +2.4%, DU; Path=-6.9% → +6.6% | S Now=NA; Path=NA | WMA200=-17.9%, UP</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%20,4 / XU030 -%8,8 / Fark -%11,6 puan | M: Hisse -%6,9 / XU030 -%4,7 / Fark -%2,2 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%20,3 / XU030 -%8,7 / Fark -%11,6 puan | M: Hisse -%6,8 / XU030 -%4,6 / Fark -%2,2 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
@@ -2052,12 +2052,12 @@
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: Action=LONG_WATCH | Trade_Action=LONG_WATCH | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -14.3%, L -17.6%, H +0.0%, DU; Path=+12.6% → -15.1% | M Now=Now -6.6%, L -10.3%, H +3.2%, UD; Path=+6.2% → -7.8% | S Now=NA; Path=NA | WMA200=-10.3%, UP</t>
+          <t>OLUMLU: Action=LONG_WATCH | Trade_Action=LONG_WATCH | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -14.2%, L -17.6%, H +0.0%, DU; Path=+12.6% → -15.1% | M Now=Now -6.6%, L -10.3%, H +3.2%, UD; Path=+6.2% → -7.8% | S Now=NA; Path=NA | WMA200=-10.2%, UP</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%14,3 / XU030 -%8,8 / Fark -%5,5 puan | M: Hisse -%6,6 / XU030 -%4,7 / Fark -%1,9 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%14,2 / XU030 -%8,7 / Fark -%5,5 puan | M: Hisse -%6,6 / XU030 -%4,6 / Fark -%2,0 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
@@ -2067,7 +2067,7 @@
       </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=SAT_ADAYI | AL basari=52 n=25 | SAT basari=42.85714285714285 n=35</t>
+          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=SAT_ADAYI | AL basari=50 n=24 | SAT basari=42.85714285714285 n=35</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: Action=LONG_WATCH | Trade_Action=LONG_WATCH | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -12.4%, L -15.5%, H +2.4%, DU; Path=-11.7% → +19.3% | M Now=Now +2.1%, L -1.6%, H +6.7%, UD; Path=+6.3% → -7.2% | S Now=NA; Path=NA | WMA200=-11.4%, UP</t>
+          <t>OLUMLU: Action=LONG_WATCH | Trade_Action=LONG_WATCH | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -12.3%, L -15.5%, H +2.4%, DU; Path=-11.7% → +19.3% | M Now=Now +2.2%, L -1.6%, H +6.7%, UD; Path=+6.3% → -7.2% | S Now=NA; Path=NA | WMA200=-11.3%, UP</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%12,4 / XU030 -%8,8 / Fark -%3,6 puan | M: Hisse +%2,1 / XU030 -%4,7 / Fark +%6,8 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%12,3 / XU030 -%8,7 / Fark -%3,6 puan | M: Hisse +%2,2 / XU030 -%4,6 / Fark +%6,8 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
@@ -2147,7 +2147,7 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: Endeks=XU030 | Karar=ÇELİŞKİLİ_BEKLE | AL basari=54.05405405405406 n=37 | SAT basari=33.9622641509434 n=53</t>
+          <t>NÖTR: Endeks=XU030 | Karar=ÇELİŞKİLİ_BEKLE | AL basari=56.75675675675676 n=37 | SAT basari=33.33333333333334 n=54</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
@@ -2178,7 +2178,7 @@
       <c r="P21" s="2" t="inlineStr">
         <is>
           <t>LONG - 19 - 6/6
-LONG - 7 - 7/3
+LONG - 7 - 7/4
 LONG - 5 - 8/2</t>
         </is>
       </c>
@@ -2212,12 +2212,12 @@
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: Action=RISK | Trade_Action=RISK | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now +86.4%, L -8.8%, H +86.4%, DU; Path=+7.8% → -18.1% | M Now=Now +27.7%, L -3.7%, H +27.7%, DU; Path=-6.6% → +8.5% | S Now=NA; Path=NA | WMA200=+66.6%, DOWN</t>
+          <t>OLUMSUZ / RİSK: Action=RISK | Trade_Action=RISK | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now +86.5%, L -8.8%, H +86.5%, DU; Path=+7.8% → -18.1% | M Now=Now +27.8%, L -3.7%, H +27.8%, DU; Path=-6.6% → +8.5% | S Now=NA; Path=NA | WMA200=+66.7%, DOWN</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse +%86,4 / XU030 -%8,8 / Fark +%95,2 puan | M: Hisse +%27,7 / XU030 -%4,7 / Fark +%32,4 puan | S: VERİ YOK</t>
+          <t>Q: Hisse +%86,5 / XU030 -%8,7 / Fark +%95,2 puan | M: Hisse +%27,8 / XU030 -%4,6 / Fark +%32,4 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr">
@@ -2242,7 +2242,7 @@
       </c>
       <c r="M22" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / GEÇ KALMA RİSKİ: Açık=EVET | Sayfa=USD | Güncel=%45,6 | Max_Aktif_Kar=%48,4 | Min=%-0,6 | Grup/Etiket=USD/LAST_3_TOP3/T5_tek_sistem|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan|keltner_kirilim</t>
+          <t>OLUMSUZ / GEÇ KALMA RİSKİ: Açık=EVET | Sayfa=USD | Güncel=%45,8 | Max_Aktif_Kar=%48,4 | Min=%-0,6 | Grup/Etiket=USD/LAST_3_TOP3/T5_tek_sistem|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan|keltner_kirilim</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: Action=LATE | Trade_Action=LATE | Önerilen=EVET | Öneren sistem=1 | Q Now=Now +17.6%, L +0.0%, H +25.4%, UD; Path=-16.4% → +27.7% | M Now=Now +2.8%, L -7.9%, H +5.0%, UD; Path=-5.5% → +13.6% | S Now=NA; Path=NA | WMA200=+3.7%, DOWN</t>
+          <t>OLUMLU: Action=LATE | Trade_Action=LATE | Önerilen=EVET | Öneren sistem=1 | Q Now=Now +17.7%, L +0.0%, H +25.4%, UD; Path=-16.4% → +27.7% | M Now=Now +2.9%, L -7.9%, H +5.0%, UD; Path=-5.5% → +13.6% | S Now=NA; Path=NA | WMA200=+3.8%, DOWN</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse +%17,6 / XU030 -%8,8 / Fark +%26,4 puan | M: Hisse +%2,8 / XU030 -%4,7 / Fark +%7,5 puan | S: VERİ YOK</t>
+          <t>Q: Hisse +%17,7 / XU030 -%8,7 / Fark +%26,4 puan | M: Hisse +%2,9 / XU030 -%4,6 / Fark +%7,5 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
@@ -2307,7 +2307,7 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: Endeks=XU030 | Karar=ÇELİŞKİLİ_BEKLE | AL basari=66.66666666666667 n=9 | SAT basari=36.8421052631579 n=57</t>
+          <t>NÖTR: Endeks=XU030 | Karar=ÇELİŞKİLİ_BEKLE | AL basari=66.66666666666667 n=9 | SAT basari=36.20689655172414 n=58</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: Action=LONG_READY | Trade_Action=LONG_READY | Önerilen=EVET | Öneren sistem=13 | Q Now=Now -18.2%, L -18.2%, H +0.1%, DU; Path=+16.5% → -15.5% | M Now=Now -7.2%, L -7.2%, H +5.3%, UD; Path=-5.4% → +10.4% | S Now=NA; Path=NA | WMA200=-15.7%, UP</t>
+          <t>OLUMLU: Action=LONG_READY | Trade_Action=LONG_READY | Önerilen=EVET | Öneren sistem=13 | Q Now=Now -18.1%, L -18.1%, H +0.1%, DU; Path=+16.5% → -15.5% | M Now=Now -7.1%, L -7.1%, H +5.3%, UD; Path=-5.4% → +10.4% | S Now=NA; Path=NA | WMA200=-15.6%, UP</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%18,2 / XU030 -%8,8 / Fark -%9,4 puan | M: Hisse -%7,2 / XU030 -%4,7 / Fark -%2,5 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%18,1 / XU030 -%8,7 / Fark -%9,4 puan | M: Hisse -%7,1 / XU030 -%4,6 / Fark -%2,5 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="I24" s="4" t="inlineStr">
@@ -2417,9 +2417,9 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>ALT -  - 11/0
+          <t>LONG - 7 - 11/0
 ALT -  - 12/2
-ALT -  - 13/2</t>
+ALT -  - 12/2</t>
         </is>
       </c>
     </row>
@@ -2452,12 +2452,12 @@
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU + RİSK: Action=RISK | Trade_Action=RISK | Önerilen=EVET | Öneren sistem=1 | Q Now=Now -3.4%, L -22.1%, H +0.0%, DU; Path=-9.4% → +18.3% | M Now=Now +12.3%, L -9.4%, H +15.1%, DU; Path=+5.8% → -7.2% | S Now=NA; Path=NA | WMA200=-4.1%, UP</t>
+          <t>OLUMLU + RİSK: Action=RISK | Trade_Action=RISK | Önerilen=EVET | Öneren sistem=1 | Q Now=Now -3.4%, L -22.1%, H +0.0%, DU; Path=-9.4% → +18.3% | M Now=Now +12.4%, L -9.4%, H +15.1%, DU; Path=+5.8% → -7.2% | S Now=NA; Path=NA | WMA200=-4.0%, UP</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%3,4 / XU030 -%8,8 / Fark +%5,4 puan | M: Hisse +%12,3 / XU030 -%4,7 / Fark +%17,0 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%3,4 / XU030 -%8,7 / Fark +%5,3 puan | M: Hisse +%12,4 / XU030 -%4,6 / Fark +%17,0 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
@@ -2497,7 +2497,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>SHORT - 1 - 1/17
+          <t>SHORT - 1 - 1/18
 SHORT - 1 - 1/14
 UST -  - 3/12</t>
         </is>
@@ -2532,12 +2532,12 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: Action=LATE | Trade_Action=LATE | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -16.0%, L -24.8%, H +0.0%, DU; Path=+14.0% → -18.2% | M Now=Now -4.2%, L -13.5%, H +1.8%, DU; Path=-5.4% → +8.8% | S Now=NA; Path=NA | WMA200=-6.7%, UP</t>
+          <t>NÖTR: Action=LATE | Trade_Action=LATE | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -15.9%, L -24.8%, H +0.0%, DU; Path=+14.0% → -18.2% | M Now=Now -4.1%, L -13.5%, H +1.8%, DU; Path=-5.4% → +8.8% | S Now=NA; Path=NA | WMA200=-6.6%, UP</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%16,0 / XU030 -%8,8 / Fark -%7,2 puan | M: Hisse -%4,2 / XU030 -%4,7 / Fark +%0,5 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%15,9 / XU030 -%8,7 / Fark -%7,2 puan | M: Hisse -%4,1 / XU030 -%4,6 / Fark +%0,5 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="I26" s="4" t="inlineStr">
@@ -2547,7 +2547,7 @@
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU + RİSK: Endeks=XU030 | Karar=AL_ADAYI | AL basari=80 n=10 | SAT basari=34.48275862068966 n=29</t>
+          <t>OLUMLU + RİSK: Endeks=XU030 | Karar=AL_ADAYI | AL basari=80 n=10 | SAT basari=37.93103448275862 n=29</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
@@ -2612,12 +2612,12 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: Action=LATE | Trade_Action=LATE | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -3.2%, L -7.0%, H +7.0%, DU; Path=+13.0% → -18.7% | M Now=Now -2.2%, L -3.8%, H +8.1%, UD; Path=+5.7% → -7.8% | S Now=NA; Path=NA | WMA200=-1.2%, UP</t>
+          <t>NÖTR: Action=LATE | Trade_Action=LATE | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -3.1%, L -7.0%, H +7.0%, DU; Path=+13.0% → -18.7% | M Now=Now -2.1%, L -3.8%, H +8.1%, UD; Path=+5.7% → -7.8% | S Now=NA; Path=NA | WMA200=-1.1%, UP</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%3,2 / XU030 -%8,8 / Fark +%5,6 puan | M: Hisse -%2,2 / XU030 -%4,7 / Fark +%2,5 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%3,1 / XU030 -%8,7 / Fark +%5,6 puan | M: Hisse -%2,1 / XU030 -%4,6 / Fark +%2,5 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="I27" s="4" t="inlineStr">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: Endeks=XU030 | Karar=AL_BEKLE_EŞİK | AL basari=70 n=40 | SAT basari=nan n=0</t>
+          <t>NÖTR: Endeks=XU030 | Karar=AL_BEKLE_EŞİK | AL basari=65 n=40 | SAT basari=nan n=0</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
@@ -2692,12 +2692,12 @@
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: Action=LONG_WATCH | Trade_Action=LONG_WATCH | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -4.4%, L -11.1%, H +7.9%, UD; Path=+17.1% → -14.4% | M Now=Now -4.6%, L -7.1%, H +4.2%, UD; Path=+9.0% → -5.4% | S Now=NA; Path=NA | WMA200=-4.8%, DOWN</t>
+          <t>OLUMLU: Action=LONG_WATCH | Trade_Action=LONG_WATCH | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -4.4%, L -11.1%, H +7.9%, UD; Path=+17.1% → -14.4% | M Now=Now -4.5%, L -7.1%, H +4.2%, UD; Path=+9.0% → -5.4% | S Now=NA; Path=NA | WMA200=-4.7%, DOWN</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%4,4 / XU030 -%8,8 / Fark +%4,4 puan | M: Hisse -%4,6 / XU030 -%4,7 / Fark +%0,1 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%4,4 / XU030 -%8,7 / Fark +%4,3 puan | M: Hisse -%4,5 / XU030 -%4,6 / Fark +%0,1 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="I28" s="5" t="inlineStr">
@@ -2707,7 +2707,7 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: Endeks=XU030 | Karar=ÇELİŞKİLİ_BEKLE | AL basari=73.6842105263158 n=38 | SAT basari=47.61904761904762 n=42</t>
+          <t>NÖTR: Endeks=XU030 | Karar=ÇELİŞKİLİ_BEKLE | AL basari=72.97297297297297 n=37 | SAT basari=46.51162790697674 n=43</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
@@ -2772,12 +2772,12 @@
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: Action=LONG_WATCH | Trade_Action=LONG_WATCH | Önerilen=EVET | Öneren sistem=8 | Q Now=Now -14.5%, L -18.4%, H +5.0%, DU; Path=+21.0% → -13.0% | M Now=Now -3.7%, L -8.1%, H +4.5%, UD; Path=+6.2% → -5.7% | S Now=NA; Path=NA | WMA200=-16.2%, UP</t>
+          <t>OLUMLU: Action=LONG_WATCH | Trade_Action=LONG_WATCH | Önerilen=EVET | Öneren sistem=8 | Q Now=Now -14.4%, L -18.4%, H +5.0%, DU; Path=+21.0% → -13.0% | M Now=Now -3.6%, L -8.1%, H +4.5%, UD; Path=+6.2% → -5.7% | S Now=NA; Path=NA | WMA200=-16.1%, UP</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%14,5 / XU030 -%8,8 / Fark -%5,7 puan | M: Hisse -%3,7 / XU030 -%4,7 / Fark +%1,0 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%14,4 / XU030 -%8,7 / Fark -%5,7 puan | M: Hisse -%3,6 / XU030 -%4,6 / Fark +%1,0 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr">
@@ -2787,7 +2787,7 @@
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=AL_BEKLE_EŞİK | AL basari=51.72413793103448 n=29 | SAT basari=30.61224489795918 n=49</t>
+          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=AL_ADAYI | AL basari=51.72413793103448 n=29 | SAT basari=30.61224489795918 n=49</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: Action=LOW_DATA | Trade_Action=LOW_DATA | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -39.4%, L -42.5%, H +18.0%, UD; Path=+55.7% → -18.8% | M Now=Now -29.3%, L -32.9%, H +0.0%, DU; Path=-12.0% → +16.8% | S Now=NA; Path=NA | WMA200=-33.2%, UP</t>
+          <t>NÖTR: Action=LOW_DATA | Trade_Action=LOW_DATA | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -39.3%, L -42.5%, H +18.0%, UD; Path=+55.7% → -18.8% | M Now=Now -29.3%, L -32.9%, H +0.0%, DU; Path=-12.0% → +16.8% | S Now=NA; Path=NA | WMA200=-33.1%, UP</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%39,4 / XU030 -%8,8 / Fark -%30,6 puan | M: Hisse -%29,3 / XU030 -%4,7 / Fark -%24,6 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%39,3 / XU030 -%8,7 / Fark -%30,6 puan | M: Hisse -%29,3 / XU030 -%4,6 / Fark -%24,7 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="I30" s="4" t="inlineStr">
@@ -2932,12 +2932,12 @@
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: Action=LONG_WATCH | Trade_Action=LONG_WATCH | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -5.8%, L -6.9%, H +8.1%, UD; Path=+17.1% → -21.6% | M Now=Now -8.2%, L -9.3%, H +0.5%, DU; Path=+2.8% → -11.0% | S Now=NA; Path=NA | WMA200=-10.7%, UP</t>
+          <t>OLUMLU: Action=LONG_WATCH | Trade_Action=LONG_WATCH | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -5.7%, L -6.9%, H +8.1%, UD; Path=+17.1% → -21.6% | M Now=Now -8.2%, L -9.3%, H +0.5%, DU; Path=+2.8% → -11.0% | S Now=NA; Path=NA | WMA200=-10.6%, UP</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%5,8 / XU030 -%8,8 / Fark +%3,0 puan | M: Hisse -%8,2 / XU030 -%4,7 / Fark -%3,5 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%5,7 / XU030 -%8,7 / Fark +%3,0 puan | M: Hisse -%8,2 / XU030 -%4,6 / Fark -%3,6 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
@@ -3012,12 +3012,12 @@
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: Action=RISK | Trade_Action=RISK | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -14.0%, L -18.1%, H +3.1%, UD; Path=+12.6% → -19.2% | M Now=Now -3.9%, L -8.6%, H +13.4%, UD; Path=+4.7% → -10.3% | S Now=NA; Path=NA | WMA200=-10.0%, UP</t>
+          <t>OLUMSUZ / RİSK: Action=RISK | Trade_Action=RISK | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -13.9%, L -18.1%, H +3.1%, UD; Path=+12.6% → -19.2% | M Now=Now -3.8%, L -8.6%, H +13.4%, UD; Path=+4.7% → -10.3% | S Now=NA; Path=NA | WMA200=-9.9%, UP</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%14,0 / XU030 -%8,8 / Fark -%5,2 puan | M: Hisse -%3,9 / XU030 -%4,7 / Fark +%0,8 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%13,9 / XU030 -%8,7 / Fark -%5,2 puan | M: Hisse -%3,8 / XU030 -%4,6 / Fark +%0,8 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="I32" s="4" t="inlineStr">
@@ -3027,7 +3027,7 @@
       </c>
       <c r="J32" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=AL_ADAYI | AL basari=50 n=20 | SAT basari=46.51162790697674 n=43</t>
+          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=AL_ADAYI | AL basari=50 n=20 | SAT basari=40.90909090909091 n=44</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: Action=LONG_WATCH | Trade_Action=LONG_WATCH | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -0.6%, L -4.1%, H +11.4%, DU; Path=+12.5% → -12.8% | M Now=Now -4.5%, L -5.6%, H +6.6%, UD; Path=-6.3% → +8.5% | S Now=NA; Path=NA | WMA200=-8.0%, UP</t>
+          <t>OLUMLU: Action=LONG_WATCH | Trade_Action=LONG_WATCH | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -0.5%, L -4.1%, H +11.4%, DU; Path=+12.5% → -12.8% | M Now=Now -4.4%, L -5.6%, H +6.6%, UD; Path=-6.3% → +8.5% | S Now=NA; Path=NA | WMA200=-7.9%, UP</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%0,6 / XU030 -%8,8 / Fark +%8,2 puan | M: Hisse -%4,5 / XU030 -%4,7 / Fark +%0,2 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%0,5 / XU030 -%8,7 / Fark +%8,2 puan | M: Hisse -%4,4 / XU030 -%4,6 / Fark +%0,2 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
@@ -3107,7 +3107,7 @@
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=AL_ADAYI | AL basari=60.52631578947368 n=38 | SAT basari=47.82608695652174 n=23</t>
+          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=AL_ADAYI | AL basari=62.16216216216216 n=37 | SAT basari=45.83333333333334 n=24</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
@@ -3172,12 +3172,12 @@
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: Action=LONG_WATCH | Trade_Action=LONG_WATCH | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -11.1%, L -17.5%, H +8.1%, UD; Path=-8.0% → +22.2% | M Now=Now -1.5%, L -8.7%, H +5.3%, DU; Path=+7.9% → -8.8% | S Now=NA; Path=NA | WMA200=-3.2%, UP</t>
+          <t>OLUMLU: Action=LONG_WATCH | Trade_Action=LONG_WATCH | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -11.0%, L -17.5%, H +8.1%, UD; Path=-8.0% → +22.2% | M Now=Now -1.4%, L -8.7%, H +5.3%, DU; Path=+7.9% → -8.8% | S Now=NA; Path=NA | WMA200=-3.1%, UP</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%11,1 / XU030 -%8,8 / Fark -%2,3 puan | M: Hisse -%1,5 / XU030 -%4,7 / Fark +%3,2 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%11,0 / XU030 -%8,7 / Fark -%2,3 puan | M: Hisse -%1,4 / XU030 -%4,6 / Fark +%3,2 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="I34" s="5" t="inlineStr">
@@ -3187,7 +3187,7 @@
       </c>
       <c r="J34" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=SAT_ADAYI | AL basari=60.71428571428572 n=28 | SAT basari=41.30434782608695 n=46</t>
+          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=SAT_ADAYI | AL basari=51.85185185185185 n=27 | SAT basari=37.5 n=48</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
@@ -3252,12 +3252,12 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: Action=LATE | Trade_Action=LATE | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -14.1%, L -16.0%, H +0.0%, DU; Path=+16.0% → -15.5% | M Now=Now -2.0%, L -4.1%, H +8.2%, DU; Path=+6.4% → -9.1% | S Now=NA; Path=NA | WMA200=-17.9%, UP</t>
+          <t>NÖTR: Action=LATE | Trade_Action=LATE | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -14.0%, L -16.0%, H +0.0%, DU; Path=+16.0% → -15.5% | M Now=Now -1.9%, L -4.1%, H +8.2%, DU; Path=+6.4% → -9.1% | S Now=NA; Path=NA | WMA200=-17.8%, UP</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%14,1 / XU030 -%8,8 / Fark -%5,3 puan | M: Hisse -%2,0 / XU030 -%4,7 / Fark +%2,7 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%14,0 / XU030 -%8,7 / Fark -%5,3 puan | M: Hisse -%1,9 / XU030 -%4,6 / Fark +%2,7 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="I35" s="4" t="inlineStr">
@@ -3267,7 +3267,7 @@
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=AL_BEKLE_EŞİK | AL basari=66.66666666666667 n=36 | SAT basari=47.61904761904762 n=42</t>
+          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=AL_BEKLE_EŞİK | AL basari=67.56756756756756 n=37 | SAT basari=45.23809523809524 n=42</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
@@ -3298,8 +3298,8 @@
       <c r="P35" s="2" t="inlineStr">
         <is>
           <t>LONG - 7 - 9/2
-LONG - 90 - 13/7
-ALT -  - 28/4</t>
+LONG - 90 - 13/8
+ALT -  - 27/4</t>
         </is>
       </c>
     </row>
@@ -3332,12 +3332,12 @@
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: Action=LONG_WATCH | Trade_Action=LONG_WATCH | Önerilen=EVET | Öneren sistem=9 | Q Now=Now -10.7%, L -16.3%, H +0.0%, DU; Path=+15.8% → -15.9% | M Now=Now -3.7%, L -9.8%, H +1.9%, DU; Path=+7.9% → -7.8% | S Now=NA; Path=NA | WMA200=-7.8%, UP</t>
+          <t>OLUMLU: Action=LONG_WATCH | Trade_Action=LONG_WATCH | Önerilen=EVET | Öneren sistem=9 | Q Now=Now -10.6%, L -16.3%, H +0.0%, DU; Path=+15.8% → -15.9% | M Now=Now -3.6%, L -9.8%, H +1.9%, DU; Path=+7.9% → -7.8% | S Now=NA; Path=NA | WMA200=-7.8%, UP</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%10,7 / XU030 -%8,8 / Fark -%1,9 puan | M: Hisse -%3,7 / XU030 -%4,7 / Fark +%1,0 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%10,6 / XU030 -%8,7 / Fark -%1,9 puan | M: Hisse -%3,6 / XU030 -%4,6 / Fark +%1,0 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
@@ -3347,7 +3347,7 @@
       </c>
       <c r="J36" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=AL_ADAYI | AL basari=45.83333333333334 n=24 | SAT basari=38.23529411764706 n=34</t>
+          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=AL_ADAYI | AL basari=43.47826086956522 n=23 | SAT basari=38.23529411764706 n=34</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>LONG - 7 - 11/6
+          <t>LONG - 7 - 10/6
 LONG - 7 - 8/4
 LONG - 85 - 13/8</t>
         </is>
@@ -3412,12 +3412,12 @@
       </c>
       <c r="G37" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: Action=LONG_WATCH | Trade_Action=LONG_WATCH | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -17.8%, L -17.8%, H +9.3%, DU; Path=+25.2% → -19.7% | M Now=Now -18.2%, L -18.2%, H +0.0%, DU; Path=-6.5% → +3.5% | S Now=NA; Path=NA | WMA200=-21.4%, UP</t>
+          <t>OLUMLU: Action=LONG_WATCH | Trade_Action=LONG_WATCH | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -17.7%, L -17.7%, H +9.3%, DU; Path=+25.2% → -19.7% | M Now=Now -18.1%, L -18.1%, H +0.0%, DU; Path=-6.5% → +3.5% | S Now=NA; Path=NA | WMA200=-21.4%, UP</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%17,8 / XU030 -%8,8 / Fark -%9,0 puan | M: Hisse -%18,2 / XU030 -%4,7 / Fark -%13,5 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%17,7 / XU030 -%8,7 / Fark -%9,0 puan | M: Hisse -%18,1 / XU030 -%4,6 / Fark -%13,5 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: Action=LATE | Trade_Action=LATE | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -35.9%, L -36.3%, H +1.4%, DU; Path=+16.9% → -12.8% | M Now=Now -20.7%, L -21.2%, H +10.3%, DU; Path=+5.7% → -8.6% | S Now=NA; Path=NA | WMA200=-34.7%, UP</t>
+          <t>NÖTR: Action=LATE | Trade_Action=LATE | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -35.8%, L -36.3%, H +1.4%, DU; Path=+16.9% → -12.8% | M Now=Now -20.6%, L -21.2%, H +10.3%, DU; Path=+5.7% → -8.6% | S Now=NA; Path=NA | WMA200=-34.7%, UP</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%35,9 / XU030 -%8,8 / Fark -%27,1 puan | M: Hisse -%20,7 / XU030 -%4,7 / Fark -%16,0 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%35,8 / XU030 -%8,7 / Fark -%27,1 puan | M: Hisse -%20,6 / XU030 -%4,6 / Fark -%16,0 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="I38" s="5" t="inlineStr">
@@ -3572,12 +3572,12 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: Action=NO_CLEAR_EDGE | Trade_Action=NO_CLEAR_EDGE | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -5.7%, L -14.4%, H +6.5%, UD; Path=+14.1% → -12.0% | M Now=Now +1.1%, L -8.2%, H +3.4%, DU; Path=+8.9% → -10.3% | S Now=NA; Path=NA | WMA200=-11.1%, UP</t>
+          <t>NÖTR: Action=NO_CLEAR_EDGE | Trade_Action=NO_CLEAR_EDGE | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -5.6%, L -14.4%, H +6.5%, UD; Path=+14.1% → -12.0% | M Now=Now +1.2%, L -8.2%, H +3.4%, DU; Path=+8.9% → -10.3% | S Now=NA; Path=NA | WMA200=-11.1%, UP</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%5,7 / XU030 -%8,8 / Fark +%3,1 puan | M: Hisse +%1,1 / XU030 -%4,7 / Fark +%5,8 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%5,6 / XU030 -%8,7 / Fark +%3,1 puan | M: Hisse +%1,2 / XU030 -%4,6 / Fark +%5,8 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="I39" s="4" t="inlineStr">
@@ -3587,7 +3587,7 @@
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=AL_ADAYI | AL basari=76.92307692307692 n=13 | SAT basari=33.33333333333334 n=30</t>
+          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=AL_ADAYI | AL basari=76.92307692307692 n=13 | SAT basari=30.3030303030303 n=33</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: Action=LONG_WATCH | Trade_Action=LONG_WATCH | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -24.3%, L -27.5%, H +0.0%, DU; Path=+12.7% → -16.4% | M Now=Now -2.4%, L -6.6%, H +2.8%, DU; Path=+6.3% → -8.8% | S Now=NA; Path=NA | WMA200=-19.3%, UP</t>
+          <t>OLUMLU: Action=LONG_WATCH | Trade_Action=LONG_WATCH | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -24.2%, L -27.5%, H +0.0%, DU; Path=+12.7% → -16.4% | M Now=Now -2.3%, L -6.6%, H +2.8%, DU; Path=+6.3% → -8.8% | S Now=NA; Path=NA | WMA200=-19.2%, UP</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%24,3 / XU030 -%8,8 / Fark -%15,5 puan | M: Hisse -%2,4 / XU030 -%4,7 / Fark +%2,3 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%24,2 / XU030 -%8,7 / Fark -%15,5 puan | M: Hisse -%2,3 / XU030 -%4,6 / Fark +%2,3 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="I40" s="5" t="inlineStr">
@@ -3667,7 +3667,7 @@
       </c>
       <c r="J40" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=SAT_ADAYI | AL basari=58.33333333333334 n=24 | SAT basari=48.48484848484848 n=33</t>
+          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=AL_BEKLE_EŞİK | AL basari=58.33333333333334 n=24 | SAT basari=45.45454545454545 n=33</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
@@ -3732,12 +3732,12 @@
       </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: Action=LONG_WATCH | Trade_Action=LONG_WATCH | Önerilen=EVET | Öneren sistem=2 | Q Now=Now -3.5%, L -10.7%, H +7.6%, DU; Path=+13.4% → -15.8% | M Now=Now -4.1%, L -11.3%, H +3.0%, DU; Path=+5.1% → -7.8% | S Now=NA; Path=NA | WMA200=-9.6%, UP</t>
+          <t>OLUMLU: Action=LONG_WATCH | Trade_Action=LONG_WATCH | Önerilen=EVET | Öneren sistem=2 | Q Now=Now -3.4%, L -10.7%, H +7.6%, DU; Path=+13.4% → -15.8% | M Now=Now -4.0%, L -11.3%, H +3.0%, DU; Path=+5.1% → -7.8% | S Now=NA; Path=NA | WMA200=-9.5%, UP</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%3,5 / XU030 -%8,8 / Fark +%5,3 puan | M: Hisse -%4,1 / XU030 -%4,7 / Fark +%0,6 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%3,4 / XU030 -%8,7 / Fark +%5,3 puan | M: Hisse -%4,0 / XU030 -%4,6 / Fark +%0,6 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
@@ -3778,7 +3778,7 @@
       <c r="P41" s="2" t="inlineStr">
         <is>
           <t>LONG - 4 - 9/3
-LONG - 4 - 7/4
+LONG - 4 - 6/4
 LONG - 4 - 9/3</t>
         </is>
       </c>
@@ -3812,12 +3812,12 @@
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: Action=LONG_READY | Trade_Action=LONG_READY | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -20.8%, L -21.2%, H +0.2%, DU; Path=-15.5% → +24.8% | M Now=Now -4.8%, L -5.2%, H +2.4%, DU; Path=-9.4% → +8.7% | S Now=NA; Path=NA | WMA200=-17.6%, UP</t>
+          <t>OLUMLU: Action=LONG_READY | Trade_Action=LONG_READY | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -20.8%, L -21.2%, H +0.2%, DU; Path=-15.5% → +24.8% | M Now=Now -4.7%, L -5.2%, H +2.4%, DU; Path=-9.4% → +8.7% | S Now=NA; Path=NA | WMA200=-17.5%, UP</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%20,8 / XU030 -%8,8 / Fark -%12,0 puan | M: Hisse -%4,8 / XU030 -%4,7 / Fark -%0,1 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%20,8 / XU030 -%8,7 / Fark -%12,1 puan | M: Hisse -%4,7 / XU030 -%4,6 / Fark -%0,1 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: Action=LONG_READY | Trade_Action=LONG_READY | Önerilen=EVET | Öneren sistem=2 | Q Now=Now -27.7%, L -27.7%, H +0.0%, DU; Path=-7.1% → +16.1% | M Now=Now -15.3%, L -15.3%, H +6.9%, DU; Path=-4.6% → +9.3% | S Now=NA; Path=NA | WMA200=-26.6%, UP</t>
+          <t>OLUMLU: Action=LONG_READY | Trade_Action=LONG_READY | Önerilen=EVET | Öneren sistem=2 | Q Now=Now -27.7%, L -27.7%, H +0.0%, DU; Path=-7.1% → +16.1% | M Now=Now -15.2%, L -15.2%, H +6.9%, DU; Path=-4.6% → +9.3% | S Now=NA; Path=NA | WMA200=-26.6%, UP</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%27,7 / XU030 -%8,8 / Fark -%18,9 puan | M: Hisse -%15,3 / XU030 -%4,7 / Fark -%10,6 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%27,7 / XU030 -%8,7 / Fark -%19,0 puan | M: Hisse -%15,2 / XU030 -%4,6 / Fark -%10,6 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="I43" s="5" t="inlineStr">
@@ -3937,9 +3937,9 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>LONG - 7 - 10/2
-SHORT - 94 - 25/8
-ALT -  - 17/4</t>
+          <t>LONG - 7 - 10/3
+SHORT - 94 - 24/8
+ALT -  - 17/3</t>
         </is>
       </c>
     </row>
@@ -3972,12 +3972,12 @@
       </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: Action=RISK | Trade_Action=RISK | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now +17.1%, L -6.4%, H +26.5%, DU; Path=+14.4% → -14.8% | M Now=Now -0.2%, L -1.3%, H +7.9%, UD; Path=-9.8% → +4.5% | S Now=NA; Path=NA | WMA200=+1.5%, UP</t>
+          <t>OLUMSUZ / RİSK: Action=RISK | Trade_Action=RISK | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now +17.2%, L -6.4%, H +26.5%, DU; Path=+14.4% → -14.8% | M Now=Now -0.1%, L -1.3%, H +7.9%, UD; Path=-9.8% → +4.5% | S Now=NA; Path=NA | WMA200=+1.6%, UP</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse +%17,1 / XU030 -%8,8 / Fark +%25,9 puan | M: Hisse -%0,2 / XU030 -%4,7 / Fark +%4,5 puan | S: VERİ YOK</t>
+          <t>Q: Hisse +%17,2 / XU030 -%8,7 / Fark +%25,9 puan | M: Hisse -%0,1 / XU030 -%4,6 / Fark +%4,5 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="I44" s="4" t="inlineStr">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="J44" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=SAT_BEKLE_EŞİK | AL basari=42.5531914893617 n=47 | SAT basari=77.77777777777777 n=9</t>
+          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=SAT_BEKLE_EŞİK | AL basari=45.65217391304348 n=46 | SAT basari=77.77777777777777 n=9</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
@@ -4052,12 +4052,12 @@
       </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: Action=LATE | Trade_Action=LATE | Önerilen=EVET | Öneren sistem=6 | Q Now=Now -9.0%, L -15.3%, H +0.0%, DU; Path=-12.2% → +15.5% | M Now=Now +3.3%, L -3.8%, H +6.7%, UD; Path=-5.6% → +8.7% | S Now=NA; Path=NA | WMA200=-8.6%, UP</t>
+          <t>OLUMLU: Action=LATE | Trade_Action=LATE | Önerilen=EVET | Öneren sistem=6 | Q Now=Now -9.0%, L -15.3%, H +0.0%, DU; Path=-12.2% → +15.5% | M Now=Now +3.4%, L -3.8%, H +6.7%, UD; Path=-5.6% → +8.7% | S Now=NA; Path=NA | WMA200=-8.5%, UP</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%9,0 / XU030 -%8,8 / Fark -%0,2 puan | M: Hisse +%3,3 / XU030 -%4,7 / Fark +%8,0 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%9,0 / XU030 -%8,7 / Fark -%0,3 puan | M: Hisse +%3,4 / XU030 -%4,6 / Fark +%8,0 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="I45" s="5" t="inlineStr">
@@ -4067,7 +4067,7 @@
       </c>
       <c r="J45" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=SAT_BEKLE_EŞİK | AL basari=52.38095238095238 n=21 | SAT basari=27.77777777777778 n=36</t>
+          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=SAT_BEKLE_EŞİK | AL basari=55 n=20 | SAT basari=27.02702702702703 n=37</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
@@ -4097,8 +4097,8 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>LONG - 7 - 10/6
-LONG - 7 - 10/6
+          <t>LONG - 7 - 10/7
+LONG - 7 - 10/7
 LONG - 7 - 5/5</t>
         </is>
       </c>
@@ -4132,12 +4132,12 @@
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: Action=LONG_READY | Trade_Action=LONG_READY | Önerilen=EVET | Öneren sistem=2 | Q Now=Now -15.7%, L -20.3%, H +5.6%, UD; Path=-10.0% → +23.6% | M Now=Now -4.9%, L -10.2%, H +0.8%, DU; Path=+5.6% → -7.2% | S Now=NA; Path=NA | WMA200=-10.3%, UP</t>
+          <t>OLUMLU: Action=LONG_READY | Trade_Action=LONG_READY | Önerilen=EVET | Öneren sistem=2 | Q Now=Now -15.6%, L -20.3%, H +5.6%, UD; Path=-10.0% → +23.6% | M Now=Now -4.8%, L -10.2%, H +0.8%, DU; Path=+5.6% → -7.2% | S Now=NA; Path=NA | WMA200=-10.2%, UP</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%15,7 / XU030 -%8,8 / Fark -%6,9 puan | M: Hisse -%4,9 / XU030 -%4,7 / Fark -%0,2 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%15,6 / XU030 -%8,7 / Fark -%6,9 puan | M: Hisse -%4,8 / XU030 -%4,6 / Fark -%0,2 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="I46" s="5" t="inlineStr">
@@ -4147,7 +4147,7 @@
       </c>
       <c r="J46" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=SAT_BEKLE_EŞİK | AL basari=35.29411764705883 n=17 | SAT basari=56.25 n=32</t>
+          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=SAT_BEKLE_EŞİK | AL basari=35.29411764705883 n=17 | SAT basari=53.125 n=32</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: Action=LATE | Trade_Action=LATE | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -9.4%, L -17.5%, H +0.4%, DU; Path=+17.2% → -16.4% | M Now=Now +6.7%, L -2.9%, H +11.1%, DU; Path=+8.4% → -6.5% | S Now=NA; Path=NA | WMA200=-5.5%, UP</t>
+          <t>NÖTR: Action=LATE | Trade_Action=LATE | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -9.3%, L -17.5%, H +0.4%, DU; Path=+17.2% → -16.4% | M Now=Now +6.8%, L -2.9%, H +11.1%, DU; Path=+8.4% → -6.5% | S Now=NA; Path=NA | WMA200=-5.4%, UP</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%9,4 / XU030 -%8,8 / Fark -%0,6 puan | M: Hisse +%6,7 / XU030 -%4,7 / Fark +%11,4 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%9,3 / XU030 -%8,7 / Fark -%0,6 puan | M: Hisse +%6,8 / XU030 -%4,6 / Fark +%11,4 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="I47" s="4" t="inlineStr">
@@ -4227,7 +4227,7 @@
       </c>
       <c r="J47" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=AL_ADAYI | AL basari=46.66666666666666 n=30 | SAT basari=51.28205128205128 n=39</t>
+          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=AL_ADAYI | AL basari=44.82758620689656 n=29 | SAT basari=51.28205128205128 n=39</t>
         </is>
       </c>
       <c r="K47" s="3" t="inlineStr">
@@ -4292,12 +4292,12 @@
       </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: Action=LONG_WATCH | Trade_Action=LONG_WATCH | Önerilen=EVET | Öneren sistem=3 | Q Now=Now +12.6%, L +0.0%, H +20.5%, UD; Path=-15.7% → +35.9% | M Now=Now -0.5%, L -5.5%, H +5.1%, UD; Path=+8.6% → -6.0% | S Now=NA; Path=NA | WMA200=+2.3%, UP</t>
+          <t>OLUMLU: Action=LONG_WATCH | Trade_Action=LONG_WATCH | Önerilen=EVET | Öneren sistem=3 | Q Now=Now +12.7%, L +0.0%, H +20.5%, UD; Path=-15.7% → +35.9% | M Now=Now -0.4%, L -5.5%, H +5.1%, UD; Path=+8.6% → -6.0% | S Now=NA; Path=NA | WMA200=+2.4%, UP</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse +%12,6 / XU030 -%8,8 / Fark +%21,4 puan | M: Hisse -%0,5 / XU030 -%4,7 / Fark +%4,2 puan | S: VERİ YOK</t>
+          <t>Q: Hisse +%12,7 / XU030 -%8,7 / Fark +%21,4 puan | M: Hisse -%0,4 / XU030 -%4,6 / Fark +%4,2 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="I48" s="5" t="inlineStr">
@@ -4307,7 +4307,7 @@
       </c>
       <c r="J48" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=AL_ADAYI | AL basari=66.66666666666667 n=69 | SAT basari=37.5 n=24</t>
+          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=AL_ADAYI | AL basari=64.70588235294117 n=68 | SAT basari=37.5 n=24</t>
         </is>
       </c>
       <c r="K48" s="3" t="inlineStr">
@@ -4372,12 +4372,12 @@
       </c>
       <c r="G49" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: Action=LONG_WATCH | Trade_Action=LONG_WATCH | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -15.6%, L -17.8%, H +0.5%, DU; Path=+9.6% → -16.3% | M Now=Now -3.8%, L -6.3%, H +6.0%, UD; Path=-3.7% → +8.7% | S Now=NA; Path=NA | WMA200=-20.4%, UP</t>
+          <t>OLUMLU: Action=LONG_WATCH | Trade_Action=LONG_WATCH | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -15.5%, L -17.8%, H +0.5%, DU; Path=+9.6% → -16.3% | M Now=Now -3.7%, L -6.3%, H +6.0%, UD; Path=-3.7% → +8.7% | S Now=NA; Path=NA | WMA200=-20.3%, UP</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%15,6 / XU030 -%8,8 / Fark -%6,8 puan | M: Hisse -%3,8 / XU030 -%4,7 / Fark +%0,9 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%15,5 / XU030 -%8,7 / Fark -%6,8 puan | M: Hisse -%3,7 / XU030 -%4,6 / Fark +%0,9 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="I49" s="5" t="inlineStr">
@@ -4419,7 +4419,7 @@
         <is>
           <t>LONG - 7 - 9/1
 LONG - 7 - 9/1
-LONG - 7 - 9/1</t>
+LONG - 7 - 9/2</t>
         </is>
       </c>
     </row>
@@ -4452,12 +4452,12 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: Action=LATE | Trade_Action=LATE | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -4.9%, L -13.9%, H +2.5%, DU; Path=+19.2% → -18.0% | M Now=Now +3.5%, L +0.0%, H +9.4%, UD; Path=-5.8% → +9.2% | S Now=NA; Path=NA | WMA200=-2.0%, UP</t>
+          <t>NÖTR: Action=LATE | Trade_Action=LATE | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -4.8%, L -13.9%, H +2.5%, DU; Path=+19.2% → -18.0% | M Now=Now +3.6%, L +0.0%, H +9.4%, UD; Path=-5.8% → +9.2% | S Now=NA; Path=NA | WMA200=-1.9%, UP</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%4,9 / XU030 -%8,8 / Fark +%3,9 puan | M: Hisse +%3,5 / XU030 -%4,7 / Fark +%8,2 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%4,8 / XU030 -%8,7 / Fark +%3,9 puan | M: Hisse +%3,6 / XU030 -%4,6 / Fark +%8,2 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="I50" s="3" t="inlineStr">
@@ -4467,7 +4467,7 @@
       </c>
       <c r="J50" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=AL_BEKLE_EŞİK | AL basari=55.81395348837209 n=43 | SAT basari=43.33333333333334 n=30</t>
+          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=AL_BEKLE_EŞİK | AL basari=55.81395348837209 n=43 | SAT basari=38.70967741935484 n=31</t>
         </is>
       </c>
       <c r="K50" s="3" t="inlineStr">
@@ -4532,12 +4532,12 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: Action=LATE | Trade_Action=LATE | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -13.2%, L -22.1%, H +0.1%, DU; Path=+14.7% → -16.2% | M Now=Now -2.8%, L -10.1%, H +3.8%, UD; Path=-6.2% → +10.3% | S Now=NA; Path=NA | WMA200=-6.9%, UP</t>
+          <t>NÖTR: Action=LATE | Trade_Action=LATE | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -13.1%, L -22.1%, H +0.1%, DU; Path=+14.7% → -16.2% | M Now=Now -2.8%, L -10.1%, H +3.8%, UD; Path=-6.2% → +10.3% | S Now=NA; Path=NA | WMA200=-6.8%, UP</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%13,2 / XU030 -%8,8 / Fark -%4,4 puan | M: Hisse -%2,8 / XU030 -%4,7 / Fark +%1,9 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%13,1 / XU030 -%8,7 / Fark -%4,4 puan | M: Hisse -%2,8 / XU030 -%4,6 / Fark +%1,8 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="I51" s="5" t="inlineStr">
@@ -4547,7 +4547,7 @@
       </c>
       <c r="J51" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=AL_ADAYI | AL basari=53.84615384615385 n=13 | SAT basari=45.45454545454545 n=33</t>
+          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=AL_ADAYI | AL basari=53.84615384615385 n=13 | SAT basari=51.51515151515152 n=33</t>
         </is>
       </c>
       <c r="K51" s="3" t="inlineStr">
@@ -4612,12 +4612,12 @@
       </c>
       <c r="G52" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: Action=RISK | Trade_Action=RISK | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -13.5%, L -14.6%, H +7.2%, DU; Path=+10.1% → -13.9% | M Now=Now -0.4%, L -1.6%, H +7.5%, UD; Path=+6.0% → -5.9% | S Now=NA; Path=NA | WMA200=-8.5%, UP</t>
+          <t>OLUMSUZ / RİSK: Action=RISK | Trade_Action=RISK | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -13.4%, L -14.6%, H +7.2%, DU; Path=+10.1% → -13.9% | M Now=Now -0.3%, L -1.6%, H +7.5%, UD; Path=+6.0% → -5.9% | S Now=NA; Path=NA | WMA200=-8.5%, UP</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%13,5 / XU030 -%8,8 / Fark -%4,7 puan | M: Hisse -%0,4 / XU030 -%4,7 / Fark +%4,3 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%13,4 / XU030 -%8,7 / Fark -%4,7 puan | M: Hisse -%0,3 / XU030 -%4,6 / Fark +%4,3 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="I52" s="3" t="inlineStr">
@@ -4627,7 +4627,7 @@
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: Endeks=XU030 | Karar=AL_ADAYI | AL basari=54.54545454545455 n=44 | SAT basari=nan n=0</t>
+          <t>NÖTR: Endeks=XU030 | Karar=AL_ADAYI | AL basari=52.27272727272727 n=44 | SAT basari=nan n=0</t>
         </is>
       </c>
       <c r="K52" s="3" t="inlineStr">
@@ -4658,8 +4658,8 @@
       <c r="P52" s="2" t="inlineStr">
         <is>
           <t>ALT -  - 15/4
-ALT -  - 15/4
-ALT -  - 15/4</t>
+ALT -  - 14/4
+ALT -  - 14/4</t>
         </is>
       </c>
     </row>
@@ -4692,12 +4692,12 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: Action=LOW_DATA | Trade_Action=LOW_DATA | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -27.8%, L -27.8%, H +8.0%, UD; Path=+31.1% → -30.5% | M Now=Now -25.9%, L -25.9%, H +4.1%, DU; Path=-12.0% → +13.4% | S Now=NA; Path=NA | WMA200=-23.8%, UP</t>
+          <t>NÖTR: Action=LOW_DATA | Trade_Action=LOW_DATA | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -27.8%, L -27.8%, H +8.0%, UD; Path=+31.1% → -30.5% | M Now=Now -25.8%, L -25.9%, H +4.1%, DU; Path=-12.0% → +13.4% | S Now=NA; Path=NA | WMA200=-23.7%, UP</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%27,8 / XU030 -%8,8 / Fark -%19,0 puan | M: Hisse -%25,9 / XU030 -%4,7 / Fark -%21,2 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%27,8 / XU030 -%8,7 / Fark -%19,1 puan | M: Hisse -%25,8 / XU030 -%4,6 / Fark -%21,2 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="I53" s="3" t="inlineStr">
@@ -4772,12 +4772,12 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: Action=NO_CLEAR_EDGE | Trade_Action=NO_CLEAR_EDGE | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -18.1%, L -18.1%, H +0.3%, DU; Path=-12.9% → +17.2% | M Now=Now -6.3%, L -6.3%, H +5.4%, UD; Path=-5.2% → +10.0% | S Now=NA; Path=NA | WMA200=-20.3%, UP</t>
+          <t>NÖTR: Action=NO_CLEAR_EDGE | Trade_Action=NO_CLEAR_EDGE | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -18.0%, L -18.0%, H +0.3%, DU; Path=-12.9% → +17.2% | M Now=Now -6.2%, L -6.2%, H +5.4%, UD; Path=-5.2% → +10.0% | S Now=NA; Path=NA | WMA200=-20.3%, UP</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%18,1 / XU030 -%8,8 / Fark -%9,3 puan | M: Hisse -%6,3 / XU030 -%4,7 / Fark -%1,6 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%18,0 / XU030 -%8,7 / Fark -%9,3 puan | M: Hisse -%6,2 / XU030 -%4,6 / Fark -%1,6 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="I54" s="5" t="inlineStr">
@@ -4818,7 +4818,7 @@
       <c r="P54" s="2" t="inlineStr">
         <is>
           <t>ALT -  - 37/1
-ALT -  - 38/2
+ALT -  - 37/2
 ALT -  - 12/1</t>
         </is>
       </c>
@@ -4852,12 +4852,12 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: Action=LATE | Trade_Action=LATE | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now +14.3%, L -8.6%, H +30.5%, DU; Path=+21.6% → -15.9% | M Now=Now -6.3%, L -10.5%, H +2.7%, DU; Path=+4.3% → -7.8% | S Now=NA; Path=NA | WMA200=+6.1%, DOWN</t>
+          <t>NÖTR: Action=LATE | Trade_Action=LATE | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now +14.4%, L -8.6%, H +30.5%, DU; Path=+21.6% → -15.9% | M Now=Now -6.2%, L -10.5%, H +2.7%, DU; Path=+4.3% → -7.8% | S Now=NA; Path=NA | WMA200=+6.2%, DOWN</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse +%14,3 / XU030 -%8,8 / Fark +%23,1 puan | M: Hisse -%6,3 / XU030 -%4,7 / Fark -%1,6 puan | S: VERİ YOK</t>
+          <t>Q: Hisse +%14,4 / XU030 -%8,7 / Fark +%23,1 puan | M: Hisse -%6,2 / XU030 -%4,6 / Fark -%1,6 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="I55" s="3" t="inlineStr">
@@ -4867,7 +4867,7 @@
       </c>
       <c r="J55" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=AL_ADAYI | AL basari=66.66666666666667 n=15 | SAT basari=31.74603174603175 n=63</t>
+          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=AL_ADAYI | AL basari=62.5 n=16 | SAT basari=31.74603174603175 n=63</t>
         </is>
       </c>
       <c r="K55" s="3" t="inlineStr">
@@ -4932,12 +4932,12 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: Action=LATE | Trade_Action=LATE | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -11.9%, L -17.1%, H +0.0%, DU; Path=-7.0% → +14.7% | M Now=Now -4.1%, L -8.6%, H +2.0%, DU; Path=-5.9% → +5.4% | S Now=NA; Path=NA | WMA200=-10.9%, UP</t>
+          <t>NÖTR: Action=LATE | Trade_Action=LATE | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -11.9%, L -17.1%, H +0.0%, DU; Path=-7.0% → +14.7% | M Now=Now -4.0%, L -8.6%, H +2.0%, DU; Path=-5.9% → +5.4% | S Now=NA; Path=NA | WMA200=-10.8%, UP</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%11,9 / XU030 -%8,8 / Fark -%3,1 puan | M: Hisse -%4,1 / XU030 -%4,7 / Fark +%0,6 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%11,9 / XU030 -%8,7 / Fark -%3,2 puan | M: Hisse -%4,0 / XU030 -%4,6 / Fark +%0,6 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="I56" s="3" t="inlineStr">
@@ -4947,7 +4947,7 @@
       </c>
       <c r="J56" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=AL_ADAYI | AL basari=48.48484848484848 n=33 | SAT basari=25.64102564102564 n=39</t>
+          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=AL_ADAYI | AL basari=48.48484848484848 n=33 | SAT basari=23.07692307692308 n=39</t>
         </is>
       </c>
       <c r="K56" s="3" t="inlineStr">
@@ -5012,12 +5012,12 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: Action=LOW_DATA | Trade_Action=LOW_DATA | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -31.1%, L -36.1%, H +22.7%, DU; Path=-2.8% → +14.1% | M Now=Now -34.3%, L -39.1%, H +0.0%, DU; Path=-8.7% → +14.1% | S Now=NA; Path=NA | WMA200=-19.2%, UP</t>
+          <t>NÖTR: Action=LOW_DATA | Trade_Action=LOW_DATA | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -31.1%, L -36.1%, H +22.7%, DU; Path=-2.8% → +14.1% | M Now=Now -34.3%, L -39.1%, H +0.0%, DU; Path=-8.7% → +14.1% | S Now=NA; Path=NA | WMA200=-19.1%, UP</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%31,1 / XU030 -%8,8 / Fark -%22,3 puan | M: Hisse -%34,3 / XU030 -%4,7 / Fark -%29,6 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%31,1 / XU030 -%8,7 / Fark -%22,4 puan | M: Hisse -%34,3 / XU030 -%4,6 / Fark -%29,7 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="I57" s="5" t="inlineStr">
@@ -5057,7 +5057,7 @@
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>ALT -  - 16/2
+          <t>ALT -  - 15/2
 ALT -  - 31/7
 -</t>
         </is>
@@ -5092,12 +5092,12 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: Action=LOW_DATA | Trade_Action=LOW_DATA | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -33.2%, L -34.2%, H +0.0%, DU; Path=-11.3% → +35.4% | M Now=Now -20.9%, L -22.0%, H +4.0%, DU; Path=+5.2% → -12.4% | S Now=NA; Path=NA | WMA200=-33.5%, UP</t>
+          <t>NÖTR: Action=LOW_DATA | Trade_Action=LOW_DATA | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -33.2%, L -34.2%, H +0.0%, DU; Path=-11.3% → +35.4% | M Now=Now -20.8%, L -22.0%, H +4.0%, DU; Path=+5.2% → -12.4% | S Now=NA; Path=NA | WMA200=-33.4%, UP</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%33,2 / XU030 -%8,8 / Fark -%24,4 puan | M: Hisse -%20,9 / XU030 -%4,7 / Fark -%16,2 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%33,2 / XU030 -%8,7 / Fark -%24,5 puan | M: Hisse -%20,8 / XU030 -%4,6 / Fark -%16,2 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="I58" s="5" t="inlineStr">
@@ -5172,12 +5172,12 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: Action=LATE | Trade_Action=LATE | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -20.9%, L -21.3%, H +12.0%, UD; Path=+10.1% → -19.8% | M Now=Now -21.8%, L -22.3%, H +0.0%, DU; Path=-7.5% → +9.0% | S Now=NA; Path=NA | WMA200=-26.1%, UP</t>
+          <t>NÖTR: Action=LATE | Trade_Action=LATE | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -20.8%, L -21.3%, H +12.0%, UD; Path=+10.1% → -19.8% | M Now=Now -21.8%, L -22.3%, H +0.0%, DU; Path=-7.5% → +9.0% | S Now=NA; Path=NA | WMA200=-26.0%, UP</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%20,9 / XU030 -%8,8 / Fark -%12,1 puan | M: Hisse -%21,8 / XU030 -%4,7 / Fark -%17,1 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%20,8 / XU030 -%8,7 / Fark -%12,1 puan | M: Hisse -%21,8 / XU030 -%4,6 / Fark -%17,2 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="I59" s="5" t="inlineStr">
@@ -5217,7 +5217,7 @@
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>ALT -  - 54/14
+          <t>ALT -  - 54/13
 ALT -  - 15/4
 ALT -  - 15/4</t>
         </is>
@@ -5252,12 +5252,12 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: Action=LOW_DATA | Trade_Action=LOW_DATA | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -17.1%, L -21.8%, H +6.0%, DU; Path=-4.3% → +53.0% | M Now=Now -12.5%, L -17.4%, H +6.3%, DU; Path=+17.4% → -14.4% | S Now=NA; Path=NA | WMA200=-19.7%, UP</t>
+          <t>NÖTR: Action=LOW_DATA | Trade_Action=LOW_DATA | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -17.0%, L -21.8%, H +6.0%, DU; Path=-4.3% → +53.0% | M Now=Now -12.4%, L -17.4%, H +6.3%, DU; Path=+17.4% → -14.4% | S Now=NA; Path=NA | WMA200=-19.6%, UP</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%17,1 / XU030 -%8,8 / Fark -%8,3 puan | M: Hisse -%12,5 / XU030 -%4,7 / Fark -%7,8 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%17,0 / XU030 -%8,7 / Fark -%8,3 puan | M: Hisse -%12,4 / XU030 -%4,6 / Fark -%7,8 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="I60" s="3" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: Action=LATE | Trade_Action=LATE | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -3.2%, L -28.3%, H +18.5%, UD; Path=+12.4% → -19.7% | M Now=Now +8.3%, L +0.0%, H +32.5%, UD; Path=+10.8% → -9.9% | S Now=NA; Path=NA | WMA200=+2.0%, DOWN</t>
+          <t>NÖTR: Action=LATE | Trade_Action=LATE | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -3.1%, L -28.3%, H +18.5%, UD; Path=+12.4% → -19.7% | M Now=Now +8.4%, L +0.0%, H +32.5%, UD; Path=+10.8% → -9.9% | S Now=NA; Path=NA | WMA200=+2.1%, DOWN</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%3,2 / XU030 -%8,8 / Fark +%5,6 puan | M: Hisse +%8,3 / XU030 -%4,7 / Fark +%13,0 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%3,1 / XU030 -%8,7 / Fark +%5,6 puan | M: Hisse +%8,4 / XU030 -%4,6 / Fark +%13,0 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="I61" s="3" t="inlineStr">
@@ -5379,7 +5379,7 @@
         <is>
           <t>SHORT - 10 - 15/15
 SHORT - 10 - 10/19
-SHORT - 2 - 3/9</t>
+SHORT - 2 - 2/9</t>
         </is>
       </c>
     </row>
@@ -5412,12 +5412,12 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: Action=LATE | Trade_Action=LATE | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -16.6%, L -21.5%, H +0.0%, DU; Path=+10.4% → -18.5% | M Now=Now +1.1%, L -4.9%, H +12.1%, UD; Path=+3.9% → -4.8% | S Now=NA; Path=NA | WMA200=-9.9%, UP</t>
+          <t>NÖTR: Action=LATE | Trade_Action=LATE | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -16.5%, L -21.5%, H +0.0%, DU; Path=+10.4% → -18.5% | M Now=Now +1.2%, L -4.9%, H +12.1%, UD; Path=+3.9% → -4.8% | S Now=NA; Path=NA | WMA200=-9.9%, UP</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%16,6 / XU030 -%8,8 / Fark -%7,8 puan | M: Hisse +%1,1 / XU030 -%4,7 / Fark +%5,8 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%16,5 / XU030 -%8,7 / Fark -%7,8 puan | M: Hisse +%1,2 / XU030 -%4,6 / Fark +%5,8 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="I62" s="3" t="inlineStr">
@@ -5427,7 +5427,7 @@
       </c>
       <c r="J62" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=AL_ADAYI | AL basari=57.14285714285715 n=21 | SAT basari=50 n=34</t>
+          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=AL_ADAYI | AL basari=57.89473684210526 n=19 | SAT basari=48.57142857142857 n=35</t>
         </is>
       </c>
       <c r="K62" s="3" t="inlineStr">
@@ -5459,7 +5459,7 @@
         <is>
           <t>LONG - 7 - 7/3
 LONG - 7 - 8/4
-SHORT - 13 - 10/7</t>
+SHORT - 13 - 9/7</t>
         </is>
       </c>
     </row>
@@ -5492,12 +5492,12 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: Action=LATE | Trade_Action=LATE | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now +5.8%, L -6.0%, H +11.0%, DU; Path=+15.1% → -13.6% | M Now=Now -0.6%, L -4.6%, H +4.3%, UD; Path=-5.6% → +8.6% | S Now=NA; Path=NA | WMA200=+1.5%, DOWN</t>
+          <t>NÖTR: Action=LATE | Trade_Action=LATE | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now +5.9%, L -6.0%, H +11.0%, DU; Path=+15.1% → -13.6% | M Now=Now -0.5%, L -4.6%, H +4.3%, UD; Path=-5.6% → +8.6% | S Now=NA; Path=NA | WMA200=+1.6%, DOWN</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse +%5,8 / XU030 -%8,8 / Fark +%14,6 puan | M: Hisse -%0,6 / XU030 -%4,7 / Fark +%4,1 puan | S: VERİ YOK</t>
+          <t>Q: Hisse +%5,9 / XU030 -%8,7 / Fark +%14,6 puan | M: Hisse -%0,5 / XU030 -%4,6 / Fark +%4,1 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="I63" s="5" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="J63" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=AL_BEKLE_EŞİK | AL basari=55.17241379310344 n=29 | SAT basari=38.23529411764706 n=34</t>
+          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=AL_BEKLE_EŞİK | AL basari=53.57142857142857 n=28 | SAT basari=35.13513513513514 n=37</t>
         </is>
       </c>
       <c r="K63" s="3" t="inlineStr">
@@ -5572,12 +5572,12 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: Action=LATE | Trade_Action=LATE | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now +13.1%, L -8.7%, H +15.8%, DU; Path=+15.3% → -20.4% | M Now=Now +4.3%, L -7.1%, H +6.5%, DU; Path=-5.2% → +7.9% | S Now=NA; Path=NA | WMA200=+12.3%, DOWN</t>
+          <t>NÖTR: Action=LATE | Trade_Action=LATE | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now +13.2%, L -8.7%, H +15.8%, DU; Path=+15.3% → -20.4% | M Now=Now +4.4%, L -7.1%, H +6.5%, DU; Path=-5.2% → +7.9% | S Now=NA; Path=NA | WMA200=+12.4%, DOWN</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse +%13,1 / XU030 -%8,8 / Fark +%21,9 puan | M: Hisse +%4,3 / XU030 -%4,7 / Fark +%9,0 puan | S: VERİ YOK</t>
+          <t>Q: Hisse +%13,2 / XU030 -%8,7 / Fark +%21,9 puan | M: Hisse +%4,4 / XU030 -%4,6 / Fark +%9,0 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="I64" s="3" t="inlineStr">
@@ -5587,7 +5587,7 @@
       </c>
       <c r="J64" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=AL_ADAYI | AL basari=nan n=2 | SAT basari=48.93617021276596 n=47</t>
+          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=AL_ADAYI | AL basari=nan n=2 | SAT basari=48.97959183673469 n=49</t>
         </is>
       </c>
       <c r="K64" s="3" t="inlineStr">
@@ -5652,12 +5652,12 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: Action=LATE | Trade_Action=LATE | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now +5.6%, L -4.9%, H +31.2%, UD; Path=-6.9% → +21.1% | M Now=Now +1.7%, L -2.3%, H +26.3%, DU; Path=-4.8% → +7.5% | S Now=NA; Path=NA | WMA200=-3.8%, DOWN</t>
+          <t>NÖTR: Action=LATE | Trade_Action=LATE | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now +5.7%, L -4.9%, H +31.2%, UD; Path=-6.9% → +21.1% | M Now=Now +1.8%, L -2.3%, H +26.3%, DU; Path=-4.8% → +7.5% | S Now=NA; Path=NA | WMA200=-3.7%, DOWN</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse +%5,6 / XU030 -%8,8 / Fark +%14,4 puan | M: Hisse +%1,7 / XU030 -%4,7 / Fark +%6,4 puan | S: VERİ YOK</t>
+          <t>Q: Hisse +%5,7 / XU030 -%8,7 / Fark +%14,4 puan | M: Hisse +%1,8 / XU030 -%4,6 / Fark +%6,4 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="I65" s="5" t="inlineStr">
@@ -5667,7 +5667,7 @@
       </c>
       <c r="J65" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=SAT_ADAYI | AL basari=66.66666666666667 n=21 | SAT basari=nan n=0</t>
+          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=SAT_ADAYI | AL basari=66.66666666666667 n=21 | SAT basari=nan n=1</t>
         </is>
       </c>
       <c r="K65" s="3" t="inlineStr">
@@ -5732,12 +5732,12 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: Action=LATE | Trade_Action=LATE | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -45.2%, L -45.2%, H +31.7%, UD; Path=+27.2% → -19.3% | M Now=Now -55.4%, L -55.4%, H +7.2%, UD; Path=-7.9% → +4.5% | S Now=NA; Path=NA | WMA200=-52.5%, UP</t>
+          <t>NÖTR: Action=LATE | Trade_Action=LATE | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -45.1%, L -45.1%, H +31.7%, UD; Path=+27.2% → -19.3% | M Now=Now -55.3%, L -55.3%, H +7.2%, UD; Path=-7.9% → +4.5% | S Now=NA; Path=NA | WMA200=-52.4%, UP</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%45,2 / XU030 -%8,8 / Fark -%36,4 puan | M: Hisse -%55,4 / XU030 -%4,7 / Fark -%50,7 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%45,1 / XU030 -%8,7 / Fark -%36,4 puan | M: Hisse -%55,3 / XU030 -%4,6 / Fark -%50,7 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="I66" s="5" t="inlineStr">
@@ -5777,8 +5777,8 @@
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>ALT -  - 115/59
-ALT -  - 115/59
+          <t>ALT -  - 114/58
+ALT -  - 114/58
 ALT -  - 104/67</t>
         </is>
       </c>
@@ -5812,12 +5812,12 @@
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: Action=RISK | Trade_Action=RISK | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -18.4%, L -18.4%, H +16.1%, DU; Path=+13.7% → -18.8% | M Now=Now -13.1%, L -13.1%, H +23.7%, DU; Path=-4.4% → +10.2% | S Now=NA; Path=NA | WMA200=-22.7%, UP</t>
+          <t>OLUMSUZ / RİSK: Action=RISK | Trade_Action=RISK | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -18.4%, L -18.4%, H +16.1%, DU; Path=+13.7% → -18.8% | M Now=Now -13.0%, L -13.0%, H +23.7%, DU; Path=-4.4% → +10.2% | S Now=NA; Path=NA | WMA200=-22.6%, UP</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%18,4 / XU030 -%8,8 / Fark -%9,6 puan | M: Hisse -%13,1 / XU030 -%4,7 / Fark -%8,4 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%18,4 / XU030 -%8,7 / Fark -%9,7 puan | M: Hisse -%13,0 / XU030 -%4,6 / Fark -%8,4 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="I67" s="5" t="inlineStr">
@@ -5892,12 +5892,12 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: Action=LATE | Trade_Action=LATE | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -16.6%, L -18.3%, H +0.0%, DU; Path=+15.6% → -15.0% | M Now=Now -2.2%, L -4.2%, H +15.4%, DU; Path=+5.2% → -9.7% | S Now=NA; Path=NA | WMA200=-14.5%, UP</t>
+          <t>NÖTR: Action=LATE | Trade_Action=LATE | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -16.6%, L -18.3%, H +0.0%, DU; Path=+15.6% → -15.0% | M Now=Now -2.1%, L -4.2%, H +15.4%, DU; Path=+5.2% → -9.7% | S Now=NA; Path=NA | WMA200=-14.4%, UP</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%16,6 / XU030 -%8,8 / Fark -%7,8 puan | M: Hisse -%2,2 / XU030 -%4,7 / Fark +%2,5 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%16,6 / XU030 -%8,7 / Fark -%7,9 puan | M: Hisse -%2,1 / XU030 -%4,6 / Fark +%2,5 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="I68" s="3" t="inlineStr">
@@ -5972,12 +5972,12 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: Action=LATE | Trade_Action=LATE | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -14.1%, L -21.2%, H +0.8%, DU; Path=-8.7% → +16.0% | M Now=Now +4.5%, L -4.1%, H +17.3%, UD; Path=+2.5% → -8.8% | S Now=NA; Path=NA | WMA200=-11.6%, UP</t>
+          <t>NÖTR: Action=LATE | Trade_Action=LATE | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -14.1%, L -21.2%, H +0.8%, DU; Path=-8.7% → +16.0% | M Now=Now +4.6%, L -4.1%, H +17.3%, UD; Path=+2.5% → -8.8% | S Now=NA; Path=NA | WMA200=-11.5%, UP</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%14,1 / XU030 -%8,8 / Fark -%5,3 puan | M: Hisse +%4,5 / XU030 -%4,7 / Fark +%9,2 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%14,1 / XU030 -%8,7 / Fark -%5,4 puan | M: Hisse +%4,6 / XU030 -%4,6 / Fark +%9,2 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="I69" s="3" t="inlineStr">
@@ -5987,7 +5987,7 @@
       </c>
       <c r="J69" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=AL_ADAYI | AL basari=76.92307692307692 n=13 | SAT basari=42.1875 n=64</t>
+          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=AL_ADAYI | AL basari=69.23076923076923 n=13 | SAT basari=42.1875 n=64</t>
         </is>
       </c>
       <c r="K69" s="3" t="inlineStr">
@@ -6019,7 +6019,7 @@
         <is>
           <t>LONG - 7 - 7/9
 LONG - 7 - 9/7
-LONG - 7 - 5/5</t>
+LONG - 7 - 4/5</t>
         </is>
       </c>
     </row>
@@ -6052,12 +6052,12 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: Action=LATE | Trade_Action=LATE | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now +63.7%, L +0.0%, H +69.7%, UD; Path=+15.9% → -15.7% | M Now=Now -0.6%, L -3.9%, H +3.0%, DU; Path=-3.4% → +8.0% | S Now=NA; Path=NA | WMA200=+30.0%, DOWN</t>
+          <t>NÖTR: Action=LATE | Trade_Action=LATE | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now +63.9%, L +0.0%, H +69.7%, UD; Path=+15.9% → -15.7% | M Now=Now -0.5%, L -3.9%, H +3.0%, DU; Path=-3.4% → +8.0% | S Now=NA; Path=NA | WMA200=+30.1%, DOWN</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse +%63,7 / XU030 -%8,8 / Fark +%72,5 puan | M: Hisse -%0,6 / XU030 -%4,7 / Fark +%4,1 puan | S: VERİ YOK</t>
+          <t>Q: Hisse +%63,9 / XU030 -%8,7 / Fark +%72,6 puan | M: Hisse -%0,5 / XU030 -%4,6 / Fark +%4,1 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="I70" s="3" t="inlineStr">
@@ -6132,12 +6132,12 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: Action=LATE | Trade_Action=LATE | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -3.2%, L -14.5%, H +9.9%, DU; Path=+13.5% → -16.8% | M Now=Now +2.3%, L -6.0%, H +16.2%, UD; Path=+8.9% → -9.1% | S Now=NA; Path=NA | WMA200=-1.9%, UP</t>
+          <t>NÖTR: Action=LATE | Trade_Action=LATE | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -3.1%, L -14.5%, H +9.9%, DU; Path=+13.5% → -16.8% | M Now=Now +2.4%, L -6.0%, H +16.2%, UD; Path=+8.9% → -9.1% | S Now=NA; Path=NA | WMA200=-1.8%, UP</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%3,2 / XU030 -%8,8 / Fark +%5,6 puan | M: Hisse +%2,3 / XU030 -%4,7 / Fark +%7,0 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%3,1 / XU030 -%8,7 / Fark +%5,6 puan | M: Hisse +%2,4 / XU030 -%4,6 / Fark +%7,0 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="I71" s="5" t="inlineStr">
@@ -6210,12 +6210,12 @@
       </c>
       <c r="G72" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: Action=LONG_WATCH | Trade_Action=LONG_WATCH | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -8.8%, L -11.1%, H +1.0%, DU; Path=+11.3% → -11.7% | M Now=Now -4.7%, L -5.4%, H +4.1%, UD; Path=+3.8% → -4.5% | S Now=NA; Path=NA | WMA200=-5.4%, DOWN</t>
+          <t>OLUMLU: Action=LONG_WATCH | Trade_Action=LONG_WATCH | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -8.7%, L -11.1%, H +1.0%, DU; Path=+11.3% → -11.7% | M Now=Now -4.6%, L -5.4%, H +4.1%, UD; Path=+3.8% → -4.5% | S Now=NA; Path=NA | WMA200=-5.3%, DOWN</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%8,8 / XU030 -%8,8 / Fark %0,0 puan | M: Hisse -%4,7 / XU030 -%4,7 / Fark %0,0 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%8,7 / XU030 -%8,7 / Fark %0,0 puan | M: Hisse -%4,6 / XU030 -%4,6 / Fark %0,0 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="I72" s="3" t="inlineStr">
@@ -6255,7 +6255,7 @@
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>ALT -  - 11/0
+          <t>LONG - 7 - 10/0
 LONG - 7 - 9/1
 LONG - 7 - 9/1</t>
         </is>
@@ -6405,12 +6405,12 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: Action=LOW_DATA | Trade_Action=LOW_DATA | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -10.1%, L -15.0%, H +22.6%, UD; Path=+24.2% → -19.6% | M Now=Now -18.7%, L -23.1%, H +0.0%, DU; Path=+2.6% → -11.0% | S Now=NA; Path=NA | WMA200=-10.5%, UP</t>
+          <t>NÖTR: Action=LOW_DATA | Trade_Action=LOW_DATA | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -10.0%, L -15.0%, H +22.6%, UD; Path=+24.2% → -19.6% | M Now=Now -18.6%, L -23.1%, H +0.0%, DU; Path=+2.6% → -11.0% | S Now=NA; Path=NA | WMA200=-10.4%, UP</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%10,1 / XU030 -%8,8 / Fark -%1,3 puan | M: Hisse -%18,7 / XU030 -%4,7 / Fark -%14,0 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%10,0 / XU030 -%8,7 / Fark -%1,3 puan | M: Hisse -%18,6 / XU030 -%4,6 / Fark -%14,0 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="I2" s="4" t="inlineStr">
@@ -6420,7 +6420,7 @@
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: Endeks=XU030 | Karar=AL_ADAYI | AL basari=66.66666666666667 n=3 | SAT basari=40 n=20</t>
+          <t>NÖTR: Endeks=XU030 | Karar=AL_ADAYI | AL basari=66.66666666666667 n=3 | SAT basari=42.85714285714285 n=21</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
@@ -6485,12 +6485,12 @@
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: Action=LONG_WATCH | Trade_Action=LONG_WATCH | Önerilen=EVET | Öneren sistem=3 | Q Now=Now -0.8%, L -9.5%, H +14.3%, UD; Path=+13.0% → -20.0% | M Now=Now -0.5%, L -4.9%, H +8.8%, UD; Path=+7.7% → -9.1% | S Now=NA; Path=NA | WMA200=-2.9%, DOWN</t>
+          <t>OLUMLU: Action=LONG_WATCH | Trade_Action=LONG_WATCH | Önerilen=EVET | Öneren sistem=3 | Q Now=Now -0.8%, L -9.5%, H +14.3%, UD; Path=+13.0% → -20.0% | M Now=Now -0.4%, L -4.9%, H +8.8%, UD; Path=+7.7% → -9.1% | S Now=NA; Path=NA | WMA200=-2.9%, DOWN</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%0,8 / XU030 -%8,8 / Fark +%8,0 puan | M: Hisse -%0,5 / XU030 -%4,7 / Fark +%4,2 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%0,8 / XU030 -%8,7 / Fark +%7,9 puan | M: Hisse -%0,4 / XU030 -%4,6 / Fark +%4,2 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="I3" s="5" t="inlineStr">
@@ -6500,7 +6500,7 @@
       </c>
       <c r="J3" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=AL_ADAYI | AL basari=65.38461538461539 n=26 | SAT basari=37.5 n=48</t>
+          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=AL_ADAYI | AL basari=66.66666666666667 n=27 | SAT basari=41.66666666666666 n=48</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
@@ -6532,7 +6532,7 @@
         <is>
           <t>LONG - 1 - 8/2
 LONG - 7 - 5/5
-LONG - 1 - 9/2</t>
+LONG - 1 - 8/2</t>
         </is>
       </c>
     </row>
@@ -6565,12 +6565,12 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: Action=LATE | Trade_Action=LATE | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -14.0%, L -17.3%, H +5.4%, DU; Path=+13.8% → -19.2% | M Now=Now +2.7%, L -0.5%, H +8.5%, UD; Path=+4.4% → -8.5% | S Now=NA; Path=NA | WMA200=-8.7%, UP</t>
+          <t>NÖTR: Action=LATE | Trade_Action=LATE | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -13.9%, L -17.3%, H +5.4%, DU; Path=+13.8% → -19.2% | M Now=Now +2.8%, L -0.5%, H +8.5%, UD; Path=+4.4% → -8.5% | S Now=NA; Path=NA | WMA200=-8.7%, UP</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%14,0 / XU030 -%8,8 / Fark -%5,2 puan | M: Hisse +%2,7 / XU030 -%4,7 / Fark +%7,4 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%13,9 / XU030 -%8,7 / Fark -%5,2 puan | M: Hisse +%2,8 / XU030 -%4,6 / Fark +%7,4 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
@@ -6645,12 +6645,12 @@
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: Action=LONG_WATCH | Trade_Action=LONG_WATCH | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -15.8%, L -23.0%, H +40.7%, UD; Path=-16.0% → +18.8% | M Now=Now -9.6%, L -17.3%, H +3.7%, UD; Path=+5.8% → -6.9% | S Now=NA; Path=NA | WMA200=-16.6%, UP</t>
+          <t>OLUMLU: Action=LONG_WATCH | Trade_Action=LONG_WATCH | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -15.7%, L -23.0%, H +40.7%, UD; Path=-16.0% → +18.8% | M Now=Now -9.5%, L -17.3%, H +3.7%, UD; Path=+5.8% → -6.9% | S Now=NA; Path=NA | WMA200=-16.6%, UP</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%15,8 / XU030 -%8,8 / Fark -%7,0 puan | M: Hisse -%9,6 / XU030 -%4,7 / Fark -%4,9 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%15,7 / XU030 -%8,7 / Fark -%7,0 puan | M: Hisse -%9,5 / XU030 -%4,6 / Fark -%4,9 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -6725,12 +6725,12 @@
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: Action=LONG_WATCH | Trade_Action=LONG_WATCH | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -12.7%, L -12.7%, H +6.2%, UD; Path=+8.2% → -13.3% | M Now=Now -8.8%, L -8.8%, H +0.0%, DU; Path=-3.3% → +10.4% | S Now=NA; Path=NA | WMA200=-14.4%, UP</t>
+          <t>OLUMLU: Action=LONG_WATCH | Trade_Action=LONG_WATCH | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -12.6%, L -12.6%, H +6.2%, UD; Path=+8.2% → -13.3% | M Now=Now -8.7%, L -8.7%, H +0.0%, DU; Path=-3.3% → +10.4% | S Now=NA; Path=NA | WMA200=-14.3%, UP</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%12,7 / XU030 -%8,8 / Fark -%3,9 puan | M: Hisse -%8,8 / XU030 -%4,7 / Fark -%4,1 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%12,6 / XU030 -%8,7 / Fark -%3,9 puan | M: Hisse -%8,7 / XU030 -%4,6 / Fark -%4,1 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
@@ -6740,7 +6740,7 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: Endeks=XU030 | Karar=AL_BEKLE_EŞİK | AL basari=63.88888888888889 n=36 | SAT basari=nan n=0</t>
+          <t>NÖTR: Endeks=XU030 | Karar=AL_BEKLE_EŞİK | AL basari=62.16216216216216 n=37 | SAT basari=nan n=0</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
@@ -6805,12 +6805,12 @@
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: Action=LONG_WATCH | Trade_Action=LONG_WATCH | Önerilen=EVET | Öneren sistem=7 | Q Now=Now +11.0%, L -2.2%, H +14.5%, DU; Path=+17.9% → -12.9% | M Now=Now +2.6%, L -1.5%, H +5.8%, UD; Path=+6.0% → -6.5% | S Now=NA; Path=NA | WMA200=+5.4%, DOWN</t>
+          <t>OLUMLU: Action=LONG_WATCH | Trade_Action=LONG_WATCH | Önerilen=EVET | Öneren sistem=7 | Q Now=Now +11.1%, L -2.2%, H +14.5%, DU; Path=+17.9% → -12.9% | M Now=Now +2.7%, L -1.5%, H +5.8%, UD; Path=+6.0% → -6.5% | S Now=NA; Path=NA | WMA200=+5.5%, DOWN</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse +%11,0 / XU030 -%8,8 / Fark +%19,8 puan | M: Hisse +%2,6 / XU030 -%4,7 / Fark +%7,3 puan | S: VERİ YOK</t>
+          <t>Q: Hisse +%11,1 / XU030 -%8,7 / Fark +%19,8 puan | M: Hisse +%2,7 / XU030 -%4,6 / Fark +%7,3 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
@@ -6820,7 +6820,7 @@
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=SAT_ADAYI | AL basari=nan n=0 | SAT basari=44.44444444444444 n=27</t>
+          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=SAT_ADAYI | AL basari=nan n=0 | SAT basari=40.74074074074074 n=27</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
@@ -6852,7 +6852,7 @@
         <is>
           <t>SHORT - 2 - 2/9
 SHORT - 10 - 4/8
-SHORT - 2 - 2/7</t>
+SHORT - 2 - 2/8</t>
         </is>
       </c>
     </row>
@@ -6885,12 +6885,12 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: Action=LONG_WATCH | Trade_Action=LONG_WATCH | Önerilen=EVET | Öneren sistem=5 | Q Now=Now -23.2%, L -24.0%, H +1.2%, DU; Path=+13.9% → -20.1% | M Now=Now -9.9%, L -10.9%, H +3.2%, DU; Path=+6.0% → -9.1% | S Now=NA; Path=NA | WMA200=-24.6%, UP</t>
+          <t>OLUMLU: Action=LONG_WATCH | Trade_Action=LONG_WATCH | Önerilen=EVET | Öneren sistem=5 | Q Now=Now -23.1%, L -24.0%, H +1.2%, DU; Path=+13.9% → -20.1% | M Now=Now -9.9%, L -10.9%, H +3.2%, DU; Path=+6.0% → -9.1% | S Now=NA; Path=NA | WMA200=-24.5%, UP</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%23,2 / XU030 -%8,8 / Fark -%14,4 puan | M: Hisse -%9,9 / XU030 -%4,7 / Fark -%5,2 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%23,1 / XU030 -%8,7 / Fark -%14,4 puan | M: Hisse -%9,9 / XU030 -%4,6 / Fark -%5,3 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
@@ -6931,7 +6931,7 @@
       <c r="P8" s="2" t="inlineStr">
         <is>
           <t>ALT -  - 14/3
-ALT -  - 38/18
+ALT -  - 38/17
 LONG - 1 - 27/0</t>
         </is>
       </c>
@@ -6965,12 +6965,12 @@
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: Action=LONG_READY | Trade_Action=LONG_READY | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -18.3%, L -20.2%, H +0.3%, DU; Path=-3.6% → +58.5% | M Now=Now -13.5%, L -15.5%, H +3.4%, UD; Path=-6.5% → +7.6% | S Now=NA; Path=NA | WMA200=-24.8%, UP</t>
+          <t>OLUMLU: Action=LONG_READY | Trade_Action=LONG_READY | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -18.2%, L -20.2%, H +0.3%, DU; Path=-3.6% → +58.5% | M Now=Now -13.5%, L -15.5%, H +3.4%, UD; Path=-6.5% → +7.6% | S Now=NA; Path=NA | WMA200=-24.8%, UP</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%18,3 / XU030 -%8,8 / Fark -%9,5 puan | M: Hisse -%13,5 / XU030 -%4,7 / Fark -%8,8 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%18,2 / XU030 -%8,7 / Fark -%9,5 puan | M: Hisse -%13,5 / XU030 -%4,6 / Fark -%8,9 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
@@ -6980,7 +6980,7 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: Endeks=XU030 | Karar=AL_BEKLE_EŞİK | AL basari=68.18181818181819 n=22 | SAT basari=nan n=0</t>
+          <t>NÖTR: Endeks=XU030 | Karar=AL_BEKLE_EŞİK | AL basari=66.66666666666667 n=21 | SAT basari=nan n=0</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: Action=RISK | Trade_Action=RISK | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -9.4%, L -11.3%, H +11.4%, UD; Path=+16.1% → -17.8% | M Now=Now +0.1%, L -1.1%, H +6.1%, UD; Path=+4.8% → -9.8% | S Now=NA; Path=NA | WMA200=-7.3%, DOWN</t>
+          <t>OLUMSUZ / RİSK: Action=RISK | Trade_Action=RISK | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -9.3%, L -11.3%, H +11.4%, UD; Path=+16.1% → -17.8% | M Now=Now +0.2%, L -1.1%, H +6.1%, UD; Path=+4.8% → -9.8% | S Now=NA; Path=NA | WMA200=-7.2%, DOWN</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%9,4 / XU030 -%8,8 / Fark -%0,6 puan | M: Hisse +%0,1 / XU030 -%4,7 / Fark +%4,8 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%9,3 / XU030 -%8,7 / Fark -%0,6 puan | M: Hisse +%0,2 / XU030 -%4,6 / Fark +%4,8 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
@@ -7060,7 +7060,7 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: Endeks=XU030 | Karar=AL_BEKLE_EŞİK | AL basari=60.41666666666666 n=48 | SAT basari=nan n=0</t>
+          <t>NÖTR: Endeks=XU030 | Karar=AL_BEKLE_EŞİK | AL basari=61.22448979591837 n=49 | SAT basari=nan n=0</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr">
@@ -7125,12 +7125,12 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: Action=LOW_DATA | Trade_Action=LOW_DATA | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -65.4%, L -67.5%, H +3.7%, UD; Path=-7.3% → +40.3% | M Now=Now -13.2%, L -18.6%, H +0.3%, DU; Path=-11.6% → +14.1% | S Now=NA; Path=NA | WMA200=-55.7%, UP</t>
+          <t>NÖTR: Action=LOW_DATA | Trade_Action=LOW_DATA | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -65.4%, L -67.5%, H +3.7%, UD; Path=-7.3% → +40.3% | M Now=Now -13.2%, L -18.6%, H +0.3%, DU; Path=-11.6% → +14.1% | S Now=NA; Path=NA | WMA200=-55.6%, UP</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%65,4 / XU030 -%8,8 / Fark -%56,6 puan | M: Hisse -%13,2 / XU030 -%4,7 / Fark -%8,5 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%65,4 / XU030 -%8,7 / Fark -%56,7 puan | M: Hisse -%13,2 / XU030 -%4,6 / Fark -%8,6 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
@@ -7140,7 +7140,7 @@
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=SAT_BEKLE_EŞİK | AL basari=nan n=1 | SAT basari=42.85714285714285 n=28</t>
+          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=SAT_BEKLE_EŞİK | AL basari=nan n=1 | SAT basari=44.82758620689656 n=29</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
@@ -7205,12 +7205,12 @@
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: Action=NO_CLEAR_EDGE | Trade_Action=NO_CLEAR_EDGE | Önerilen=EVET | Öneren sistem=1 | Q Now=Now -20.2%, L -20.2%, H +3.0%, DU; Path=+19.8% → -15.3% | M Now=Now -7.2%, L -7.2%, H +1.1%, DU; Path=-6.5% → +8.6% | S Now=NA; Path=NA | WMA200=-20.4%, UP</t>
+          <t>OLUMLU: Action=NO_CLEAR_EDGE | Trade_Action=NO_CLEAR_EDGE | Önerilen=EVET | Öneren sistem=1 | Q Now=Now -20.1%, L -20.1%, H +3.0%, DU; Path=+19.8% → -15.3% | M Now=Now -7.1%, L -7.1%, H +1.1%, DU; Path=-6.5% → +8.6% | S Now=NA; Path=NA | WMA200=-20.4%, UP</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%20,2 / XU030 -%8,8 / Fark -%11,4 puan | M: Hisse -%7,2 / XU030 -%4,7 / Fark -%2,5 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%20,1 / XU030 -%8,7 / Fark -%11,4 puan | M: Hisse -%7,1 / XU030 -%4,6 / Fark -%2,5 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
@@ -7220,7 +7220,7 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: Endeks=XU030 | Karar=AL_BEKLE_EŞİK | AL basari=54.54545454545455 n=44 | SAT basari=nan n=0</t>
+          <t>NÖTR: Endeks=XU030 | Karar=AL_BEKLE_EŞİK | AL basari=50 n=42 | SAT basari=nan n=0</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
@@ -7250,8 +7250,8 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>LONG - 5 - 17/1
-LONG - 5 - 17/1
+          <t>LONG - 5 - 16/1
+LONG - 5 - 16/1
 ALT -  - 15/2</t>
         </is>
       </c>
@@ -7285,12 +7285,12 @@
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: Action=LONG_WATCH | Trade_Action=LONG_WATCH | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -12.8%, L -26.7%, H +2.9%, UD; Path=+17.0% → -14.4% | M Now=Now -10.0%, L -24.3%, H +0.0%, DU; Path=+9.0% → -5.1% | S Now=NA; Path=NA | WMA200=-22.0%, UP</t>
+          <t>OLUMLU: Action=LONG_WATCH | Trade_Action=LONG_WATCH | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -12.8%, L -26.7%, H +2.9%, UD; Path=+17.0% → -14.4% | M Now=Now -9.9%, L -24.3%, H +0.0%, DU; Path=+9.0% → -5.1% | S Now=NA; Path=NA | WMA200=-22.0%, UP</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%12,8 / XU030 -%8,8 / Fark -%4,0 puan | M: Hisse -%10,0 / XU030 -%4,7 / Fark -%5,3 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%12,8 / XU030 -%8,7 / Fark -%4,1 puan | M: Hisse -%9,9 / XU030 -%4,6 / Fark -%5,3 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
@@ -7300,7 +7300,7 @@
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=SAT_BEKLE_EŞİK | AL basari=nan n=0 | SAT basari=35.71428571428572 n=28</t>
+          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=SAT_BEKLE_EŞİK | AL basari=nan n=0 | SAT basari=33.33333333333334 n=27</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
@@ -7330,7 +7330,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>UST -  - 2/12
+          <t>UST -  - 3/12
 LONG - 1 - 19/3
 ALT -  - 20/2</t>
         </is>
@@ -7365,12 +7365,12 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: Action=LOW_DATA | Trade_Action=LOW_DATA | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now +13.9%, L -27.7%, H +13.9%, DU; Path=+70.0% → -20.5% | M Now=Now +31.0%, L +0.0%, H +31.0%, UD; Path=+11.3% → -20.5% | S Now=NA; Path=NA | WMA200=+32.9%, DOWN</t>
+          <t>NÖTR: Action=LOW_DATA | Trade_Action=LOW_DATA | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now +14.0%, L -27.7%, H +14.0%, DU; Path=+70.0% → -20.5% | M Now=Now +31.1%, L +0.0%, H +31.1%, UD; Path=+11.3% → -20.5% | S Now=NA; Path=NA | WMA200=+33.0%, DOWN</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse +%13,9 / XU030 -%8,8 / Fark +%22,7 puan | M: Hisse +%31,0 / XU030 -%4,7 / Fark +%35,7 puan | S: VERİ YOK</t>
+          <t>Q: Hisse +%14,0 / XU030 -%8,7 / Fark +%22,7 puan | M: Hisse +%31,1 / XU030 -%4,6 / Fark +%35,7 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
@@ -7395,7 +7395,7 @@
       </c>
       <c r="M14" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / GEÇ KALMA RİSKİ: Açık=EVET | Sayfa=USD | Güncel=%13,7 | Max_Aktif_Kar=%14,3 | Min=%0,0 | Grup/Etiket=USD/LAST_3_TOP3/T5_tek_sistem|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan|keltner_kirilim</t>
+          <t>OLUMSUZ / GEÇ KALMA RİSKİ: Açık=EVET | Sayfa=USD | Güncel=%13,8 | Max_Aktif_Kar=%14,4 | Min=%0,0 | Grup/Etiket=USD/LAST_3_TOP3/T5_tek_sistem|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan|keltner_kirilim</t>
         </is>
       </c>
       <c r="N14" s="4" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: Action=LATE | Trade_Action=LATE | Önerilen=EVET | Öneren sistem=2 | Q Now=Now -2.3%, L -12.4%, H +10.3%, UD; Path=-11.4% → +22.3% | M Now=Now -4.1%, L -12.6%, H +8.3%, UD; Path=-5.2% → +11.5% | S Now=NA; Path=NA | WMA200=-9.3%, UP</t>
+          <t>OLUMLU: Action=LATE | Trade_Action=LATE | Önerilen=EVET | Öneren sistem=2 | Q Now=Now -2.2%, L -12.4%, H +10.3%, UD; Path=-11.4% → +22.3% | M Now=Now -4.0%, L -12.6%, H +8.3%, UD; Path=-5.2% → +11.5% | S Now=NA; Path=NA | WMA200=-9.2%, UP</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%2,3 / XU030 -%8,8 / Fark +%6,5 puan | M: Hisse -%4,1 / XU030 -%4,7 / Fark +%0,6 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%2,2 / XU030 -%8,7 / Fark +%6,5 puan | M: Hisse -%4,0 / XU030 -%4,6 / Fark +%0,6 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
@@ -7460,7 +7460,7 @@
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=SAT_BEKLE_EŞİK | AL basari=nan n=0 | SAT basari=40 n=40</t>
+          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=SAT_BEKLE_EŞİK | AL basari=nan n=0 | SAT basari=38.46153846153846 n=39</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
@@ -7491,7 +7491,7 @@
       <c r="P15" s="2" t="inlineStr">
         <is>
           <t>LONG - 1 - 10/3
-LONG - 7 - 13/12
+LONG - 7 - 12/12
 LONG - 1 - 10/3</t>
         </is>
       </c>
@@ -7525,12 +7525,12 @@
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: Action=LONG_READY | Trade_Action=LONG_READY | Önerilen=EVET | Öneren sistem=2 | Q Now=Now -16.2%, L -16.2%, H +2.2%, DU; Path=-8.4% → +17.8% | M Now=Now -7.9%, L -7.9%, H +9.7%, UD; Path=-4.5% → +8.3% | S Now=NA; Path=NA | WMA200=-20.6%, UP</t>
+          <t>OLUMLU: Action=LONG_READY | Trade_Action=LONG_READY | Önerilen=EVET | Öneren sistem=2 | Q Now=Now -16.1%, L -16.1%, H +2.2%, DU; Path=-8.4% → +17.8% | M Now=Now -7.8%, L -7.8%, H +9.7%, UD; Path=-4.5% → +8.3% | S Now=NA; Path=NA | WMA200=-20.5%, UP</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%16,2 / XU030 -%8,8 / Fark -%7,4 puan | M: Hisse -%7,9 / XU030 -%4,7 / Fark -%3,2 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%16,1 / XU030 -%8,7 / Fark -%7,4 puan | M: Hisse -%7,8 / XU030 -%4,6 / Fark -%3,2 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=SAT_ADAYI | AL basari=56.81818181818182 n=44 | SAT basari=59.09090909090909 n=22</t>
+          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=SAT_ADAYI | AL basari=57.77777777777778 n=45 | SAT basari=56.52173913043478 n=23</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
@@ -7605,12 +7605,12 @@
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: Action=LONG_WATCH | Trade_Action=LONG_WATCH | Önerilen=EVET | Öneren sistem=3 | Q Now=Now -52.4%, L -56.6%, H +5.2%, UD; Path=-20.9% → +28.1% | M Now=Now -46.0%, L -50.8%, H +7.8%, UD; Path=+10.4% → -12.2% | S Now=NA; Path=NA | WMA200=-50.3%, UP</t>
+          <t>OLUMLU: Action=LONG_WATCH | Trade_Action=LONG_WATCH | Önerilen=EVET | Öneren sistem=3 | Q Now=Now -52.3%, L -56.6%, H +5.2%, UD; Path=-20.9% → +28.1% | M Now=Now -45.9%, L -50.8%, H +7.8%, UD; Path=+10.4% → -12.2% | S Now=NA; Path=NA | WMA200=-50.3%, UP</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%52,4 / XU030 -%8,8 / Fark -%43,6 puan | M: Hisse -%46,0 / XU030 -%4,7 / Fark -%41,3 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%52,3 / XU030 -%8,7 / Fark -%43,6 puan | M: Hisse -%45,9 / XU030 -%4,6 / Fark -%41,3 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
@@ -7650,8 +7650,8 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>ALT -  - 79/58
-ALT -  - 160/92
+          <t>ALT -  - 78/58
+ALT -  - 159/92
 ALT -  - 56/41</t>
         </is>
       </c>
@@ -7685,12 +7685,12 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: Action=NO_CLEAR_EDGE | Trade_Action=NO_CLEAR_EDGE | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -21.1%, L -25.8%, H +6.0%, DU; Path=-14.1% → +20.9% | M Now=Now -7.0%, L -12.4%, H +2.3%, DU; Path=-5.4% → +11.2% | S Now=NA; Path=NA | WMA200=-8.5%, UP</t>
+          <t>NÖTR: Action=NO_CLEAR_EDGE | Trade_Action=NO_CLEAR_EDGE | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -21.1%, L -25.8%, H +6.0%, DU; Path=-14.1% → +20.9% | M Now=Now -6.9%, L -12.4%, H +2.3%, DU; Path=-5.4% → +11.2% | S Now=NA; Path=NA | WMA200=-8.4%, UP</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%21,1 / XU030 -%8,8 / Fark -%12,3 puan | M: Hisse -%7,0 / XU030 -%4,7 / Fark -%2,3 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%21,1 / XU030 -%8,7 / Fark -%12,4 puan | M: Hisse -%6,9 / XU030 -%4,6 / Fark -%2,3 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
@@ -7700,7 +7700,7 @@
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=SAT_BEKLE_EŞİK | AL basari=72.72727272727273 n=11 | SAT basari=44.73684210526316 n=76</t>
+          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=SAT_BEKLE_EŞİK | AL basari=70 n=10 | SAT basari=45.33333333333334 n=75</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
@@ -7732,7 +7732,7 @@
         <is>
           <t>LONG - 3 - 4/6
 SHORT - 68 - 7/12
-LONG - 1 - 8/2</t>
+LONG - 1 - 8/3</t>
         </is>
       </c>
     </row>
@@ -7765,12 +7765,12 @@
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: Action=NO_CLEAR_EDGE | Trade_Action=NO_CLEAR_EDGE | Önerilen=EVET | Öneren sistem=7 | Q Now=Now -20.4%, L -26.4%, H +6.8%, UD; Path=+12.0% → -16.3% | M Now=Now -6.9%, L -7.1%, H +2.4%, DU; Path=-6.9% → +6.6% | S Now=NA; Path=NA | WMA200=-17.9%, UP</t>
+          <t>OLUMLU: Action=NO_CLEAR_EDGE | Trade_Action=NO_CLEAR_EDGE | Önerilen=EVET | Öneren sistem=7 | Q Now=Now -20.3%, L -26.4%, H +6.8%, UD; Path=+12.0% → -16.3% | M Now=Now -6.8%, L -7.1%, H +2.4%, DU; Path=-6.9% → +6.6% | S Now=NA; Path=NA | WMA200=-17.9%, UP</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%20,4 / XU030 -%8,8 / Fark -%11,6 puan | M: Hisse -%6,9 / XU030 -%4,7 / Fark -%2,2 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%20,3 / XU030 -%8,7 / Fark -%11,6 puan | M: Hisse -%6,8 / XU030 -%4,6 / Fark -%2,2 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: Action=LONG_WATCH | Trade_Action=LONG_WATCH | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -14.3%, L -17.6%, H +0.0%, DU; Path=+12.6% → -15.1% | M Now=Now -6.6%, L -10.3%, H +3.2%, UD; Path=+6.2% → -7.8% | S Now=NA; Path=NA | WMA200=-10.3%, UP</t>
+          <t>OLUMLU: Action=LONG_WATCH | Trade_Action=LONG_WATCH | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -14.2%, L -17.6%, H +0.0%, DU; Path=+12.6% → -15.1% | M Now=Now -6.6%, L -10.3%, H +3.2%, UD; Path=+6.2% → -7.8% | S Now=NA; Path=NA | WMA200=-10.2%, UP</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%14,3 / XU030 -%8,8 / Fark -%5,5 puan | M: Hisse -%6,6 / XU030 -%4,7 / Fark -%1,9 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%14,2 / XU030 -%8,7 / Fark -%5,5 puan | M: Hisse -%6,6 / XU030 -%4,6 / Fark -%2,0 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
@@ -7860,7 +7860,7 @@
       </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=SAT_ADAYI | AL basari=52 n=25 | SAT basari=42.85714285714285 n=35</t>
+          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=SAT_ADAYI | AL basari=50 n=24 | SAT basari=42.85714285714285 n=35</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
@@ -7925,12 +7925,12 @@
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: Action=LONG_WATCH | Trade_Action=LONG_WATCH | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -12.4%, L -15.5%, H +2.4%, DU; Path=-11.7% → +19.3% | M Now=Now +2.1%, L -1.6%, H +6.7%, UD; Path=+6.3% → -7.2% | S Now=NA; Path=NA | WMA200=-11.4%, UP</t>
+          <t>OLUMLU: Action=LONG_WATCH | Trade_Action=LONG_WATCH | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -12.3%, L -15.5%, H +2.4%, DU; Path=-11.7% → +19.3% | M Now=Now +2.2%, L -1.6%, H +6.7%, UD; Path=+6.3% → -7.2% | S Now=NA; Path=NA | WMA200=-11.3%, UP</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%12,4 / XU030 -%8,8 / Fark -%3,6 puan | M: Hisse +%2,1 / XU030 -%4,7 / Fark +%6,8 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%12,3 / XU030 -%8,7 / Fark -%3,6 puan | M: Hisse +%2,2 / XU030 -%4,6 / Fark +%6,8 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
@@ -7940,7 +7940,7 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: Endeks=XU030 | Karar=ÇELİŞKİLİ_BEKLE | AL basari=54.05405405405406 n=37 | SAT basari=33.9622641509434 n=53</t>
+          <t>NÖTR: Endeks=XU030 | Karar=ÇELİŞKİLİ_BEKLE | AL basari=56.75675675675676 n=37 | SAT basari=33.33333333333334 n=54</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
@@ -7971,7 +7971,7 @@
       <c r="P21" s="2" t="inlineStr">
         <is>
           <t>LONG - 19 - 6/6
-LONG - 7 - 7/3
+LONG - 7 - 7/4
 LONG - 5 - 8/2</t>
         </is>
       </c>
@@ -8005,12 +8005,12 @@
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: Action=RISK | Trade_Action=RISK | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now +86.4%, L -8.8%, H +86.4%, DU; Path=+7.8% → -18.1% | M Now=Now +27.7%, L -3.7%, H +27.7%, DU; Path=-6.6% → +8.5% | S Now=NA; Path=NA | WMA200=+66.6%, DOWN</t>
+          <t>OLUMSUZ / RİSK: Action=RISK | Trade_Action=RISK | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now +86.5%, L -8.8%, H +86.5%, DU; Path=+7.8% → -18.1% | M Now=Now +27.8%, L -3.7%, H +27.8%, DU; Path=-6.6% → +8.5% | S Now=NA; Path=NA | WMA200=+66.7%, DOWN</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse +%86,4 / XU030 -%8,8 / Fark +%95,2 puan | M: Hisse +%27,7 / XU030 -%4,7 / Fark +%32,4 puan | S: VERİ YOK</t>
+          <t>Q: Hisse +%86,5 / XU030 -%8,7 / Fark +%95,2 puan | M: Hisse +%27,8 / XU030 -%4,6 / Fark +%32,4 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr">
@@ -8035,7 +8035,7 @@
       </c>
       <c r="M22" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / GEÇ KALMA RİSKİ: Açık=EVET | Sayfa=USD | Güncel=%45,6 | Max_Aktif_Kar=%48,4 | Min=%-0,6 | Grup/Etiket=USD/LAST_3_TOP3/T5_tek_sistem|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan|keltner_kirilim</t>
+          <t>OLUMSUZ / GEÇ KALMA RİSKİ: Açık=EVET | Sayfa=USD | Güncel=%45,8 | Max_Aktif_Kar=%48,4 | Min=%-0,6 | Grup/Etiket=USD/LAST_3_TOP3/T5_tek_sistem|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan|keltner_kirilim</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
@@ -8085,12 +8085,12 @@
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: Action=LATE | Trade_Action=LATE | Önerilen=EVET | Öneren sistem=1 | Q Now=Now +17.6%, L +0.0%, H +25.4%, UD; Path=-16.4% → +27.7% | M Now=Now +2.8%, L -7.9%, H +5.0%, UD; Path=-5.5% → +13.6% | S Now=NA; Path=NA | WMA200=+3.7%, DOWN</t>
+          <t>OLUMLU: Action=LATE | Trade_Action=LATE | Önerilen=EVET | Öneren sistem=1 | Q Now=Now +17.7%, L +0.0%, H +25.4%, UD; Path=-16.4% → +27.7% | M Now=Now +2.9%, L -7.9%, H +5.0%, UD; Path=-5.5% → +13.6% | S Now=NA; Path=NA | WMA200=+3.8%, DOWN</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse +%17,6 / XU030 -%8,8 / Fark +%26,4 puan | M: Hisse +%2,8 / XU030 -%4,7 / Fark +%7,5 puan | S: VERİ YOK</t>
+          <t>Q: Hisse +%17,7 / XU030 -%8,7 / Fark +%26,4 puan | M: Hisse +%2,9 / XU030 -%4,6 / Fark +%7,5 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
@@ -8100,7 +8100,7 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: Endeks=XU030 | Karar=ÇELİŞKİLİ_BEKLE | AL basari=66.66666666666667 n=9 | SAT basari=36.8421052631579 n=57</t>
+          <t>NÖTR: Endeks=XU030 | Karar=ÇELİŞKİLİ_BEKLE | AL basari=66.66666666666667 n=9 | SAT basari=36.20689655172414 n=58</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
@@ -8165,12 +8165,12 @@
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: Action=LONG_READY | Trade_Action=LONG_READY | Önerilen=EVET | Öneren sistem=13 | Q Now=Now -18.2%, L -18.2%, H +0.1%, DU; Path=+16.5% → -15.5% | M Now=Now -7.2%, L -7.2%, H +5.3%, UD; Path=-5.4% → +10.4% | S Now=NA; Path=NA | WMA200=-15.7%, UP</t>
+          <t>OLUMLU: Action=LONG_READY | Trade_Action=LONG_READY | Önerilen=EVET | Öneren sistem=13 | Q Now=Now -18.1%, L -18.1%, H +0.1%, DU; Path=+16.5% → -15.5% | M Now=Now -7.1%, L -7.1%, H +5.3%, UD; Path=-5.4% → +10.4% | S Now=NA; Path=NA | WMA200=-15.6%, UP</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%18,2 / XU030 -%8,8 / Fark -%9,4 puan | M: Hisse -%7,2 / XU030 -%4,7 / Fark -%2,5 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%18,1 / XU030 -%8,7 / Fark -%9,4 puan | M: Hisse -%7,1 / XU030 -%4,6 / Fark -%2,5 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="I24" s="4" t="inlineStr">
@@ -8210,9 +8210,9 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>ALT -  - 11/0
+          <t>LONG - 7 - 11/0
 ALT -  - 12/2
-ALT -  - 13/2</t>
+ALT -  - 12/2</t>
         </is>
       </c>
     </row>
@@ -8245,12 +8245,12 @@
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU + RİSK: Action=RISK | Trade_Action=RISK | Önerilen=EVET | Öneren sistem=1 | Q Now=Now -3.4%, L -22.1%, H +0.0%, DU; Path=-9.4% → +18.3% | M Now=Now +12.3%, L -9.4%, H +15.1%, DU; Path=+5.8% → -7.2% | S Now=NA; Path=NA | WMA200=-4.1%, UP</t>
+          <t>OLUMLU + RİSK: Action=RISK | Trade_Action=RISK | Önerilen=EVET | Öneren sistem=1 | Q Now=Now -3.4%, L -22.1%, H +0.0%, DU; Path=-9.4% → +18.3% | M Now=Now +12.4%, L -9.4%, H +15.1%, DU; Path=+5.8% → -7.2% | S Now=NA; Path=NA | WMA200=-4.0%, UP</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%3,4 / XU030 -%8,8 / Fark +%5,4 puan | M: Hisse +%12,3 / XU030 -%4,7 / Fark +%17,0 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%3,4 / XU030 -%8,7 / Fark +%5,3 puan | M: Hisse +%12,4 / XU030 -%4,6 / Fark +%17,0 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
@@ -8290,7 +8290,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>SHORT - 1 - 1/17
+          <t>SHORT - 1 - 1/18
 SHORT - 1 - 1/14
 UST -  - 3/12</t>
         </is>
@@ -8325,12 +8325,12 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: Action=LATE | Trade_Action=LATE | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -16.0%, L -24.8%, H +0.0%, DU; Path=+14.0% → -18.2% | M Now=Now -4.2%, L -13.5%, H +1.8%, DU; Path=-5.4% → +8.8% | S Now=NA; Path=NA | WMA200=-6.7%, UP</t>
+          <t>NÖTR: Action=LATE | Trade_Action=LATE | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -15.9%, L -24.8%, H +0.0%, DU; Path=+14.0% → -18.2% | M Now=Now -4.1%, L -13.5%, H +1.8%, DU; Path=-5.4% → +8.8% | S Now=NA; Path=NA | WMA200=-6.6%, UP</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%16,0 / XU030 -%8,8 / Fark -%7,2 puan | M: Hisse -%4,2 / XU030 -%4,7 / Fark +%0,5 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%15,9 / XU030 -%8,7 / Fark -%7,2 puan | M: Hisse -%4,1 / XU030 -%4,6 / Fark +%0,5 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="I26" s="4" t="inlineStr">
@@ -8340,7 +8340,7 @@
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU + RİSK: Endeks=XU030 | Karar=AL_ADAYI | AL basari=80 n=10 | SAT basari=34.48275862068966 n=29</t>
+          <t>OLUMLU + RİSK: Endeks=XU030 | Karar=AL_ADAYI | AL basari=80 n=10 | SAT basari=37.93103448275862 n=29</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
@@ -8826,12 +8826,12 @@
       </c>
       <c r="H2" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: Action=LONG_WATCH | Trade_Action=LONG_WATCH | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -8.8%, L -11.1%, H +1.0%, DU; Path=+11.3% → -11.7% | M Now=Now -4.7%, L -5.4%, H +4.1%, UD; Path=+3.8% → -4.5% | S Now=NA; Path=NA | WMA200=-5.4%, DOWN</t>
+          <t>OLUMLU: Action=LONG_WATCH | Trade_Action=LONG_WATCH | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -8.7%, L -11.1%, H +1.0%, DU; Path=+11.3% → -11.7% | M Now=Now -4.6%, L -5.4%, H +4.1%, UD; Path=+3.8% → -4.5% | S Now=NA; Path=NA | WMA200=-5.3%, DOWN</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%8,8 / XU030 -%8,8 / Fark %0,0 puan | M: Hisse -%4,7 / XU030 -%4,7 / Fark %0,0 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%8,7 / XU030 -%8,7 / Fark %0,0 puan | M: Hisse -%4,6 / XU030 -%4,6 / Fark %0,0 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr">
@@ -8871,7 +8871,7 @@
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>ALT -  - 11/0
+          <t>LONG - 7 - 10/0
 LONG - 7 - 9/1
 LONG - 7 - 9/1</t>
         </is>
@@ -8913,12 +8913,12 @@
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: Action=LOW_DATA | Trade_Action=LOW_DATA | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -10.1%, L -15.0%, H +22.6%, UD; Path=+24.2% → -19.6% | M Now=Now -18.7%, L -23.1%, H +0.0%, DU; Path=+2.6% → -11.0% | S Now=NA; Path=NA | WMA200=-10.5%, UP</t>
+          <t>NÖTR: Action=LOW_DATA | Trade_Action=LOW_DATA | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -10.0%, L -15.0%, H +22.6%, UD; Path=+24.2% → -19.6% | M Now=Now -18.6%, L -23.1%, H +0.0%, DU; Path=+2.6% → -11.0% | S Now=NA; Path=NA | WMA200=-10.4%, UP</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%10,1 / XU030 -%8,8 / Fark -%1,3 puan | M: Hisse -%18,7 / XU030 -%4,7 / Fark -%14,0 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%10,0 / XU030 -%8,7 / Fark -%1,3 puan | M: Hisse -%18,6 / XU030 -%4,6 / Fark -%14,0 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
@@ -8928,7 +8928,7 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: Endeks=XU030 | Karar=AL_ADAYI | AL basari=66.66666666666667 n=3 | SAT basari=40 n=20</t>
+          <t>NÖTR: Endeks=XU030 | Karar=AL_ADAYI | AL basari=66.66666666666667 n=3 | SAT basari=42.85714285714285 n=21</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -9000,12 +9000,12 @@
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: Action=LONG_WATCH | Trade_Action=LONG_WATCH | Önerilen=EVET | Öneren sistem=3 | Q Now=Now -0.8%, L -9.5%, H +14.3%, UD; Path=+13.0% → -20.0% | M Now=Now -0.5%, L -4.9%, H +8.8%, UD; Path=+7.7% → -9.1% | S Now=NA; Path=NA | WMA200=-2.9%, DOWN</t>
+          <t>OLUMLU: Action=LONG_WATCH | Trade_Action=LONG_WATCH | Önerilen=EVET | Öneren sistem=3 | Q Now=Now -0.8%, L -9.5%, H +14.3%, UD; Path=+13.0% → -20.0% | M Now=Now -0.4%, L -4.9%, H +8.8%, UD; Path=+7.7% → -9.1% | S Now=NA; Path=NA | WMA200=-2.9%, DOWN</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%0,8 / XU030 -%8,8 / Fark +%8,0 puan | M: Hisse -%0,5 / XU030 -%4,7 / Fark +%4,2 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%0,8 / XU030 -%8,7 / Fark +%7,9 puan | M: Hisse -%0,4 / XU030 -%4,6 / Fark +%4,2 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="J4" s="5" t="inlineStr">
@@ -9015,7 +9015,7 @@
       </c>
       <c r="K4" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=AL_ADAYI | AL basari=65.38461538461539 n=26 | SAT basari=37.5 n=48</t>
+          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=AL_ADAYI | AL basari=66.66666666666667 n=27 | SAT basari=41.66666666666666 n=48</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
@@ -9047,7 +9047,7 @@
         <is>
           <t>LONG - 1 - 8/2
 LONG - 7 - 5/5
-LONG - 1 - 9/2</t>
+LONG - 1 - 8/2</t>
         </is>
       </c>
     </row>
@@ -9087,12 +9087,12 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: Action=LATE | Trade_Action=LATE | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -14.0%, L -17.3%, H +5.4%, DU; Path=+13.8% → -19.2% | M Now=Now +2.7%, L -0.5%, H +8.5%, UD; Path=+4.4% → -8.5% | S Now=NA; Path=NA | WMA200=-8.7%, UP</t>
+          <t>NÖTR: Action=LATE | Trade_Action=LATE | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -13.9%, L -17.3%, H +5.4%, DU; Path=+13.8% → -19.2% | M Now=Now +2.8%, L -0.5%, H +8.5%, UD; Path=+4.4% → -8.5% | S Now=NA; Path=NA | WMA200=-8.7%, UP</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%14,0 / XU030 -%8,8 / Fark -%5,2 puan | M: Hisse +%2,7 / XU030 -%4,7 / Fark +%7,4 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%13,9 / XU030 -%8,7 / Fark -%5,2 puan | M: Hisse +%2,8 / XU030 -%4,6 / Fark +%7,4 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
@@ -9174,12 +9174,12 @@
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: Action=LONG_WATCH | Trade_Action=LONG_WATCH | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -15.8%, L -23.0%, H +40.7%, UD; Path=-16.0% → +18.8% | M Now=Now -9.6%, L -17.3%, H +3.7%, UD; Path=+5.8% → -6.9% | S Now=NA; Path=NA | WMA200=-16.6%, UP</t>
+          <t>OLUMLU: Action=LONG_WATCH | Trade_Action=LONG_WATCH | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -15.7%, L -23.0%, H +40.7%, UD; Path=-16.0% → +18.8% | M Now=Now -9.5%, L -17.3%, H +3.7%, UD; Path=+5.8% → -6.9% | S Now=NA; Path=NA | WMA200=-16.6%, UP</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%15,8 / XU030 -%8,8 / Fark -%7,0 puan | M: Hisse -%9,6 / XU030 -%4,7 / Fark -%4,9 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%15,7 / XU030 -%8,7 / Fark -%7,0 puan | M: Hisse -%9,5 / XU030 -%4,6 / Fark -%4,9 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -9261,12 +9261,12 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: Action=LONG_WATCH | Trade_Action=LONG_WATCH | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -12.7%, L -12.7%, H +6.2%, UD; Path=+8.2% → -13.3% | M Now=Now -8.8%, L -8.8%, H +0.0%, DU; Path=-3.3% → +10.4% | S Now=NA; Path=NA | WMA200=-14.4%, UP</t>
+          <t>OLUMLU: Action=LONG_WATCH | Trade_Action=LONG_WATCH | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -12.6%, L -12.6%, H +6.2%, UD; Path=+8.2% → -13.3% | M Now=Now -8.7%, L -8.7%, H +0.0%, DU; Path=-3.3% → +10.4% | S Now=NA; Path=NA | WMA200=-14.3%, UP</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%12,7 / XU030 -%8,8 / Fark -%3,9 puan | M: Hisse -%8,8 / XU030 -%4,7 / Fark -%4,1 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%12,6 / XU030 -%8,7 / Fark -%3,9 puan | M: Hisse -%8,7 / XU030 -%4,6 / Fark -%4,1 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -9276,7 +9276,7 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: Endeks=XU030 | Karar=AL_BEKLE_EŞİK | AL basari=63.88888888888889 n=36 | SAT basari=nan n=0</t>
+          <t>NÖTR: Endeks=XU030 | Karar=AL_BEKLE_EŞİK | AL basari=62.16216216216216 n=37 | SAT basari=nan n=0</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
@@ -9348,12 +9348,12 @@
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: Action=LONG_WATCH | Trade_Action=LONG_WATCH | Önerilen=EVET | Öneren sistem=7 | Q Now=Now +11.0%, L -2.2%, H +14.5%, DU; Path=+17.9% → -12.9% | M Now=Now +2.6%, L -1.5%, H +5.8%, UD; Path=+6.0% → -6.5% | S Now=NA; Path=NA | WMA200=+5.4%, DOWN</t>
+          <t>OLUMLU: Action=LONG_WATCH | Trade_Action=LONG_WATCH | Önerilen=EVET | Öneren sistem=7 | Q Now=Now +11.1%, L -2.2%, H +14.5%, DU; Path=+17.9% → -12.9% | M Now=Now +2.7%, L -1.5%, H +5.8%, UD; Path=+6.0% → -6.5% | S Now=NA; Path=NA | WMA200=+5.5%, DOWN</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse +%11,0 / XU030 -%8,8 / Fark +%19,8 puan | M: Hisse +%2,6 / XU030 -%4,7 / Fark +%7,3 puan | S: VERİ YOK</t>
+          <t>Q: Hisse +%11,1 / XU030 -%8,7 / Fark +%19,8 puan | M: Hisse +%2,7 / XU030 -%4,6 / Fark +%7,3 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
@@ -9363,7 +9363,7 @@
       </c>
       <c r="K8" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=SAT_ADAYI | AL basari=nan n=0 | SAT basari=44.44444444444444 n=27</t>
+          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=SAT_ADAYI | AL basari=nan n=0 | SAT basari=40.74074074074074 n=27</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
@@ -9395,7 +9395,7 @@
         <is>
           <t>SHORT - 2 - 2/9
 SHORT - 10 - 4/8
-SHORT - 2 - 2/7</t>
+SHORT - 2 - 2/8</t>
         </is>
       </c>
     </row>
@@ -9435,12 +9435,12 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: Action=LONG_WATCH | Trade_Action=LONG_WATCH | Önerilen=EVET | Öneren sistem=5 | Q Now=Now -23.2%, L -24.0%, H +1.2%, DU; Path=+13.9% → -20.1% | M Now=Now -9.9%, L -10.9%, H +3.2%, DU; Path=+6.0% → -9.1% | S Now=NA; Path=NA | WMA200=-24.6%, UP</t>
+          <t>OLUMLU: Action=LONG_WATCH | Trade_Action=LONG_WATCH | Önerilen=EVET | Öneren sistem=5 | Q Now=Now -23.1%, L -24.0%, H +1.2%, DU; Path=+13.9% → -20.1% | M Now=Now -9.9%, L -10.9%, H +3.2%, DU; Path=+6.0% → -9.1% | S Now=NA; Path=NA | WMA200=-24.5%, UP</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%23,2 / XU030 -%8,8 / Fark -%14,4 puan | M: Hisse -%9,9 / XU030 -%4,7 / Fark -%5,2 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%23,1 / XU030 -%8,7 / Fark -%14,4 puan | M: Hisse -%9,9 / XU030 -%4,6 / Fark -%5,3 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
@@ -9481,7 +9481,7 @@
       <c r="Q9" s="2" t="inlineStr">
         <is>
           <t>ALT -  - 14/3
-ALT -  - 38/18
+ALT -  - 38/17
 LONG - 1 - 27/0</t>
         </is>
       </c>
@@ -9522,12 +9522,12 @@
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: Action=LONG_READY | Trade_Action=LONG_READY | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -18.3%, L -20.2%, H +0.3%, DU; Path=-3.6% → +58.5% | M Now=Now -13.5%, L -15.5%, H +3.4%, UD; Path=-6.5% → +7.6% | S Now=NA; Path=NA | WMA200=-24.8%, UP</t>
+          <t>OLUMLU: Action=LONG_READY | Trade_Action=LONG_READY | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -18.2%, L -20.2%, H +0.3%, DU; Path=-3.6% → +58.5% | M Now=Now -13.5%, L -15.5%, H +3.4%, UD; Path=-6.5% → +7.6% | S Now=NA; Path=NA | WMA200=-24.8%, UP</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%18,3 / XU030 -%8,8 / Fark -%9,5 puan | M: Hisse -%13,5 / XU030 -%4,7 / Fark -%8,8 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%18,2 / XU030 -%8,7 / Fark -%9,5 puan | M: Hisse -%13,5 / XU030 -%4,6 / Fark -%8,9 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
@@ -9537,7 +9537,7 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: Endeks=XU030 | Karar=AL_BEKLE_EŞİK | AL basari=68.18181818181819 n=22 | SAT basari=nan n=0</t>
+          <t>NÖTR: Endeks=XU030 | Karar=AL_BEKLE_EŞİK | AL basari=66.66666666666667 n=21 | SAT basari=nan n=0</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
@@ -9609,12 +9609,12 @@
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: Action=RISK | Trade_Action=RISK | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -9.4%, L -11.3%, H +11.4%, UD; Path=+16.1% → -17.8% | M Now=Now +0.1%, L -1.1%, H +6.1%, UD; Path=+4.8% → -9.8% | S Now=NA; Path=NA | WMA200=-7.3%, DOWN</t>
+          <t>OLUMSUZ / RİSK: Action=RISK | Trade_Action=RISK | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -9.3%, L -11.3%, H +11.4%, UD; Path=+16.1% → -17.8% | M Now=Now +0.2%, L -1.1%, H +6.1%, UD; Path=+4.8% → -9.8% | S Now=NA; Path=NA | WMA200=-7.2%, DOWN</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%9,4 / XU030 -%8,8 / Fark -%0,6 puan | M: Hisse +%0,1 / XU030 -%4,7 / Fark +%4,8 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%9,3 / XU030 -%8,7 / Fark -%0,6 puan | M: Hisse +%0,2 / XU030 -%4,6 / Fark +%4,8 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
@@ -9624,7 +9624,7 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: Endeks=XU030 | Karar=AL_BEKLE_EŞİK | AL basari=60.41666666666666 n=48 | SAT basari=nan n=0</t>
+          <t>NÖTR: Endeks=XU030 | Karar=AL_BEKLE_EŞİK | AL basari=61.22448979591837 n=49 | SAT basari=nan n=0</t>
         </is>
       </c>
       <c r="L11" s="4" t="inlineStr">
@@ -9696,12 +9696,12 @@
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: Action=LOW_DATA | Trade_Action=LOW_DATA | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -65.4%, L -67.5%, H +3.7%, UD; Path=-7.3% → +40.3% | M Now=Now -13.2%, L -18.6%, H +0.3%, DU; Path=-11.6% → +14.1% | S Now=NA; Path=NA | WMA200=-55.7%, UP</t>
+          <t>NÖTR: Action=LOW_DATA | Trade_Action=LOW_DATA | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -65.4%, L -67.5%, H +3.7%, UD; Path=-7.3% → +40.3% | M Now=Now -13.2%, L -18.6%, H +0.3%, DU; Path=-11.6% → +14.1% | S Now=NA; Path=NA | WMA200=-55.6%, UP</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%65,4 / XU030 -%8,8 / Fark -%56,6 puan | M: Hisse -%13,2 / XU030 -%4,7 / Fark -%8,5 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%65,4 / XU030 -%8,7 / Fark -%56,7 puan | M: Hisse -%13,2 / XU030 -%4,6 / Fark -%8,6 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -9711,7 +9711,7 @@
       </c>
       <c r="K12" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=SAT_BEKLE_EŞİK | AL basari=nan n=1 | SAT basari=42.85714285714285 n=28</t>
+          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=SAT_BEKLE_EŞİK | AL basari=nan n=1 | SAT basari=44.82758620689656 n=29</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
@@ -9783,12 +9783,12 @@
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: Action=NO_CLEAR_EDGE | Trade_Action=NO_CLEAR_EDGE | Önerilen=EVET | Öneren sistem=1 | Q Now=Now -20.2%, L -20.2%, H +3.0%, DU; Path=+19.8% → -15.3% | M Now=Now -7.2%, L -7.2%, H +1.1%, DU; Path=-6.5% → +8.6% | S Now=NA; Path=NA | WMA200=-20.4%, UP</t>
+          <t>OLUMLU: Action=NO_CLEAR_EDGE | Trade_Action=NO_CLEAR_EDGE | Önerilen=EVET | Öneren sistem=1 | Q Now=Now -20.1%, L -20.1%, H +3.0%, DU; Path=+19.8% → -15.3% | M Now=Now -7.1%, L -7.1%, H +1.1%, DU; Path=-6.5% → +8.6% | S Now=NA; Path=NA | WMA200=-20.4%, UP</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%20,2 / XU030 -%8,8 / Fark -%11,4 puan | M: Hisse -%7,2 / XU030 -%4,7 / Fark -%2,5 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%20,1 / XU030 -%8,7 / Fark -%11,4 puan | M: Hisse -%7,1 / XU030 -%4,6 / Fark -%2,5 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
@@ -9798,7 +9798,7 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: Endeks=XU030 | Karar=AL_BEKLE_EŞİK | AL basari=54.54545454545455 n=44 | SAT basari=nan n=0</t>
+          <t>NÖTR: Endeks=XU030 | Karar=AL_BEKLE_EŞİK | AL basari=50 n=42 | SAT basari=nan n=0</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
@@ -9828,8 +9828,8 @@
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>LONG - 5 - 17/1
-LONG - 5 - 17/1
+          <t>LONG - 5 - 16/1
+LONG - 5 - 16/1
 ALT -  - 15/2</t>
         </is>
       </c>
@@ -9870,12 +9870,12 @@
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: Action=LONG_WATCH | Trade_Action=LONG_WATCH | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -12.8%, L -26.7%, H +2.9%, UD; Path=+17.0% → -14.4% | M Now=Now -10.0%, L -24.3%, H +0.0%, DU; Path=+9.0% → -5.1% | S Now=NA; Path=NA | WMA200=-22.0%, UP</t>
+          <t>OLUMLU: Action=LONG_WATCH | Trade_Action=LONG_WATCH | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -12.8%, L -26.7%, H +2.9%, UD; Path=+17.0% → -14.4% | M Now=Now -9.9%, L -24.3%, H +0.0%, DU; Path=+9.0% → -5.1% | S Now=NA; Path=NA | WMA200=-22.0%, UP</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%12,8 / XU030 -%8,8 / Fark -%4,0 puan | M: Hisse -%10,0 / XU030 -%4,7 / Fark -%5,3 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%12,8 / XU030 -%8,7 / Fark -%4,1 puan | M: Hisse -%9,9 / XU030 -%4,6 / Fark -%5,3 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -9885,7 +9885,7 @@
       </c>
       <c r="K14" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=SAT_BEKLE_EŞİK | AL basari=nan n=0 | SAT basari=35.71428571428572 n=28</t>
+          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=SAT_BEKLE_EŞİK | AL basari=nan n=0 | SAT basari=33.33333333333334 n=27</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
@@ -9915,7 +9915,7 @@
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>UST -  - 2/12
+          <t>UST -  - 3/12
 LONG - 1 - 19/3
 ALT -  - 20/2</t>
         </is>
@@ -9957,12 +9957,12 @@
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: Action=LOW_DATA | Trade_Action=LOW_DATA | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now +13.9%, L -27.7%, H +13.9%, DU; Path=+70.0% → -20.5% | M Now=Now +31.0%, L +0.0%, H +31.0%, UD; Path=+11.3% → -20.5% | S Now=NA; Path=NA | WMA200=+32.9%, DOWN</t>
+          <t>NÖTR: Action=LOW_DATA | Trade_Action=LOW_DATA | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now +14.0%, L -27.7%, H +14.0%, DU; Path=+70.0% → -20.5% | M Now=Now +31.1%, L +0.0%, H +31.1%, UD; Path=+11.3% → -20.5% | S Now=NA; Path=NA | WMA200=+33.0%, DOWN</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse +%13,9 / XU030 -%8,8 / Fark +%22,7 puan | M: Hisse +%31,0 / XU030 -%4,7 / Fark +%35,7 puan | S: VERİ YOK</t>
+          <t>Q: Hisse +%14,0 / XU030 -%8,7 / Fark +%22,7 puan | M: Hisse +%31,1 / XU030 -%4,6 / Fark +%35,7 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="J15" s="5" t="inlineStr">
@@ -9987,7 +9987,7 @@
       </c>
       <c r="N15" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / GEÇ KALMA RİSKİ: Açık=EVET | Sayfa=USD | Güncel=%13,7 | Max_Aktif_Kar=%14,3 | Min=%0,0 | Grup/Etiket=USD/LAST_3_TOP3/T5_tek_sistem|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan|keltner_kirilim</t>
+          <t>OLUMSUZ / GEÇ KALMA RİSKİ: Açık=EVET | Sayfa=USD | Güncel=%13,8 | Max_Aktif_Kar=%14,4 | Min=%0,0 | Grup/Etiket=USD/LAST_3_TOP3/T5_tek_sistem|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan|keltner_kirilim</t>
         </is>
       </c>
       <c r="O15" s="4" t="inlineStr">
@@ -10044,12 +10044,12 @@
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: Action=LATE | Trade_Action=LATE | Önerilen=EVET | Öneren sistem=2 | Q Now=Now -2.3%, L -12.4%, H +10.3%, UD; Path=-11.4% → +22.3% | M Now=Now -4.1%, L -12.6%, H +8.3%, UD; Path=-5.2% → +11.5% | S Now=NA; Path=NA | WMA200=-9.3%, UP</t>
+          <t>OLUMLU: Action=LATE | Trade_Action=LATE | Önerilen=EVET | Öneren sistem=2 | Q Now=Now -2.2%, L -12.4%, H +10.3%, UD; Path=-11.4% → +22.3% | M Now=Now -4.0%, L -12.6%, H +8.3%, UD; Path=-5.2% → +11.5% | S Now=NA; Path=NA | WMA200=-9.2%, UP</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%2,3 / XU030 -%8,8 / Fark +%6,5 puan | M: Hisse -%4,1 / XU030 -%4,7 / Fark +%0,6 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%2,2 / XU030 -%8,7 / Fark +%6,5 puan | M: Hisse -%4,0 / XU030 -%4,6 / Fark +%0,6 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
@@ -10059,7 +10059,7 @@
       </c>
       <c r="K16" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=SAT_BEKLE_EŞİK | AL basari=nan n=0 | SAT basari=40 n=40</t>
+          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=SAT_BEKLE_EŞİK | AL basari=nan n=0 | SAT basari=38.46153846153846 n=39</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
@@ -10090,7 +10090,7 @@
       <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>LONG - 1 - 10/3
-LONG - 7 - 13/12
+LONG - 7 - 12/12
 LONG - 1 - 10/3</t>
         </is>
       </c>
@@ -10131,12 +10131,12 @@
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: Action=LONG_READY | Trade_Action=LONG_READY | Önerilen=EVET | Öneren sistem=2 | Q Now=Now -16.2%, L -16.2%, H +2.2%, DU; Path=-8.4% → +17.8% | M Now=Now -7.9%, L -7.9%, H +9.7%, UD; Path=-4.5% → +8.3% | S Now=NA; Path=NA | WMA200=-20.6%, UP</t>
+          <t>OLUMLU: Action=LONG_READY | Trade_Action=LONG_READY | Önerilen=EVET | Öneren sistem=2 | Q Now=Now -16.1%, L -16.1%, H +2.2%, DU; Path=-8.4% → +17.8% | M Now=Now -7.8%, L -7.8%, H +9.7%, UD; Path=-4.5% → +8.3% | S Now=NA; Path=NA | WMA200=-20.5%, UP</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%16,2 / XU030 -%8,8 / Fark -%7,4 puan | M: Hisse -%7,9 / XU030 -%4,7 / Fark -%3,2 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%16,1 / XU030 -%8,7 / Fark -%7,4 puan | M: Hisse -%7,8 / XU030 -%4,6 / Fark -%3,2 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
@@ -10146,7 +10146,7 @@
       </c>
       <c r="K17" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=SAT_ADAYI | AL basari=56.81818181818182 n=44 | SAT basari=59.09090909090909 n=22</t>
+          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=SAT_ADAYI | AL basari=57.77777777777778 n=45 | SAT basari=56.52173913043478 n=23</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
@@ -10218,12 +10218,12 @@
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: Action=LONG_WATCH | Trade_Action=LONG_WATCH | Önerilen=EVET | Öneren sistem=3 | Q Now=Now -52.4%, L -56.6%, H +5.2%, UD; Path=-20.9% → +28.1% | M Now=Now -46.0%, L -50.8%, H +7.8%, UD; Path=+10.4% → -12.2% | S Now=NA; Path=NA | WMA200=-50.3%, UP</t>
+          <t>OLUMLU: Action=LONG_WATCH | Trade_Action=LONG_WATCH | Önerilen=EVET | Öneren sistem=3 | Q Now=Now -52.3%, L -56.6%, H +5.2%, UD; Path=-20.9% → +28.1% | M Now=Now -45.9%, L -50.8%, H +7.8%, UD; Path=+10.4% → -12.2% | S Now=NA; Path=NA | WMA200=-50.3%, UP</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%52,4 / XU030 -%8,8 / Fark -%43,6 puan | M: Hisse -%46,0 / XU030 -%4,7 / Fark -%41,3 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%52,3 / XU030 -%8,7 / Fark -%43,6 puan | M: Hisse -%45,9 / XU030 -%4,6 / Fark -%41,3 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
@@ -10263,8 +10263,8 @@
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>ALT -  - 79/58
-ALT -  - 160/92
+          <t>ALT -  - 78/58
+ALT -  - 159/92
 ALT -  - 56/41</t>
         </is>
       </c>
@@ -10305,12 +10305,12 @@
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: Action=NO_CLEAR_EDGE | Trade_Action=NO_CLEAR_EDGE | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -21.1%, L -25.8%, H +6.0%, DU; Path=-14.1% → +20.9% | M Now=Now -7.0%, L -12.4%, H +2.3%, DU; Path=-5.4% → +11.2% | S Now=NA; Path=NA | WMA200=-8.5%, UP</t>
+          <t>NÖTR: Action=NO_CLEAR_EDGE | Trade_Action=NO_CLEAR_EDGE | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -21.1%, L -25.8%, H +6.0%, DU; Path=-14.1% → +20.9% | M Now=Now -6.9%, L -12.4%, H +2.3%, DU; Path=-5.4% → +11.2% | S Now=NA; Path=NA | WMA200=-8.4%, UP</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%21,1 / XU030 -%8,8 / Fark -%12,3 puan | M: Hisse -%7,0 / XU030 -%4,7 / Fark -%2,3 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%21,1 / XU030 -%8,7 / Fark -%12,4 puan | M: Hisse -%6,9 / XU030 -%4,6 / Fark -%2,3 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
@@ -10320,7 +10320,7 @@
       </c>
       <c r="K19" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=SAT_BEKLE_EŞİK | AL basari=72.72727272727273 n=11 | SAT basari=44.73684210526316 n=76</t>
+          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=SAT_BEKLE_EŞİK | AL basari=70 n=10 | SAT basari=45.33333333333334 n=75</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
@@ -10352,7 +10352,7 @@
         <is>
           <t>LONG - 3 - 4/6
 SHORT - 68 - 7/12
-LONG - 1 - 8/2</t>
+LONG - 1 - 8/3</t>
         </is>
       </c>
     </row>
@@ -10392,12 +10392,12 @@
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: Action=NO_CLEAR_EDGE | Trade_Action=NO_CLEAR_EDGE | Önerilen=EVET | Öneren sistem=7 | Q Now=Now -20.4%, L -26.4%, H +6.8%, UD; Path=+12.0% → -16.3% | M Now=Now -6.9%, L -7.1%, H +2.4%, DU; Path=-6.9% → +6.6% | S Now=NA; Path=NA | WMA200=-17.9%, UP</t>
+          <t>OLUMLU: Action=NO_CLEAR_EDGE | Trade_Action=NO_CLEAR_EDGE | Önerilen=EVET | Öneren sistem=7 | Q Now=Now -20.3%, L -26.4%, H +6.8%, UD; Path=+12.0% → -16.3% | M Now=Now -6.8%, L -7.1%, H +2.4%, DU; Path=-6.9% → +6.6% | S Now=NA; Path=NA | WMA200=-17.9%, UP</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%20,4 / XU030 -%8,8 / Fark -%11,6 puan | M: Hisse -%6,9 / XU030 -%4,7 / Fark -%2,2 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%20,3 / XU030 -%8,7 / Fark -%11,6 puan | M: Hisse -%6,8 / XU030 -%4,6 / Fark -%2,2 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
@@ -10479,12 +10479,12 @@
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: Action=LONG_WATCH | Trade_Action=LONG_WATCH | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -14.3%, L -17.6%, H +0.0%, DU; Path=+12.6% → -15.1% | M Now=Now -6.6%, L -10.3%, H +3.2%, UD; Path=+6.2% → -7.8% | S Now=NA; Path=NA | WMA200=-10.3%, UP</t>
+          <t>OLUMLU: Action=LONG_WATCH | Trade_Action=LONG_WATCH | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -14.2%, L -17.6%, H +0.0%, DU; Path=+12.6% → -15.1% | M Now=Now -6.6%, L -10.3%, H +3.2%, UD; Path=+6.2% → -7.8% | S Now=NA; Path=NA | WMA200=-10.2%, UP</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%14,3 / XU030 -%8,8 / Fark -%5,5 puan | M: Hisse -%6,6 / XU030 -%4,7 / Fark -%1,9 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%14,2 / XU030 -%8,7 / Fark -%5,5 puan | M: Hisse -%6,6 / XU030 -%4,6 / Fark -%2,0 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
@@ -10494,7 +10494,7 @@
       </c>
       <c r="K21" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=SAT_ADAYI | AL basari=52 n=25 | SAT basari=42.85714285714285 n=35</t>
+          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=SAT_ADAYI | AL basari=50 n=24 | SAT basari=42.85714285714285 n=35</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
@@ -10566,12 +10566,12 @@
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: Action=LONG_WATCH | Trade_Action=LONG_WATCH | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -12.4%, L -15.5%, H +2.4%, DU; Path=-11.7% → +19.3% | M Now=Now +2.1%, L -1.6%, H +6.7%, UD; Path=+6.3% → -7.2% | S Now=NA; Path=NA | WMA200=-11.4%, UP</t>
+          <t>OLUMLU: Action=LONG_WATCH | Trade_Action=LONG_WATCH | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -12.3%, L -15.5%, H +2.4%, DU; Path=-11.7% → +19.3% | M Now=Now +2.2%, L -1.6%, H +6.7%, UD; Path=+6.3% → -7.2% | S Now=NA; Path=NA | WMA200=-11.3%, UP</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%12,4 / XU030 -%8,8 / Fark -%3,6 puan | M: Hisse +%2,1 / XU030 -%4,7 / Fark +%6,8 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%12,3 / XU030 -%8,7 / Fark -%3,6 puan | M: Hisse +%2,2 / XU030 -%4,6 / Fark +%6,8 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
@@ -10581,7 +10581,7 @@
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: Endeks=XU030 | Karar=ÇELİŞKİLİ_BEKLE | AL basari=54.05405405405406 n=37 | SAT basari=33.9622641509434 n=53</t>
+          <t>NÖTR: Endeks=XU030 | Karar=ÇELİŞKİLİ_BEKLE | AL basari=56.75675675675676 n=37 | SAT basari=33.33333333333334 n=54</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
@@ -10612,7 +10612,7 @@
       <c r="Q22" s="2" t="inlineStr">
         <is>
           <t>LONG - 19 - 6/6
-LONG - 7 - 7/3
+LONG - 7 - 7/4
 LONG - 5 - 8/2</t>
         </is>
       </c>
@@ -10653,12 +10653,12 @@
       </c>
       <c r="H23" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: Action=RISK | Trade_Action=RISK | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now +86.4%, L -8.8%, H +86.4%, DU; Path=+7.8% → -18.1% | M Now=Now +27.7%, L -3.7%, H +27.7%, DU; Path=-6.6% → +8.5% | S Now=NA; Path=NA | WMA200=+66.6%, DOWN</t>
+          <t>OLUMSUZ / RİSK: Action=RISK | Trade_Action=RISK | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now +86.5%, L -8.8%, H +86.5%, DU; Path=+7.8% → -18.1% | M Now=Now +27.8%, L -3.7%, H +27.8%, DU; Path=-6.6% → +8.5% | S Now=NA; Path=NA | WMA200=+66.7%, DOWN</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse +%86,4 / XU030 -%8,8 / Fark +%95,2 puan | M: Hisse +%27,7 / XU030 -%4,7 / Fark +%32,4 puan | S: VERİ YOK</t>
+          <t>Q: Hisse +%86,5 / XU030 -%8,7 / Fark +%95,2 puan | M: Hisse +%27,8 / XU030 -%4,6 / Fark +%32,4 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
@@ -10683,7 +10683,7 @@
       </c>
       <c r="N23" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / GEÇ KALMA RİSKİ: Açık=EVET | Sayfa=USD | Güncel=%45,6 | Max_Aktif_Kar=%48,4 | Min=%-0,6 | Grup/Etiket=USD/LAST_3_TOP3/T5_tek_sistem|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan|keltner_kirilim</t>
+          <t>OLUMSUZ / GEÇ KALMA RİSKİ: Açık=EVET | Sayfa=USD | Güncel=%45,8 | Max_Aktif_Kar=%48,4 | Min=%-0,6 | Grup/Etiket=USD/LAST_3_TOP3/T5_tek_sistem|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan|keltner_kirilim</t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
@@ -10740,12 +10740,12 @@
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: Action=LATE | Trade_Action=LATE | Önerilen=EVET | Öneren sistem=1 | Q Now=Now +17.6%, L +0.0%, H +25.4%, UD; Path=-16.4% → +27.7% | M Now=Now +2.8%, L -7.9%, H +5.0%, UD; Path=-5.5% → +13.6% | S Now=NA; Path=NA | WMA200=+3.7%, DOWN</t>
+          <t>OLUMLU: Action=LATE | Trade_Action=LATE | Önerilen=EVET | Öneren sistem=1 | Q Now=Now +17.7%, L +0.0%, H +25.4%, UD; Path=-16.4% → +27.7% | M Now=Now +2.9%, L -7.9%, H +5.0%, UD; Path=-5.5% → +13.6% | S Now=NA; Path=NA | WMA200=+3.8%, DOWN</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse +%17,6 / XU030 -%8,8 / Fark +%26,4 puan | M: Hisse +%2,8 / XU030 -%4,7 / Fark +%7,5 puan | S: VERİ YOK</t>
+          <t>Q: Hisse +%17,7 / XU030 -%8,7 / Fark +%26,4 puan | M: Hisse +%2,9 / XU030 -%4,6 / Fark +%7,5 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
@@ -10755,7 +10755,7 @@
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: Endeks=XU030 | Karar=ÇELİŞKİLİ_BEKLE | AL basari=66.66666666666667 n=9 | SAT basari=36.8421052631579 n=57</t>
+          <t>NÖTR: Endeks=XU030 | Karar=ÇELİŞKİLİ_BEKLE | AL basari=66.66666666666667 n=9 | SAT basari=36.20689655172414 n=58</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
@@ -10827,12 +10827,12 @@
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: Action=LONG_READY | Trade_Action=LONG_READY | Önerilen=EVET | Öneren sistem=13 | Q Now=Now -18.2%, L -18.2%, H +0.1%, DU; Path=+16.5% → -15.5% | M Now=Now -7.2%, L -7.2%, H +5.3%, UD; Path=-5.4% → +10.4% | S Now=NA; Path=NA | WMA200=-15.7%, UP</t>
+          <t>OLUMLU: Action=LONG_READY | Trade_Action=LONG_READY | Önerilen=EVET | Öneren sistem=13 | Q Now=Now -18.1%, L -18.1%, H +0.1%, DU; Path=+16.5% → -15.5% | M Now=Now -7.1%, L -7.1%, H +5.3%, UD; Path=-5.4% → +10.4% | S Now=NA; Path=NA | WMA200=-15.6%, UP</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%18,2 / XU030 -%8,8 / Fark -%9,4 puan | M: Hisse -%7,2 / XU030 -%4,7 / Fark -%2,5 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%18,1 / XU030 -%8,7 / Fark -%9,4 puan | M: Hisse -%7,1 / XU030 -%4,6 / Fark -%2,5 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
@@ -10872,9 +10872,9 @@
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t>ALT -  - 11/0
+          <t>LONG - 7 - 11/0
 ALT -  - 12/2
-ALT -  - 13/2</t>
+ALT -  - 12/2</t>
         </is>
       </c>
     </row>
@@ -10914,12 +10914,12 @@
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU + RİSK: Action=RISK | Trade_Action=RISK | Önerilen=EVET | Öneren sistem=1 | Q Now=Now -3.4%, L -22.1%, H +0.0%, DU; Path=-9.4% → +18.3% | M Now=Now +12.3%, L -9.4%, H +15.1%, DU; Path=+5.8% → -7.2% | S Now=NA; Path=NA | WMA200=-4.1%, UP</t>
+          <t>OLUMLU + RİSK: Action=RISK | Trade_Action=RISK | Önerilen=EVET | Öneren sistem=1 | Q Now=Now -3.4%, L -22.1%, H +0.0%, DU; Path=-9.4% → +18.3% | M Now=Now +12.4%, L -9.4%, H +15.1%, DU; Path=+5.8% → -7.2% | S Now=NA; Path=NA | WMA200=-4.0%, UP</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%3,4 / XU030 -%8,8 / Fark +%5,4 puan | M: Hisse +%12,3 / XU030 -%4,7 / Fark +%17,0 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%3,4 / XU030 -%8,7 / Fark +%5,3 puan | M: Hisse +%12,4 / XU030 -%4,6 / Fark +%17,0 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
@@ -10959,7 +10959,7 @@
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>SHORT - 1 - 1/17
+          <t>SHORT - 1 - 1/18
 SHORT - 1 - 1/14
 UST -  - 3/12</t>
         </is>
@@ -11001,12 +11001,12 @@
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: Action=LATE | Trade_Action=LATE | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -16.0%, L -24.8%, H +0.0%, DU; Path=+14.0% → -18.2% | M Now=Now -4.2%, L -13.5%, H +1.8%, DU; Path=-5.4% → +8.8% | S Now=NA; Path=NA | WMA200=-6.7%, UP</t>
+          <t>NÖTR: Action=LATE | Trade_Action=LATE | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -15.9%, L -24.8%, H +0.0%, DU; Path=+14.0% → -18.2% | M Now=Now -4.1%, L -13.5%, H +1.8%, DU; Path=-5.4% → +8.8% | S Now=NA; Path=NA | WMA200=-6.6%, UP</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%16,0 / XU030 -%8,8 / Fark -%7,2 puan | M: Hisse -%4,2 / XU030 -%4,7 / Fark +%0,5 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%15,9 / XU030 -%8,7 / Fark -%7,2 puan | M: Hisse -%4,1 / XU030 -%4,6 / Fark +%0,5 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
@@ -11016,7 +11016,7 @@
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU + RİSK: Endeks=XU030 | Karar=AL_ADAYI | AL basari=80 n=10 | SAT basari=34.48275862068966 n=29</t>
+          <t>OLUMLU + RİSK: Endeks=XU030 | Karar=AL_ADAYI | AL basari=80 n=10 | SAT basari=37.93103448275862 n=29</t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
@@ -11088,12 +11088,12 @@
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: Action=LATE | Trade_Action=LATE | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -3.2%, L -7.0%, H +7.0%, DU; Path=+13.0% → -18.7% | M Now=Now -2.2%, L -3.8%, H +8.1%, UD; Path=+5.7% → -7.8% | S Now=NA; Path=NA | WMA200=-1.2%, UP</t>
+          <t>NÖTR: Action=LATE | Trade_Action=LATE | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -3.1%, L -7.0%, H +7.0%, DU; Path=+13.0% → -18.7% | M Now=Now -2.1%, L -3.8%, H +8.1%, UD; Path=+5.7% → -7.8% | S Now=NA; Path=NA | WMA200=-1.1%, UP</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%3,2 / XU030 -%8,8 / Fark +%5,6 puan | M: Hisse -%2,2 / XU030 -%4,7 / Fark +%2,5 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%3,1 / XU030 -%8,7 / Fark +%5,6 puan | M: Hisse -%2,1 / XU030 -%4,6 / Fark +%2,5 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr">
@@ -11103,7 +11103,7 @@
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: Endeks=XU030 | Karar=AL_BEKLE_EŞİK | AL basari=70 n=40 | SAT basari=nan n=0</t>
+          <t>NÖTR: Endeks=XU030 | Karar=AL_BEKLE_EŞİK | AL basari=65 n=40 | SAT basari=nan n=0</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
@@ -11175,12 +11175,12 @@
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: Action=LONG_WATCH | Trade_Action=LONG_WATCH | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -4.4%, L -11.1%, H +7.9%, UD; Path=+17.1% → -14.4% | M Now=Now -4.6%, L -7.1%, H +4.2%, UD; Path=+9.0% → -5.4% | S Now=NA; Path=NA | WMA200=-4.8%, DOWN</t>
+          <t>OLUMLU: Action=LONG_WATCH | Trade_Action=LONG_WATCH | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -4.4%, L -11.1%, H +7.9%, UD; Path=+17.1% → -14.4% | M Now=Now -4.5%, L -7.1%, H +4.2%, UD; Path=+9.0% → -5.4% | S Now=NA; Path=NA | WMA200=-4.7%, DOWN</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%4,4 / XU030 -%8,8 / Fark +%4,4 puan | M: Hisse -%4,6 / XU030 -%4,7 / Fark +%0,1 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%4,4 / XU030 -%8,7 / Fark +%4,3 puan | M: Hisse -%4,5 / XU030 -%4,6 / Fark +%0,1 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
@@ -11190,7 +11190,7 @@
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: Endeks=XU030 | Karar=ÇELİŞKİLİ_BEKLE | AL basari=73.6842105263158 n=38 | SAT basari=47.61904761904762 n=42</t>
+          <t>NÖTR: Endeks=XU030 | Karar=ÇELİŞKİLİ_BEKLE | AL basari=72.97297297297297 n=37 | SAT basari=46.51162790697674 n=43</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
@@ -11262,12 +11262,12 @@
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: Action=LONG_WATCH | Trade_Action=LONG_WATCH | Önerilen=EVET | Öneren sistem=8 | Q Now=Now -14.5%, L -18.4%, H +5.0%, DU; Path=+21.0% → -13.0% | M Now=Now -3.7%, L -8.1%, H +4.5%, UD; Path=+6.2% → -5.7% | S Now=NA; Path=NA | WMA200=-16.2%, UP</t>
+          <t>OLUMLU: Action=LONG_WATCH | Trade_Action=LONG_WATCH | Önerilen=EVET | Öneren sistem=8 | Q Now=Now -14.4%, L -18.4%, H +5.0%, DU; Path=+21.0% → -13.0% | M Now=Now -3.6%, L -8.1%, H +4.5%, UD; Path=+6.2% → -5.7% | S Now=NA; Path=NA | WMA200=-16.1%, UP</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%14,5 / XU030 -%8,8 / Fark -%5,7 puan | M: Hisse -%3,7 / XU030 -%4,7 / Fark +%1,0 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%14,4 / XU030 -%8,7 / Fark -%5,7 puan | M: Hisse -%3,6 / XU030 -%4,6 / Fark +%1,0 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="J30" s="5" t="inlineStr">
@@ -11277,7 +11277,7 @@
       </c>
       <c r="K30" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=AL_BEKLE_EŞİK | AL basari=51.72413793103448 n=29 | SAT basari=30.61224489795918 n=49</t>
+          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=AL_ADAYI | AL basari=51.72413793103448 n=29 | SAT basari=30.61224489795918 n=49</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
@@ -11349,12 +11349,12 @@
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: Action=LOW_DATA | Trade_Action=LOW_DATA | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -39.4%, L -42.5%, H +18.0%, UD; Path=+55.7% → -18.8% | M Now=Now -29.3%, L -32.9%, H +0.0%, DU; Path=-12.0% → +16.8% | S Now=NA; Path=NA | WMA200=-33.2%, UP</t>
+          <t>NÖTR: Action=LOW_DATA | Trade_Action=LOW_DATA | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -39.3%, L -42.5%, H +18.0%, UD; Path=+55.7% → -18.8% | M Now=Now -29.3%, L -32.9%, H +0.0%, DU; Path=-12.0% → +16.8% | S Now=NA; Path=NA | WMA200=-33.1%, UP</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%39,4 / XU030 -%8,8 / Fark -%30,6 puan | M: Hisse -%29,3 / XU030 -%4,7 / Fark -%24,6 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%39,3 / XU030 -%8,7 / Fark -%30,6 puan | M: Hisse -%29,3 / XU030 -%4,6 / Fark -%24,7 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr">
@@ -11436,12 +11436,12 @@
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: Action=LONG_WATCH | Trade_Action=LONG_WATCH | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -5.8%, L -6.9%, H +8.1%, UD; Path=+17.1% → -21.6% | M Now=Now -8.2%, L -9.3%, H +0.5%, DU; Path=+2.8% → -11.0% | S Now=NA; Path=NA | WMA200=-10.7%, UP</t>
+          <t>OLUMLU: Action=LONG_WATCH | Trade_Action=LONG_WATCH | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -5.7%, L -6.9%, H +8.1%, UD; Path=+17.1% → -21.6% | M Now=Now -8.2%, L -9.3%, H +0.5%, DU; Path=+2.8% → -11.0% | S Now=NA; Path=NA | WMA200=-10.6%, UP</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%5,8 / XU030 -%8,8 / Fark +%3,0 puan | M: Hisse -%8,2 / XU030 -%4,7 / Fark -%3,5 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%5,7 / XU030 -%8,7 / Fark +%3,0 puan | M: Hisse -%8,2 / XU030 -%4,6 / Fark -%3,6 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
@@ -11523,12 +11523,12 @@
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: Action=RISK | Trade_Action=RISK | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -14.0%, L -18.1%, H +3.1%, UD; Path=+12.6% → -19.2% | M Now=Now -3.9%, L -8.6%, H +13.4%, UD; Path=+4.7% → -10.3% | S Now=NA; Path=NA | WMA200=-10.0%, UP</t>
+          <t>OLUMSUZ / RİSK: Action=RISK | Trade_Action=RISK | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -13.9%, L -18.1%, H +3.1%, UD; Path=+12.6% → -19.2% | M Now=Now -3.8%, L -8.6%, H +13.4%, UD; Path=+4.7% → -10.3% | S Now=NA; Path=NA | WMA200=-9.9%, UP</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%14,0 / XU030 -%8,8 / Fark -%5,2 puan | M: Hisse -%3,9 / XU030 -%4,7 / Fark +%0,8 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%13,9 / XU030 -%8,7 / Fark -%5,2 puan | M: Hisse -%3,8 / XU030 -%4,6 / Fark +%0,8 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
@@ -11538,7 +11538,7 @@
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=AL_ADAYI | AL basari=50 n=20 | SAT basari=46.51162790697674 n=43</t>
+          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=AL_ADAYI | AL basari=50 n=20 | SAT basari=40.90909090909091 n=44</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
@@ -11610,12 +11610,12 @@
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: Action=LONG_WATCH | Trade_Action=LONG_WATCH | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -0.6%, L -4.1%, H +11.4%, DU; Path=+12.5% → -12.8% | M Now=Now -4.5%, L -5.6%, H +6.6%, UD; Path=-6.3% → +8.5% | S Now=NA; Path=NA | WMA200=-8.0%, UP</t>
+          <t>OLUMLU: Action=LONG_WATCH | Trade_Action=LONG_WATCH | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -0.5%, L -4.1%, H +11.4%, DU; Path=+12.5% → -12.8% | M Now=Now -4.4%, L -5.6%, H +6.6%, UD; Path=-6.3% → +8.5% | S Now=NA; Path=NA | WMA200=-7.9%, UP</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%0,6 / XU030 -%8,8 / Fark +%8,2 puan | M: Hisse -%4,5 / XU030 -%4,7 / Fark +%0,2 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%0,5 / XU030 -%8,7 / Fark +%8,2 puan | M: Hisse -%4,4 / XU030 -%4,6 / Fark +%0,2 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="J34" s="5" t="inlineStr">
@@ -11625,7 +11625,7 @@
       </c>
       <c r="K34" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=AL_ADAYI | AL basari=60.52631578947368 n=38 | SAT basari=47.82608695652174 n=23</t>
+          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=AL_ADAYI | AL basari=62.16216216216216 n=37 | SAT basari=45.83333333333334 n=24</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
@@ -11697,12 +11697,12 @@
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: Action=LONG_WATCH | Trade_Action=LONG_WATCH | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -11.1%, L -17.5%, H +8.1%, UD; Path=-8.0% → +22.2% | M Now=Now -1.5%, L -8.7%, H +5.3%, DU; Path=+7.9% → -8.8% | S Now=NA; Path=NA | WMA200=-3.2%, UP</t>
+          <t>OLUMLU: Action=LONG_WATCH | Trade_Action=LONG_WATCH | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -11.0%, L -17.5%, H +8.1%, UD; Path=-8.0% → +22.2% | M Now=Now -1.4%, L -8.7%, H +5.3%, DU; Path=+7.9% → -8.8% | S Now=NA; Path=NA | WMA200=-3.1%, UP</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%11,1 / XU030 -%8,8 / Fark -%2,3 puan | M: Hisse -%1,5 / XU030 -%4,7 / Fark +%3,2 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%11,0 / XU030 -%8,7 / Fark -%2,3 puan | M: Hisse -%1,4 / XU030 -%4,6 / Fark +%3,2 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr">
@@ -11712,7 +11712,7 @@
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=SAT_ADAYI | AL basari=60.71428571428572 n=28 | SAT basari=41.30434782608695 n=46</t>
+          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=SAT_ADAYI | AL basari=51.85185185185185 n=27 | SAT basari=37.5 n=48</t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
@@ -11784,12 +11784,12 @@
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: Action=LATE | Trade_Action=LATE | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -14.1%, L -16.0%, H +0.0%, DU; Path=+16.0% → -15.5% | M Now=Now -2.0%, L -4.1%, H +8.2%, DU; Path=+6.4% → -9.1% | S Now=NA; Path=NA | WMA200=-17.9%, UP</t>
+          <t>NÖTR: Action=LATE | Trade_Action=LATE | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -14.0%, L -16.0%, H +0.0%, DU; Path=+16.0% → -15.5% | M Now=Now -1.9%, L -4.1%, H +8.2%, DU; Path=+6.4% → -9.1% | S Now=NA; Path=NA | WMA200=-17.8%, UP</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%14,1 / XU030 -%8,8 / Fark -%5,3 puan | M: Hisse -%2,0 / XU030 -%4,7 / Fark +%2,7 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%14,0 / XU030 -%8,7 / Fark -%5,3 puan | M: Hisse -%1,9 / XU030 -%4,6 / Fark +%2,7 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="J36" s="4" t="inlineStr">
@@ -11799,7 +11799,7 @@
       </c>
       <c r="K36" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=AL_BEKLE_EŞİK | AL basari=66.66666666666667 n=36 | SAT basari=47.61904761904762 n=42</t>
+          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=AL_BEKLE_EŞİK | AL basari=67.56756756756756 n=37 | SAT basari=45.23809523809524 n=42</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
@@ -11830,8 +11830,8 @@
       <c r="Q36" s="2" t="inlineStr">
         <is>
           <t>LONG - 7 - 9/2
-LONG - 90 - 13/7
-ALT -  - 28/4</t>
+LONG - 90 - 13/8
+ALT -  - 27/4</t>
         </is>
       </c>
     </row>
@@ -11871,12 +11871,12 @@
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: Action=LONG_WATCH | Trade_Action=LONG_WATCH | Önerilen=EVET | Öneren sistem=9 | Q Now=Now -10.7%, L -16.3%, H +0.0%, DU; Path=+15.8% → -15.9% | M Now=Now -3.7%, L -9.8%, H +1.9%, DU; Path=+7.9% → -7.8% | S Now=NA; Path=NA | WMA200=-7.8%, UP</t>
+          <t>OLUMLU: Action=LONG_WATCH | Trade_Action=LONG_WATCH | Önerilen=EVET | Öneren sistem=9 | Q Now=Now -10.6%, L -16.3%, H +0.0%, DU; Path=+15.8% → -15.9% | M Now=Now -3.6%, L -9.8%, H +1.9%, DU; Path=+7.9% → -7.8% | S Now=NA; Path=NA | WMA200=-7.8%, UP</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%10,7 / XU030 -%8,8 / Fark -%1,9 puan | M: Hisse -%3,7 / XU030 -%4,7 / Fark +%1,0 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%10,6 / XU030 -%8,7 / Fark -%1,9 puan | M: Hisse -%3,6 / XU030 -%4,6 / Fark +%1,0 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
@@ -11886,7 +11886,7 @@
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=AL_ADAYI | AL basari=45.83333333333334 n=24 | SAT basari=38.23529411764706 n=34</t>
+          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=AL_ADAYI | AL basari=43.47826086956522 n=23 | SAT basari=38.23529411764706 n=34</t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
@@ -11916,7 +11916,7 @@
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t>LONG - 7 - 11/6
+          <t>LONG - 7 - 10/6
 LONG - 7 - 8/4
 LONG - 85 - 13/8</t>
         </is>
@@ -11958,12 +11958,12 @@
       </c>
       <c r="H38" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: Action=LONG_WATCH | Trade_Action=LONG_WATCH | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -17.8%, L -17.8%, H +9.3%, DU; Path=+25.2% → -19.7% | M Now=Now -18.2%, L -18.2%, H +0.0%, DU; Path=-6.5% → +3.5% | S Now=NA; Path=NA | WMA200=-21.4%, UP</t>
+          <t>OLUMLU: Action=LONG_WATCH | Trade_Action=LONG_WATCH | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -17.7%, L -17.7%, H +9.3%, DU; Path=+25.2% → -19.7% | M Now=Now -18.1%, L -18.1%, H +0.0%, DU; Path=-6.5% → +3.5% | S Now=NA; Path=NA | WMA200=-21.4%, UP</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%17,8 / XU030 -%8,8 / Fark -%9,0 puan | M: Hisse -%18,2 / XU030 -%4,7 / Fark -%13,5 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%17,7 / XU030 -%8,7 / Fark -%9,0 puan | M: Hisse -%18,1 / XU030 -%4,6 / Fark -%13,5 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="J38" s="5" t="inlineStr">
@@ -12045,12 +12045,12 @@
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: Action=LATE | Trade_Action=LATE | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -35.9%, L -36.3%, H +1.4%, DU; Path=+16.9% → -12.8% | M Now=Now -20.7%, L -21.2%, H +10.3%, DU; Path=+5.7% → -8.6% | S Now=NA; Path=NA | WMA200=-34.7%, UP</t>
+          <t>NÖTR: Action=LATE | Trade_Action=LATE | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -35.8%, L -36.3%, H +1.4%, DU; Path=+16.9% → -12.8% | M Now=Now -20.6%, L -21.2%, H +10.3%, DU; Path=+5.7% → -8.6% | S Now=NA; Path=NA | WMA200=-34.7%, UP</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%35,9 / XU030 -%8,8 / Fark -%27,1 puan | M: Hisse -%20,7 / XU030 -%4,7 / Fark -%16,0 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%35,8 / XU030 -%8,7 / Fark -%27,1 puan | M: Hisse -%20,6 / XU030 -%4,6 / Fark -%16,0 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr">
@@ -12132,12 +12132,12 @@
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: Action=NO_CLEAR_EDGE | Trade_Action=NO_CLEAR_EDGE | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -5.7%, L -14.4%, H +6.5%, UD; Path=+14.1% → -12.0% | M Now=Now +1.1%, L -8.2%, H +3.4%, DU; Path=+8.9% → -10.3% | S Now=NA; Path=NA | WMA200=-11.1%, UP</t>
+          <t>NÖTR: Action=NO_CLEAR_EDGE | Trade_Action=NO_CLEAR_EDGE | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -5.6%, L -14.4%, H +6.5%, UD; Path=+14.1% → -12.0% | M Now=Now +1.2%, L -8.2%, H +3.4%, DU; Path=+8.9% → -10.3% | S Now=NA; Path=NA | WMA200=-11.1%, UP</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%5,7 / XU030 -%8,8 / Fark +%3,1 puan | M: Hisse +%1,1 / XU030 -%4,7 / Fark +%5,8 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%5,6 / XU030 -%8,7 / Fark +%3,1 puan | M: Hisse +%1,2 / XU030 -%4,6 / Fark +%5,8 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="J40" s="4" t="inlineStr">
@@ -12147,7 +12147,7 @@
       </c>
       <c r="K40" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=AL_ADAYI | AL basari=76.92307692307692 n=13 | SAT basari=33.33333333333334 n=30</t>
+          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=AL_ADAYI | AL basari=76.92307692307692 n=13 | SAT basari=30.3030303030303 n=33</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="H41" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: Action=LONG_WATCH | Trade_Action=LONG_WATCH | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -24.3%, L -27.5%, H +0.0%, DU; Path=+12.7% → -16.4% | M Now=Now -2.4%, L -6.6%, H +2.8%, DU; Path=+6.3% → -8.8% | S Now=NA; Path=NA | WMA200=-19.3%, UP</t>
+          <t>OLUMLU: Action=LONG_WATCH | Trade_Action=LONG_WATCH | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -24.2%, L -27.5%, H +0.0%, DU; Path=+12.7% → -16.4% | M Now=Now -2.3%, L -6.6%, H +2.8%, DU; Path=+6.3% → -8.8% | S Now=NA; Path=NA | WMA200=-19.2%, UP</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%24,3 / XU030 -%8,8 / Fark -%15,5 puan | M: Hisse -%2,4 / XU030 -%4,7 / Fark +%2,3 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%24,2 / XU030 -%8,7 / Fark -%15,5 puan | M: Hisse -%2,3 / XU030 -%4,6 / Fark +%2,3 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr">
@@ -12234,7 +12234,7 @@
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=SAT_ADAYI | AL basari=58.33333333333334 n=24 | SAT basari=48.48484848484848 n=33</t>
+          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=AL_BEKLE_EŞİK | AL basari=58.33333333333334 n=24 | SAT basari=45.45454545454545 n=33</t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
@@ -12306,12 +12306,12 @@
       </c>
       <c r="H42" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: Action=LONG_WATCH | Trade_Action=LONG_WATCH | Önerilen=EVET | Öneren sistem=2 | Q Now=Now -3.5%, L -10.7%, H +7.6%, DU; Path=+13.4% → -15.8% | M Now=Now -4.1%, L -11.3%, H +3.0%, DU; Path=+5.1% → -7.8% | S Now=NA; Path=NA | WMA200=-9.6%, UP</t>
+          <t>OLUMLU: Action=LONG_WATCH | Trade_Action=LONG_WATCH | Önerilen=EVET | Öneren sistem=2 | Q Now=Now -3.4%, L -10.7%, H +7.6%, DU; Path=+13.4% → -15.8% | M Now=Now -4.0%, L -11.3%, H +3.0%, DU; Path=+5.1% → -7.8% | S Now=NA; Path=NA | WMA200=-9.5%, UP</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%3,5 / XU030 -%8,8 / Fark +%5,3 puan | M: Hisse -%4,1 / XU030 -%4,7 / Fark +%0,6 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%3,4 / XU030 -%8,7 / Fark +%5,3 puan | M: Hisse -%4,0 / XU030 -%4,6 / Fark +%0,6 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
@@ -12352,7 +12352,7 @@
       <c r="Q42" s="2" t="inlineStr">
         <is>
           <t>LONG - 4 - 9/3
-LONG - 4 - 7/4
+LONG - 4 - 6/4
 LONG - 4 - 9/3</t>
         </is>
       </c>
@@ -12393,12 +12393,12 @@
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: Action=LONG_READY | Trade_Action=LONG_READY | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -20.8%, L -21.2%, H +0.2%, DU; Path=-15.5% → +24.8% | M Now=Now -4.8%, L -5.2%, H +2.4%, DU; Path=-9.4% → +8.7% | S Now=NA; Path=NA | WMA200=-17.6%, UP</t>
+          <t>OLUMLU: Action=LONG_READY | Trade_Action=LONG_READY | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -20.8%, L -21.2%, H +0.2%, DU; Path=-15.5% → +24.8% | M Now=Now -4.7%, L -5.2%, H +2.4%, DU; Path=-9.4% → +8.7% | S Now=NA; Path=NA | WMA200=-17.5%, UP</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%20,8 / XU030 -%8,8 / Fark -%12,0 puan | M: Hisse -%4,8 / XU030 -%4,7 / Fark -%0,1 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%20,8 / XU030 -%8,7 / Fark -%12,1 puan | M: Hisse -%4,7 / XU030 -%4,6 / Fark -%0,1 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
@@ -12480,12 +12480,12 @@
       </c>
       <c r="H44" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: Action=LONG_READY | Trade_Action=LONG_READY | Önerilen=EVET | Öneren sistem=2 | Q Now=Now -27.7%, L -27.7%, H +0.0%, DU; Path=-7.1% → +16.1% | M Now=Now -15.3%, L -15.3%, H +6.9%, DU; Path=-4.6% → +9.3% | S Now=NA; Path=NA | WMA200=-26.6%, UP</t>
+          <t>OLUMLU: Action=LONG_READY | Trade_Action=LONG_READY | Önerilen=EVET | Öneren sistem=2 | Q Now=Now -27.7%, L -27.7%, H +0.0%, DU; Path=-7.1% → +16.1% | M Now=Now -15.2%, L -15.2%, H +6.9%, DU; Path=-4.6% → +9.3% | S Now=NA; Path=NA | WMA200=-26.6%, UP</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%27,7 / XU030 -%8,8 / Fark -%18,9 puan | M: Hisse -%15,3 / XU030 -%4,7 / Fark -%10,6 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%27,7 / XU030 -%8,7 / Fark -%19,0 puan | M: Hisse -%15,2 / XU030 -%4,6 / Fark -%10,6 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="J44" s="5" t="inlineStr">
@@ -12525,9 +12525,9 @@
       </c>
       <c r="Q44" s="2" t="inlineStr">
         <is>
-          <t>LONG - 7 - 10/2
-SHORT - 94 - 25/8
-ALT -  - 17/4</t>
+          <t>LONG - 7 - 10/3
+SHORT - 94 - 24/8
+ALT -  - 17/3</t>
         </is>
       </c>
     </row>
@@ -12567,12 +12567,12 @@
       </c>
       <c r="H45" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: Action=RISK | Trade_Action=RISK | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now +17.1%, L -6.4%, H +26.5%, DU; Path=+14.4% → -14.8% | M Now=Now -0.2%, L -1.3%, H +7.9%, UD; Path=-9.8% → +4.5% | S Now=NA; Path=NA | WMA200=+1.5%, UP</t>
+          <t>OLUMSUZ / RİSK: Action=RISK | Trade_Action=RISK | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now +17.2%, L -6.4%, H +26.5%, DU; Path=+14.4% → -14.8% | M Now=Now -0.1%, L -1.3%, H +7.9%, UD; Path=-9.8% → +4.5% | S Now=NA; Path=NA | WMA200=+1.6%, UP</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse +%17,1 / XU030 -%8,8 / Fark +%25,9 puan | M: Hisse -%0,2 / XU030 -%4,7 / Fark +%4,5 puan | S: VERİ YOK</t>
+          <t>Q: Hisse +%17,2 / XU030 -%8,7 / Fark +%25,9 puan | M: Hisse -%0,1 / XU030 -%4,6 / Fark +%4,5 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="J45" s="4" t="inlineStr">
@@ -12582,7 +12582,7 @@
       </c>
       <c r="K45" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=SAT_BEKLE_EŞİK | AL basari=42.5531914893617 n=47 | SAT basari=77.77777777777777 n=9</t>
+          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=SAT_BEKLE_EŞİK | AL basari=45.65217391304348 n=46 | SAT basari=77.77777777777777 n=9</t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
@@ -12654,12 +12654,12 @@
       </c>
       <c r="H46" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: Action=LATE | Trade_Action=LATE | Önerilen=EVET | Öneren sistem=6 | Q Now=Now -9.0%, L -15.3%, H +0.0%, DU; Path=-12.2% → +15.5% | M Now=Now +3.3%, L -3.8%, H +6.7%, UD; Path=-5.6% → +8.7% | S Now=NA; Path=NA | WMA200=-8.6%, UP</t>
+          <t>OLUMLU: Action=LATE | Trade_Action=LATE | Önerilen=EVET | Öneren sistem=6 | Q Now=Now -9.0%, L -15.3%, H +0.0%, DU; Path=-12.2% → +15.5% | M Now=Now +3.4%, L -3.8%, H +6.7%, UD; Path=-5.6% → +8.7% | S Now=NA; Path=NA | WMA200=-8.5%, UP</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%9,0 / XU030 -%8,8 / Fark -%0,2 puan | M: Hisse +%3,3 / XU030 -%4,7 / Fark +%8,0 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%9,0 / XU030 -%8,7 / Fark -%0,3 puan | M: Hisse +%3,4 / XU030 -%4,6 / Fark +%8,0 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="J46" s="5" t="inlineStr">
@@ -12669,7 +12669,7 @@
       </c>
       <c r="K46" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=SAT_BEKLE_EŞİK | AL basari=52.38095238095238 n=21 | SAT basari=27.77777777777778 n=36</t>
+          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=SAT_BEKLE_EŞİK | AL basari=55 n=20 | SAT basari=27.02702702702703 n=37</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
@@ -12699,8 +12699,8 @@
       </c>
       <c r="Q46" s="2" t="inlineStr">
         <is>
-          <t>LONG - 7 - 10/6
-LONG - 7 - 10/6
+          <t>LONG - 7 - 10/7
+LONG - 7 - 10/7
 LONG - 7 - 5/5</t>
         </is>
       </c>
@@ -12741,12 +12741,12 @@
       </c>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: Action=LONG_READY | Trade_Action=LONG_READY | Önerilen=EVET | Öneren sistem=2 | Q Now=Now -15.7%, L -20.3%, H +5.6%, UD; Path=-10.0% → +23.6% | M Now=Now -4.9%, L -10.2%, H +0.8%, DU; Path=+5.6% → -7.2% | S Now=NA; Path=NA | WMA200=-10.3%, UP</t>
+          <t>OLUMLU: Action=LONG_READY | Trade_Action=LONG_READY | Önerilen=EVET | Öneren sistem=2 | Q Now=Now -15.6%, L -20.3%, H +5.6%, UD; Path=-10.0% → +23.6% | M Now=Now -4.8%, L -10.2%, H +0.8%, DU; Path=+5.6% → -7.2% | S Now=NA; Path=NA | WMA200=-10.2%, UP</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%15,7 / XU030 -%8,8 / Fark -%6,9 puan | M: Hisse -%4,9 / XU030 -%4,7 / Fark -%0,2 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%15,6 / XU030 -%8,7 / Fark -%6,9 puan | M: Hisse -%4,8 / XU030 -%4,6 / Fark -%0,2 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="J47" s="5" t="inlineStr">
@@ -12756,7 +12756,7 @@
       </c>
       <c r="K47" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=SAT_BEKLE_EŞİK | AL basari=35.29411764705883 n=17 | SAT basari=56.25 n=32</t>
+          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=SAT_BEKLE_EŞİK | AL basari=35.29411764705883 n=17 | SAT basari=53.125 n=32</t>
         </is>
       </c>
       <c r="L47" s="3" t="inlineStr">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: Action=LATE | Trade_Action=LATE | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -9.4%, L -17.5%, H +0.4%, DU; Path=+17.2% → -16.4% | M Now=Now +6.7%, L -2.9%, H +11.1%, DU; Path=+8.4% → -6.5% | S Now=NA; Path=NA | WMA200=-5.5%, UP</t>
+          <t>NÖTR: Action=LATE | Trade_Action=LATE | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -9.3%, L -17.5%, H +0.4%, DU; Path=+17.2% → -16.4% | M Now=Now +6.8%, L -2.9%, H +11.1%, DU; Path=+8.4% → -6.5% | S Now=NA; Path=NA | WMA200=-5.4%, UP</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%9,4 / XU030 -%8,8 / Fark -%0,6 puan | M: Hisse +%6,7 / XU030 -%4,7 / Fark +%11,4 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%9,3 / XU030 -%8,7 / Fark -%0,6 puan | M: Hisse +%6,8 / XU030 -%4,6 / Fark +%11,4 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="J48" s="4" t="inlineStr">
@@ -12843,7 +12843,7 @@
       </c>
       <c r="K48" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=AL_ADAYI | AL basari=46.66666666666666 n=30 | SAT basari=51.28205128205128 n=39</t>
+          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=AL_ADAYI | AL basari=44.82758620689656 n=29 | SAT basari=51.28205128205128 n=39</t>
         </is>
       </c>
       <c r="L48" s="3" t="inlineStr">
@@ -12915,12 +12915,12 @@
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: Action=LONG_WATCH | Trade_Action=LONG_WATCH | Önerilen=EVET | Öneren sistem=3 | Q Now=Now +12.6%, L +0.0%, H +20.5%, UD; Path=-15.7% → +35.9% | M Now=Now -0.5%, L -5.5%, H +5.1%, UD; Path=+8.6% → -6.0% | S Now=NA; Path=NA | WMA200=+2.3%, UP</t>
+          <t>OLUMLU: Action=LONG_WATCH | Trade_Action=LONG_WATCH | Önerilen=EVET | Öneren sistem=3 | Q Now=Now +12.7%, L +0.0%, H +20.5%, UD; Path=-15.7% → +35.9% | M Now=Now -0.4%, L -5.5%, H +5.1%, UD; Path=+8.6% → -6.0% | S Now=NA; Path=NA | WMA200=+2.4%, UP</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse +%12,6 / XU030 -%8,8 / Fark +%21,4 puan | M: Hisse -%0,5 / XU030 -%4,7 / Fark +%4,2 puan | S: VERİ YOK</t>
+          <t>Q: Hisse +%12,7 / XU030 -%8,7 / Fark +%21,4 puan | M: Hisse -%0,4 / XU030 -%4,6 / Fark +%4,2 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="J49" s="5" t="inlineStr">
@@ -12930,7 +12930,7 @@
       </c>
       <c r="K49" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=AL_ADAYI | AL basari=66.66666666666667 n=69 | SAT basari=37.5 n=24</t>
+          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=AL_ADAYI | AL basari=64.70588235294117 n=68 | SAT basari=37.5 n=24</t>
         </is>
       </c>
       <c r="L49" s="3" t="inlineStr">
@@ -13002,12 +13002,12 @@
       </c>
       <c r="H50" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: Action=LONG_WATCH | Trade_Action=LONG_WATCH | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -15.6%, L -17.8%, H +0.5%, DU; Path=+9.6% → -16.3% | M Now=Now -3.8%, L -6.3%, H +6.0%, UD; Path=-3.7% → +8.7% | S Now=NA; Path=NA | WMA200=-20.4%, UP</t>
+          <t>OLUMLU: Action=LONG_WATCH | Trade_Action=LONG_WATCH | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -15.5%, L -17.8%, H +0.5%, DU; Path=+9.6% → -16.3% | M Now=Now -3.7%, L -6.3%, H +6.0%, UD; Path=-3.7% → +8.7% | S Now=NA; Path=NA | WMA200=-20.3%, UP</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%15,6 / XU030 -%8,8 / Fark -%6,8 puan | M: Hisse -%3,8 / XU030 -%4,7 / Fark +%0,9 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%15,5 / XU030 -%8,7 / Fark -%6,8 puan | M: Hisse -%3,7 / XU030 -%4,6 / Fark +%0,9 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="J50" s="5" t="inlineStr">
@@ -13049,7 +13049,7 @@
         <is>
           <t>LONG - 7 - 9/1
 LONG - 7 - 9/1
-LONG - 7 - 9/1</t>
+LONG - 7 - 9/2</t>
         </is>
       </c>
     </row>
@@ -13089,12 +13089,12 @@
       </c>
       <c r="H51" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: Action=LATE | Trade_Action=LATE | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -4.9%, L -13.9%, H +2.5%, DU; Path=+19.2% → -18.0% | M Now=Now +3.5%, L +0.0%, H +9.4%, UD; Path=-5.8% → +9.2% | S Now=NA; Path=NA | WMA200=-2.0%, UP</t>
+          <t>NÖTR: Action=LATE | Trade_Action=LATE | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -4.8%, L -13.9%, H +2.5%, DU; Path=+19.2% → -18.0% | M Now=Now +3.6%, L +0.0%, H +9.4%, UD; Path=-5.8% → +9.2% | S Now=NA; Path=NA | WMA200=-1.9%, UP</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%4,9 / XU030 -%8,8 / Fark +%3,9 puan | M: Hisse +%3,5 / XU030 -%4,7 / Fark +%8,2 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%4,8 / XU030 -%8,7 / Fark +%3,9 puan | M: Hisse +%3,6 / XU030 -%4,6 / Fark +%8,2 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="J51" s="3" t="inlineStr">
@@ -13104,7 +13104,7 @@
       </c>
       <c r="K51" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=AL_BEKLE_EŞİK | AL basari=55.81395348837209 n=43 | SAT basari=43.33333333333334 n=30</t>
+          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=AL_BEKLE_EŞİK | AL basari=55.81395348837209 n=43 | SAT basari=38.70967741935484 n=31</t>
         </is>
       </c>
       <c r="L51" s="3" t="inlineStr">
@@ -13176,12 +13176,12 @@
       </c>
       <c r="H52" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: Action=LATE | Trade_Action=LATE | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -13.2%, L -22.1%, H +0.1%, DU; Path=+14.7% → -16.2% | M Now=Now -2.8%, L -10.1%, H +3.8%, UD; Path=-6.2% → +10.3% | S Now=NA; Path=NA | WMA200=-6.9%, UP</t>
+          <t>NÖTR: Action=LATE | Trade_Action=LATE | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -13.1%, L -22.1%, H +0.1%, DU; Path=+14.7% → -16.2% | M Now=Now -2.8%, L -10.1%, H +3.8%, UD; Path=-6.2% → +10.3% | S Now=NA; Path=NA | WMA200=-6.8%, UP</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%13,2 / XU030 -%8,8 / Fark -%4,4 puan | M: Hisse -%2,8 / XU030 -%4,7 / Fark +%1,9 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%13,1 / XU030 -%8,7 / Fark -%4,4 puan | M: Hisse -%2,8 / XU030 -%4,6 / Fark +%1,8 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="J52" s="5" t="inlineStr">
@@ -13191,7 +13191,7 @@
       </c>
       <c r="K52" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=AL_ADAYI | AL basari=53.84615384615385 n=13 | SAT basari=45.45454545454545 n=33</t>
+          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=AL_ADAYI | AL basari=53.84615384615385 n=13 | SAT basari=51.51515151515152 n=33</t>
         </is>
       </c>
       <c r="L52" s="3" t="inlineStr">
@@ -13263,12 +13263,12 @@
       </c>
       <c r="H53" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: Action=RISK | Trade_Action=RISK | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -13.5%, L -14.6%, H +7.2%, DU; Path=+10.1% → -13.9% | M Now=Now -0.4%, L -1.6%, H +7.5%, UD; Path=+6.0% → -5.9% | S Now=NA; Path=NA | WMA200=-8.5%, UP</t>
+          <t>OLUMSUZ / RİSK: Action=RISK | Trade_Action=RISK | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -13.4%, L -14.6%, H +7.2%, DU; Path=+10.1% → -13.9% | M Now=Now -0.3%, L -1.6%, H +7.5%, UD; Path=+6.0% → -5.9% | S Now=NA; Path=NA | WMA200=-8.5%, UP</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%13,5 / XU030 -%8,8 / Fark -%4,7 puan | M: Hisse -%0,4 / XU030 -%4,7 / Fark +%4,3 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%13,4 / XU030 -%8,7 / Fark -%4,7 puan | M: Hisse -%0,3 / XU030 -%4,6 / Fark +%4,3 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="J53" s="3" t="inlineStr">
@@ -13278,7 +13278,7 @@
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: Endeks=XU030 | Karar=AL_ADAYI | AL basari=54.54545454545455 n=44 | SAT basari=nan n=0</t>
+          <t>NÖTR: Endeks=XU030 | Karar=AL_ADAYI | AL basari=52.27272727272727 n=44 | SAT basari=nan n=0</t>
         </is>
       </c>
       <c r="L53" s="3" t="inlineStr">
@@ -13309,8 +13309,8 @@
       <c r="Q53" s="2" t="inlineStr">
         <is>
           <t>ALT -  - 15/4
-ALT -  - 15/4
-ALT -  - 15/4</t>
+ALT -  - 14/4
+ALT -  - 14/4</t>
         </is>
       </c>
     </row>
@@ -13350,12 +13350,12 @@
       </c>
       <c r="H54" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: Action=LOW_DATA | Trade_Action=LOW_DATA | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -27.8%, L -27.8%, H +8.0%, UD; Path=+31.1% → -30.5% | M Now=Now -25.9%, L -25.9%, H +4.1%, DU; Path=-12.0% → +13.4% | S Now=NA; Path=NA | WMA200=-23.8%, UP</t>
+          <t>NÖTR: Action=LOW_DATA | Trade_Action=LOW_DATA | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -27.8%, L -27.8%, H +8.0%, UD; Path=+31.1% → -30.5% | M Now=Now -25.8%, L -25.9%, H +4.1%, DU; Path=-12.0% → +13.4% | S Now=NA; Path=NA | WMA200=-23.7%, UP</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%27,8 / XU030 -%8,8 / Fark -%19,0 puan | M: Hisse -%25,9 / XU030 -%4,7 / Fark -%21,2 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%27,8 / XU030 -%8,7 / Fark -%19,1 puan | M: Hisse -%25,8 / XU030 -%4,6 / Fark -%21,2 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="J54" s="3" t="inlineStr">
@@ -13437,12 +13437,12 @@
       </c>
       <c r="H55" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: Action=NO_CLEAR_EDGE | Trade_Action=NO_CLEAR_EDGE | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -18.1%, L -18.1%, H +0.3%, DU; Path=-12.9% → +17.2% | M Now=Now -6.3%, L -6.3%, H +5.4%, UD; Path=-5.2% → +10.0% | S Now=NA; Path=NA | WMA200=-20.3%, UP</t>
+          <t>NÖTR: Action=NO_CLEAR_EDGE | Trade_Action=NO_CLEAR_EDGE | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -18.0%, L -18.0%, H +0.3%, DU; Path=-12.9% → +17.2% | M Now=Now -6.2%, L -6.2%, H +5.4%, UD; Path=-5.2% → +10.0% | S Now=NA; Path=NA | WMA200=-20.3%, UP</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%18,1 / XU030 -%8,8 / Fark -%9,3 puan | M: Hisse -%6,3 / XU030 -%4,7 / Fark -%1,6 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%18,0 / XU030 -%8,7 / Fark -%9,3 puan | M: Hisse -%6,2 / XU030 -%4,6 / Fark -%1,6 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="J55" s="5" t="inlineStr">
@@ -13483,7 +13483,7 @@
       <c r="Q55" s="2" t="inlineStr">
         <is>
           <t>ALT -  - 37/1
-ALT -  - 38/2
+ALT -  - 37/2
 ALT -  - 12/1</t>
         </is>
       </c>
@@ -13524,12 +13524,12 @@
       </c>
       <c r="H56" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: Action=LATE | Trade_Action=LATE | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now +14.3%, L -8.6%, H +30.5%, DU; Path=+21.6% → -15.9% | M Now=Now -6.3%, L -10.5%, H +2.7%, DU; Path=+4.3% → -7.8% | S Now=NA; Path=NA | WMA200=+6.1%, DOWN</t>
+          <t>NÖTR: Action=LATE | Trade_Action=LATE | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now +14.4%, L -8.6%, H +30.5%, DU; Path=+21.6% → -15.9% | M Now=Now -6.2%, L -10.5%, H +2.7%, DU; Path=+4.3% → -7.8% | S Now=NA; Path=NA | WMA200=+6.2%, DOWN</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse +%14,3 / XU030 -%8,8 / Fark +%23,1 puan | M: Hisse -%6,3 / XU030 -%4,7 / Fark -%1,6 puan | S: VERİ YOK</t>
+          <t>Q: Hisse +%14,4 / XU030 -%8,7 / Fark +%23,1 puan | M: Hisse -%6,2 / XU030 -%4,6 / Fark -%1,6 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="J56" s="3" t="inlineStr">
@@ -13539,7 +13539,7 @@
       </c>
       <c r="K56" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=AL_ADAYI | AL basari=66.66666666666667 n=15 | SAT basari=31.74603174603175 n=63</t>
+          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=AL_ADAYI | AL basari=62.5 n=16 | SAT basari=31.74603174603175 n=63</t>
         </is>
       </c>
       <c r="L56" s="3" t="inlineStr">
@@ -13611,12 +13611,12 @@
       </c>
       <c r="H57" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: Action=LATE | Trade_Action=LATE | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -11.9%, L -17.1%, H +0.0%, DU; Path=-7.0% → +14.7% | M Now=Now -4.1%, L -8.6%, H +2.0%, DU; Path=-5.9% → +5.4% | S Now=NA; Path=NA | WMA200=-10.9%, UP</t>
+          <t>NÖTR: Action=LATE | Trade_Action=LATE | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -11.9%, L -17.1%, H +0.0%, DU; Path=-7.0% → +14.7% | M Now=Now -4.0%, L -8.6%, H +2.0%, DU; Path=-5.9% → +5.4% | S Now=NA; Path=NA | WMA200=-10.8%, UP</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%11,9 / XU030 -%8,8 / Fark -%3,1 puan | M: Hisse -%4,1 / XU030 -%4,7 / Fark +%0,6 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%11,9 / XU030 -%8,7 / Fark -%3,2 puan | M: Hisse -%4,0 / XU030 -%4,6 / Fark +%0,6 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="J57" s="3" t="inlineStr">
@@ -13626,7 +13626,7 @@
       </c>
       <c r="K57" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=AL_ADAYI | AL basari=48.48484848484848 n=33 | SAT basari=25.64102564102564 n=39</t>
+          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=AL_ADAYI | AL basari=48.48484848484848 n=33 | SAT basari=23.07692307692308 n=39</t>
         </is>
       </c>
       <c r="L57" s="3" t="inlineStr">
@@ -13698,12 +13698,12 @@
       </c>
       <c r="H58" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: Action=LOW_DATA | Trade_Action=LOW_DATA | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -31.1%, L -36.1%, H +22.7%, DU; Path=-2.8% → +14.1% | M Now=Now -34.3%, L -39.1%, H +0.0%, DU; Path=-8.7% → +14.1% | S Now=NA; Path=NA | WMA200=-19.2%, UP</t>
+          <t>NÖTR: Action=LOW_DATA | Trade_Action=LOW_DATA | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -31.1%, L -36.1%, H +22.7%, DU; Path=-2.8% → +14.1% | M Now=Now -34.3%, L -39.1%, H +0.0%, DU; Path=-8.7% → +14.1% | S Now=NA; Path=NA | WMA200=-19.1%, UP</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%31,1 / XU030 -%8,8 / Fark -%22,3 puan | M: Hisse -%34,3 / XU030 -%4,7 / Fark -%29,6 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%31,1 / XU030 -%8,7 / Fark -%22,4 puan | M: Hisse -%34,3 / XU030 -%4,6 / Fark -%29,7 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="J58" s="5" t="inlineStr">
@@ -13743,7 +13743,7 @@
       </c>
       <c r="Q58" s="2" t="inlineStr">
         <is>
-          <t>ALT -  - 16/2
+          <t>ALT -  - 15/2
 ALT -  - 31/7
 -</t>
         </is>
@@ -13785,12 +13785,12 @@
       </c>
       <c r="H59" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: Action=LOW_DATA | Trade_Action=LOW_DATA | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -33.2%, L -34.2%, H +0.0%, DU; Path=-11.3% → +35.4% | M Now=Now -20.9%, L -22.0%, H +4.0%, DU; Path=+5.2% → -12.4% | S Now=NA; Path=NA | WMA200=-33.5%, UP</t>
+          <t>NÖTR: Action=LOW_DATA | Trade_Action=LOW_DATA | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -33.2%, L -34.2%, H +0.0%, DU; Path=-11.3% → +35.4% | M Now=Now -20.8%, L -22.0%, H +4.0%, DU; Path=+5.2% → -12.4% | S Now=NA; Path=NA | WMA200=-33.4%, UP</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%33,2 / XU030 -%8,8 / Fark -%24,4 puan | M: Hisse -%20,9 / XU030 -%4,7 / Fark -%16,2 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%33,2 / XU030 -%8,7 / Fark -%24,5 puan | M: Hisse -%20,8 / XU030 -%4,6 / Fark -%16,2 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="J59" s="5" t="inlineStr">
@@ -13872,12 +13872,12 @@
       </c>
       <c r="H60" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: Action=LATE | Trade_Action=LATE | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -20.9%, L -21.3%, H +12.0%, UD; Path=+10.1% → -19.8% | M Now=Now -21.8%, L -22.3%, H +0.0%, DU; Path=-7.5% → +9.0% | S Now=NA; Path=NA | WMA200=-26.1%, UP</t>
+          <t>NÖTR: Action=LATE | Trade_Action=LATE | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -20.8%, L -21.3%, H +12.0%, UD; Path=+10.1% → -19.8% | M Now=Now -21.8%, L -22.3%, H +0.0%, DU; Path=-7.5% → +9.0% | S Now=NA; Path=NA | WMA200=-26.0%, UP</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%20,9 / XU030 -%8,8 / Fark -%12,1 puan | M: Hisse -%21,8 / XU030 -%4,7 / Fark -%17,1 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%20,8 / XU030 -%8,7 / Fark -%12,1 puan | M: Hisse -%21,8 / XU030 -%4,6 / Fark -%17,2 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="J60" s="5" t="inlineStr">
@@ -13917,7 +13917,7 @@
       </c>
       <c r="Q60" s="2" t="inlineStr">
         <is>
-          <t>ALT -  - 54/14
+          <t>ALT -  - 54/13
 ALT -  - 15/4
 ALT -  - 15/4</t>
         </is>
@@ -13959,12 +13959,12 @@
       </c>
       <c r="H61" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: Action=LOW_DATA | Trade_Action=LOW_DATA | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -17.1%, L -21.8%, H +6.0%, DU; Path=-4.3% → +53.0% | M Now=Now -12.5%, L -17.4%, H +6.3%, DU; Path=+17.4% → -14.4% | S Now=NA; Path=NA | WMA200=-19.7%, UP</t>
+          <t>NÖTR: Action=LOW_DATA | Trade_Action=LOW_DATA | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -17.0%, L -21.8%, H +6.0%, DU; Path=-4.3% → +53.0% | M Now=Now -12.4%, L -17.4%, H +6.3%, DU; Path=+17.4% → -14.4% | S Now=NA; Path=NA | WMA200=-19.6%, UP</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%17,1 / XU030 -%8,8 / Fark -%8,3 puan | M: Hisse -%12,5 / XU030 -%4,7 / Fark -%7,8 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%17,0 / XU030 -%8,7 / Fark -%8,3 puan | M: Hisse -%12,4 / XU030 -%4,6 / Fark -%7,8 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="J61" s="3" t="inlineStr">
@@ -14046,12 +14046,12 @@
       </c>
       <c r="H62" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: Action=LATE | Trade_Action=LATE | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -3.2%, L -28.3%, H +18.5%, UD; Path=+12.4% → -19.7% | M Now=Now +8.3%, L +0.0%, H +32.5%, UD; Path=+10.8% → -9.9% | S Now=NA; Path=NA | WMA200=+2.0%, DOWN</t>
+          <t>NÖTR: Action=LATE | Trade_Action=LATE | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -3.1%, L -28.3%, H +18.5%, UD; Path=+12.4% → -19.7% | M Now=Now +8.4%, L +0.0%, H +32.5%, UD; Path=+10.8% → -9.9% | S Now=NA; Path=NA | WMA200=+2.1%, DOWN</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%3,2 / XU030 -%8,8 / Fark +%5,6 puan | M: Hisse +%8,3 / XU030 -%4,7 / Fark +%13,0 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%3,1 / XU030 -%8,7 / Fark +%5,6 puan | M: Hisse +%8,4 / XU030 -%4,6 / Fark +%13,0 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="J62" s="3" t="inlineStr">
@@ -14093,7 +14093,7 @@
         <is>
           <t>SHORT - 10 - 15/15
 SHORT - 10 - 10/19
-SHORT - 2 - 3/9</t>
+SHORT - 2 - 2/9</t>
         </is>
       </c>
     </row>
@@ -14133,12 +14133,12 @@
       </c>
       <c r="H63" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: Action=LATE | Trade_Action=LATE | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -16.6%, L -21.5%, H +0.0%, DU; Path=+10.4% → -18.5% | M Now=Now +1.1%, L -4.9%, H +12.1%, UD; Path=+3.9% → -4.8% | S Now=NA; Path=NA | WMA200=-9.9%, UP</t>
+          <t>NÖTR: Action=LATE | Trade_Action=LATE | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -16.5%, L -21.5%, H +0.0%, DU; Path=+10.4% → -18.5% | M Now=Now +1.2%, L -4.9%, H +12.1%, UD; Path=+3.9% → -4.8% | S Now=NA; Path=NA | WMA200=-9.9%, UP</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%16,6 / XU030 -%8,8 / Fark -%7,8 puan | M: Hisse +%1,1 / XU030 -%4,7 / Fark +%5,8 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%16,5 / XU030 -%8,7 / Fark -%7,8 puan | M: Hisse +%1,2 / XU030 -%4,6 / Fark +%5,8 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="J63" s="3" t="inlineStr">
@@ -14148,7 +14148,7 @@
       </c>
       <c r="K63" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=AL_ADAYI | AL basari=57.14285714285715 n=21 | SAT basari=50 n=34</t>
+          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=AL_ADAYI | AL basari=57.89473684210526 n=19 | SAT basari=48.57142857142857 n=35</t>
         </is>
       </c>
       <c r="L63" s="3" t="inlineStr">
@@ -14180,7 +14180,7 @@
         <is>
           <t>LONG - 7 - 7/3
 LONG - 7 - 8/4
-SHORT - 13 - 10/7</t>
+SHORT - 13 - 9/7</t>
         </is>
       </c>
     </row>
@@ -14220,12 +14220,12 @@
       </c>
       <c r="H64" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: Action=LATE | Trade_Action=LATE | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now +5.8%, L -6.0%, H +11.0%, DU; Path=+15.1% → -13.6% | M Now=Now -0.6%, L -4.6%, H +4.3%, UD; Path=-5.6% → +8.6% | S Now=NA; Path=NA | WMA200=+1.5%, DOWN</t>
+          <t>NÖTR: Action=LATE | Trade_Action=LATE | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now +5.9%, L -6.0%, H +11.0%, DU; Path=+15.1% → -13.6% | M Now=Now -0.5%, L -4.6%, H +4.3%, UD; Path=-5.6% → +8.6% | S Now=NA; Path=NA | WMA200=+1.6%, DOWN</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse +%5,8 / XU030 -%8,8 / Fark +%14,6 puan | M: Hisse -%0,6 / XU030 -%4,7 / Fark +%4,1 puan | S: VERİ YOK</t>
+          <t>Q: Hisse +%5,9 / XU030 -%8,7 / Fark +%14,6 puan | M: Hisse -%0,5 / XU030 -%4,6 / Fark +%4,1 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="J64" s="5" t="inlineStr">
@@ -14235,7 +14235,7 @@
       </c>
       <c r="K64" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=AL_BEKLE_EŞİK | AL basari=55.17241379310344 n=29 | SAT basari=38.23529411764706 n=34</t>
+          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=AL_BEKLE_EŞİK | AL basari=53.57142857142857 n=28 | SAT basari=35.13513513513514 n=37</t>
         </is>
       </c>
       <c r="L64" s="3" t="inlineStr">
@@ -14307,12 +14307,12 @@
       </c>
       <c r="H65" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: Action=LATE | Trade_Action=LATE | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now +13.1%, L -8.7%, H +15.8%, DU; Path=+15.3% → -20.4% | M Now=Now +4.3%, L -7.1%, H +6.5%, DU; Path=-5.2% → +7.9% | S Now=NA; Path=NA | WMA200=+12.3%, DOWN</t>
+          <t>NÖTR: Action=LATE | Trade_Action=LATE | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now +13.2%, L -8.7%, H +15.8%, DU; Path=+15.3% → -20.4% | M Now=Now +4.4%, L -7.1%, H +6.5%, DU; Path=-5.2% → +7.9% | S Now=NA; Path=NA | WMA200=+12.4%, DOWN</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse +%13,1 / XU030 -%8,8 / Fark +%21,9 puan | M: Hisse +%4,3 / XU030 -%4,7 / Fark +%9,0 puan | S: VERİ YOK</t>
+          <t>Q: Hisse +%13,2 / XU030 -%8,7 / Fark +%21,9 puan | M: Hisse +%4,4 / XU030 -%4,6 / Fark +%9,0 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="J65" s="3" t="inlineStr">
@@ -14322,7 +14322,7 @@
       </c>
       <c r="K65" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=AL_ADAYI | AL basari=nan n=2 | SAT basari=48.93617021276596 n=47</t>
+          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=AL_ADAYI | AL basari=nan n=2 | SAT basari=48.97959183673469 n=49</t>
         </is>
       </c>
       <c r="L65" s="3" t="inlineStr">
@@ -14394,12 +14394,12 @@
       </c>
       <c r="H66" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: Action=LATE | Trade_Action=LATE | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now +5.6%, L -4.9%, H +31.2%, UD; Path=-6.9% → +21.1% | M Now=Now +1.7%, L -2.3%, H +26.3%, DU; Path=-4.8% → +7.5% | S Now=NA; Path=NA | WMA200=-3.8%, DOWN</t>
+          <t>NÖTR: Action=LATE | Trade_Action=LATE | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now +5.7%, L -4.9%, H +31.2%, UD; Path=-6.9% → +21.1% | M Now=Now +1.8%, L -2.3%, H +26.3%, DU; Path=-4.8% → +7.5% | S Now=NA; Path=NA | WMA200=-3.7%, DOWN</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse +%5,6 / XU030 -%8,8 / Fark +%14,4 puan | M: Hisse +%1,7 / XU030 -%4,7 / Fark +%6,4 puan | S: VERİ YOK</t>
+          <t>Q: Hisse +%5,7 / XU030 -%8,7 / Fark +%14,4 puan | M: Hisse +%1,8 / XU030 -%4,6 / Fark +%6,4 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="J66" s="5" t="inlineStr">
@@ -14409,7 +14409,7 @@
       </c>
       <c r="K66" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=SAT_ADAYI | AL basari=66.66666666666667 n=21 | SAT basari=nan n=0</t>
+          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=SAT_ADAYI | AL basari=66.66666666666667 n=21 | SAT basari=nan n=1</t>
         </is>
       </c>
       <c r="L66" s="3" t="inlineStr">
@@ -14481,12 +14481,12 @@
       </c>
       <c r="H67" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: Action=LATE | Trade_Action=LATE | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -45.2%, L -45.2%, H +31.7%, UD; Path=+27.2% → -19.3% | M Now=Now -55.4%, L -55.4%, H +7.2%, UD; Path=-7.9% → +4.5% | S Now=NA; Path=NA | WMA200=-52.5%, UP</t>
+          <t>NÖTR: Action=LATE | Trade_Action=LATE | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -45.1%, L -45.1%, H +31.7%, UD; Path=+27.2% → -19.3% | M Now=Now -55.3%, L -55.3%, H +7.2%, UD; Path=-7.9% → +4.5% | S Now=NA; Path=NA | WMA200=-52.4%, UP</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%45,2 / XU030 -%8,8 / Fark -%36,4 puan | M: Hisse -%55,4 / XU030 -%4,7 / Fark -%50,7 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%45,1 / XU030 -%8,7 / Fark -%36,4 puan | M: Hisse -%55,3 / XU030 -%4,6 / Fark -%50,7 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="J67" s="5" t="inlineStr">
@@ -14526,8 +14526,8 @@
       </c>
       <c r="Q67" s="2" t="inlineStr">
         <is>
-          <t>ALT -  - 115/59
-ALT -  - 115/59
+          <t>ALT -  - 114/58
+ALT -  - 114/58
 ALT -  - 104/67</t>
         </is>
       </c>
@@ -14568,12 +14568,12 @@
       </c>
       <c r="H68" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: Action=RISK | Trade_Action=RISK | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -18.4%, L -18.4%, H +16.1%, DU; Path=+13.7% → -18.8% | M Now=Now -13.1%, L -13.1%, H +23.7%, DU; Path=-4.4% → +10.2% | S Now=NA; Path=NA | WMA200=-22.7%, UP</t>
+          <t>OLUMSUZ / RİSK: Action=RISK | Trade_Action=RISK | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -18.4%, L -18.4%, H +16.1%, DU; Path=+13.7% → -18.8% | M Now=Now -13.0%, L -13.0%, H +23.7%, DU; Path=-4.4% → +10.2% | S Now=NA; Path=NA | WMA200=-22.6%, UP</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%18,4 / XU030 -%8,8 / Fark -%9,6 puan | M: Hisse -%13,1 / XU030 -%4,7 / Fark -%8,4 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%18,4 / XU030 -%8,7 / Fark -%9,7 puan | M: Hisse -%13,0 / XU030 -%4,6 / Fark -%8,4 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="J68" s="5" t="inlineStr">
@@ -14655,12 +14655,12 @@
       </c>
       <c r="H69" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: Action=LATE | Trade_Action=LATE | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -16.6%, L -18.3%, H +0.0%, DU; Path=+15.6% → -15.0% | M Now=Now -2.2%, L -4.2%, H +15.4%, DU; Path=+5.2% → -9.7% | S Now=NA; Path=NA | WMA200=-14.5%, UP</t>
+          <t>NÖTR: Action=LATE | Trade_Action=LATE | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -16.6%, L -18.3%, H +0.0%, DU; Path=+15.6% → -15.0% | M Now=Now -2.1%, L -4.2%, H +15.4%, DU; Path=+5.2% → -9.7% | S Now=NA; Path=NA | WMA200=-14.4%, UP</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%16,6 / XU030 -%8,8 / Fark -%7,8 puan | M: Hisse -%2,2 / XU030 -%4,7 / Fark +%2,5 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%16,6 / XU030 -%8,7 / Fark -%7,9 puan | M: Hisse -%2,1 / XU030 -%4,6 / Fark +%2,5 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="J69" s="3" t="inlineStr">
@@ -14742,12 +14742,12 @@
       </c>
       <c r="H70" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: Action=LATE | Trade_Action=LATE | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -14.1%, L -21.2%, H +0.8%, DU; Path=-8.7% → +16.0% | M Now=Now +4.5%, L -4.1%, H +17.3%, UD; Path=+2.5% → -8.8% | S Now=NA; Path=NA | WMA200=-11.6%, UP</t>
+          <t>NÖTR: Action=LATE | Trade_Action=LATE | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -14.1%, L -21.2%, H +0.8%, DU; Path=-8.7% → +16.0% | M Now=Now +4.6%, L -4.1%, H +17.3%, UD; Path=+2.5% → -8.8% | S Now=NA; Path=NA | WMA200=-11.5%, UP</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%14,1 / XU030 -%8,8 / Fark -%5,3 puan | M: Hisse +%4,5 / XU030 -%4,7 / Fark +%9,2 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%14,1 / XU030 -%8,7 / Fark -%5,4 puan | M: Hisse +%4,6 / XU030 -%4,6 / Fark +%9,2 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="J70" s="3" t="inlineStr">
@@ -14757,7 +14757,7 @@
       </c>
       <c r="K70" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=AL_ADAYI | AL basari=76.92307692307692 n=13 | SAT basari=42.1875 n=64</t>
+          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=AL_ADAYI | AL basari=69.23076923076923 n=13 | SAT basari=42.1875 n=64</t>
         </is>
       </c>
       <c r="L70" s="3" t="inlineStr">
@@ -14789,7 +14789,7 @@
         <is>
           <t>LONG - 7 - 7/9
 LONG - 7 - 9/7
-LONG - 7 - 5/5</t>
+LONG - 7 - 4/5</t>
         </is>
       </c>
     </row>
@@ -14829,12 +14829,12 @@
       </c>
       <c r="H71" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: Action=LATE | Trade_Action=LATE | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now +63.7%, L +0.0%, H +69.7%, UD; Path=+15.9% → -15.7% | M Now=Now -0.6%, L -3.9%, H +3.0%, DU; Path=-3.4% → +8.0% | S Now=NA; Path=NA | WMA200=+30.0%, DOWN</t>
+          <t>NÖTR: Action=LATE | Trade_Action=LATE | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now +63.9%, L +0.0%, H +69.7%, UD; Path=+15.9% → -15.7% | M Now=Now -0.5%, L -3.9%, H +3.0%, DU; Path=-3.4% → +8.0% | S Now=NA; Path=NA | WMA200=+30.1%, DOWN</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse +%63,7 / XU030 -%8,8 / Fark +%72,5 puan | M: Hisse -%0,6 / XU030 -%4,7 / Fark +%4,1 puan | S: VERİ YOK</t>
+          <t>Q: Hisse +%63,9 / XU030 -%8,7 / Fark +%72,6 puan | M: Hisse -%0,5 / XU030 -%4,6 / Fark +%4,1 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="J71" s="3" t="inlineStr">
@@ -14916,12 +14916,12 @@
       </c>
       <c r="H72" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: Action=LATE | Trade_Action=LATE | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -3.2%, L -14.5%, H +9.9%, DU; Path=+13.5% → -16.8% | M Now=Now +2.3%, L -6.0%, H +16.2%, UD; Path=+8.9% → -9.1% | S Now=NA; Path=NA | WMA200=-1.9%, UP</t>
+          <t>NÖTR: Action=LATE | Trade_Action=LATE | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -3.1%, L -14.5%, H +9.9%, DU; Path=+13.5% → -16.8% | M Now=Now +2.4%, L -6.0%, H +16.2%, UD; Path=+8.9% → -9.1% | S Now=NA; Path=NA | WMA200=-1.8%, UP</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%3,2 / XU030 -%8,8 / Fark +%5,6 puan | M: Hisse +%2,3 / XU030 -%4,7 / Fark +%7,0 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%3,1 / XU030 -%8,7 / Fark +%5,6 puan | M: Hisse +%2,4 / XU030 -%4,6 / Fark +%7,0 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="J72" s="5" t="inlineStr">

--- a/OZET_tr.xlsx
+++ b/OZET_tr.xlsx
@@ -622,7 +622,7 @@
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="J2" s="4" t="inlineStr">
@@ -702,7 +702,7 @@
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="J3" s="5" t="inlineStr">
@@ -782,7 +782,7 @@
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=U</t>
         </is>
       </c>
       <c r="J4" s="5" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
@@ -942,7 +942,7 @@
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="J6" s="5" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="J7" s="5" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=D</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=D</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
@@ -1262,7 +1262,7 @@
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=D; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=D; gun-kosullu: 3g=U / 4g=D</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
         </is>
       </c>
       <c r="J11" s="5" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="J12" s="5" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=U</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=D / 4g=U; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>NÖTR: BIS genel kapanis: 3g=D / 4g=U; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="J14" s="5" t="inlineStr">
@@ -1662,7 +1662,7 @@
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=D; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=D; gun-kosullu: 3g=U / 4g=U</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
         </is>
       </c>
       <c r="J16" s="5" t="inlineStr">
@@ -1822,7 +1822,7 @@
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=U</t>
         </is>
       </c>
       <c r="J17" s="5" t="inlineStr">
@@ -1902,7 +1902,7 @@
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="J18" s="5" t="inlineStr">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=U</t>
         </is>
       </c>
       <c r="J19" s="5" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=D / 4g=U; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>NÖTR: BIS genel kapanis: 3g=D / 4g=U; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -2142,7 +2142,7 @@
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=D / 4g=U; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>NÖTR: BIS genel kapanis: 3g=D / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -2222,7 +2222,7 @@
       </c>
       <c r="I22" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
         </is>
       </c>
       <c r="J23" s="5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="I24" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
@@ -2462,7 +2462,7 @@
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
@@ -2542,7 +2542,7 @@
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=U</t>
         </is>
       </c>
       <c r="J26" s="5" t="inlineStr">
@@ -2622,7 +2622,7 @@
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=D; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=D; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="J27" s="5" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=D; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=D; gun-kosullu: 3g=D / 4g=N</t>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr">
@@ -2782,7 +2782,7 @@
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=D / 4g=U; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>NÖTR: BIS genel kapanis: 3g=D / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=N; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=N; gun-kosullu: 3g=N / 4g=D</t>
         </is>
       </c>
       <c r="J30" s="4" t="inlineStr">
@@ -2942,7 +2942,7 @@
       </c>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=D; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=D; gun-kosullu: 3g=N / 4g=D</t>
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr">
@@ -3022,7 +3022,7 @@
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=D</t>
         </is>
       </c>
       <c r="J32" s="4" t="inlineStr">
@@ -3102,7 +3102,7 @@
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=D / 4g=U; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>NÖTR: BIS genel kapanis: 3g=D / 4g=U; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr">
@@ -3182,7 +3182,7 @@
       </c>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=D / 4g=U; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>NÖTR: BIS genel kapanis: 3g=D / 4g=U; gun-kosullu: 3g=D / 4g=U</t>
         </is>
       </c>
       <c r="J34" s="5" t="inlineStr">
@@ -3262,7 +3262,7 @@
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr">
@@ -3342,7 +3342,7 @@
       </c>
       <c r="I36" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=D / 4g=U; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>NÖTR: BIS genel kapanis: 3g=D / 4g=U; gun-kosullu: 3g=D / 4g=U</t>
         </is>
       </c>
       <c r="J36" s="4" t="inlineStr">
@@ -3422,7 +3422,7 @@
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr">
@@ -3502,7 +3502,7 @@
       </c>
       <c r="I38" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=D / 4g=U</t>
         </is>
       </c>
       <c r="J38" s="5" t="inlineStr">
@@ -3582,7 +3582,7 @@
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=U</t>
         </is>
       </c>
       <c r="J39" s="4" t="inlineStr">
@@ -3662,7 +3662,7 @@
       </c>
       <c r="I40" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=U / 4g=D</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
@@ -3742,7 +3742,7 @@
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=N</t>
         </is>
       </c>
       <c r="J41" s="4" t="inlineStr">
@@ -3822,7 +3822,7 @@
       </c>
       <c r="I42" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="J42" s="5" t="inlineStr">
@@ -3902,7 +3902,7 @@
       </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=U / 4g=D</t>
         </is>
       </c>
       <c r="J43" s="4" t="inlineStr">
@@ -3982,7 +3982,7 @@
       </c>
       <c r="I44" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=D / 4g=U</t>
         </is>
       </c>
       <c r="J44" s="5" t="inlineStr">
@@ -4062,7 +4062,7 @@
       </c>
       <c r="I45" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=D / 4g=U; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>NÖTR: BIS genel kapanis: 3g=D / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
         </is>
       </c>
       <c r="J45" s="5" t="inlineStr">
@@ -4142,7 +4142,7 @@
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=N / 4g=D</t>
         </is>
       </c>
       <c r="J46" s="5" t="inlineStr">
@@ -4222,7 +4222,7 @@
       </c>
       <c r="I47" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="J47" s="4" t="inlineStr">
@@ -4302,7 +4302,7 @@
       </c>
       <c r="I48" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=D / 4g=U</t>
         </is>
       </c>
       <c r="J48" s="4" t="inlineStr">
@@ -4382,7 +4382,7 @@
       </c>
       <c r="I49" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=D; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=D; gun-kosullu: 3g=U / 4g=U</t>
         </is>
       </c>
       <c r="J49" s="4" t="inlineStr">
@@ -4462,7 +4462,7 @@
       </c>
       <c r="I50" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=D / 4g=N</t>
         </is>
       </c>
       <c r="J50" s="5" t="inlineStr">
@@ -4542,7 +4542,7 @@
       </c>
       <c r="I51" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=U / 4g=D</t>
         </is>
       </c>
       <c r="J51" s="5" t="inlineStr">
@@ -4622,7 +4622,7 @@
       </c>
       <c r="I52" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=D / 4g=U; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>NÖTR: BIS genel kapanis: 3g=D / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
         </is>
       </c>
       <c r="J52" s="5" t="inlineStr">
@@ -4702,7 +4702,7 @@
       </c>
       <c r="I53" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=D / 4g=U; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>NÖTR: BIS genel kapanis: 3g=D / 4g=U; gun-kosullu: 3g=U / 4g=D</t>
         </is>
       </c>
       <c r="J53" s="4" t="inlineStr">
@@ -4782,7 +4782,7 @@
       </c>
       <c r="I54" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="J54" s="4" t="inlineStr">
@@ -4862,7 +4862,7 @@
       </c>
       <c r="I55" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=D / 4g=U; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>NÖTR: BIS genel kapanis: 3g=D / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
         </is>
       </c>
       <c r="J55" s="5" t="inlineStr">
@@ -4942,7 +4942,7 @@
       </c>
       <c r="I56" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=D; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=D; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="J56" s="5" t="inlineStr">
@@ -5022,7 +5022,7 @@
       </c>
       <c r="I57" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=D / 4g=U; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>NÖTR: BIS genel kapanis: 3g=D / 4g=U; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="J57" s="4" t="inlineStr">
@@ -5102,7 +5102,7 @@
       </c>
       <c r="I58" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=U</t>
         </is>
       </c>
       <c r="J58" s="4" t="inlineStr">
@@ -5182,7 +5182,7 @@
       </c>
       <c r="I59" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=N; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=N; gun-kosullu: 3g=U / 4g=U</t>
         </is>
       </c>
       <c r="J59" s="4" t="inlineStr">
@@ -5262,7 +5262,7 @@
       </c>
       <c r="I60" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="J60" s="4" t="inlineStr">
@@ -5342,7 +5342,7 @@
       </c>
       <c r="I61" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=D; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=D; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="J61" s="5" t="inlineStr">
@@ -5422,7 +5422,7 @@
       </c>
       <c r="I62" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=D / 4g=U</t>
         </is>
       </c>
       <c r="J62" s="4" t="inlineStr">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="I63" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=U</t>
         </is>
       </c>
       <c r="J63" s="4" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="I64" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="J64" s="5" t="inlineStr">
@@ -5662,7 +5662,7 @@
       </c>
       <c r="I65" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=U / 4g=D</t>
         </is>
       </c>
       <c r="J65" s="4" t="inlineStr">
@@ -5742,7 +5742,7 @@
       </c>
       <c r="I66" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="J66" s="5" t="inlineStr">
@@ -5822,7 +5822,7 @@
       </c>
       <c r="I67" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="J67" s="5" t="inlineStr">
@@ -5902,7 +5902,7 @@
       </c>
       <c r="I68" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="J68" s="4" t="inlineStr">
@@ -5982,7 +5982,7 @@
       </c>
       <c r="I69" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="J69" s="5" t="inlineStr">
@@ -6062,7 +6062,7 @@
       </c>
       <c r="I70" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=D; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=D; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="J70" s="5" t="inlineStr">
@@ -6142,7 +6142,7 @@
       </c>
       <c r="I71" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=U / 4g=N</t>
         </is>
       </c>
       <c r="J71" s="5" t="inlineStr">
@@ -6220,7 +6220,7 @@
       </c>
       <c r="I72" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
         </is>
       </c>
       <c r="J72" s="4" t="inlineStr">
@@ -6415,7 +6415,7 @@
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="J2" s="4" t="inlineStr">
@@ -6495,7 +6495,7 @@
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="J3" s="5" t="inlineStr">
@@ -6575,7 +6575,7 @@
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=U</t>
         </is>
       </c>
       <c r="J4" s="5" t="inlineStr">
@@ -6655,7 +6655,7 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
@@ -6735,7 +6735,7 @@
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="J6" s="5" t="inlineStr">
@@ -6815,7 +6815,7 @@
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="J7" s="5" t="inlineStr">
@@ -6895,7 +6895,7 @@
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=D</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
@@ -6975,7 +6975,7 @@
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=D</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
@@ -7055,7 +7055,7 @@
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=D; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=D; gun-kosullu: 3g=U / 4g=D</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -7135,7 +7135,7 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
         </is>
       </c>
       <c r="J11" s="5" t="inlineStr">
@@ -7215,7 +7215,7 @@
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="J12" s="5" t="inlineStr">
@@ -7295,7 +7295,7 @@
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=U</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
@@ -7375,7 +7375,7 @@
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=D / 4g=U; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>NÖTR: BIS genel kapanis: 3g=D / 4g=U; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="J14" s="5" t="inlineStr">
@@ -7455,7 +7455,7 @@
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=D; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=D; gun-kosullu: 3g=U / 4g=U</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -7535,7 +7535,7 @@
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
         </is>
       </c>
       <c r="J16" s="5" t="inlineStr">
@@ -7615,7 +7615,7 @@
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=U</t>
         </is>
       </c>
       <c r="J17" s="5" t="inlineStr">
@@ -7695,7 +7695,7 @@
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="J18" s="5" t="inlineStr">
@@ -7775,7 +7775,7 @@
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=U</t>
         </is>
       </c>
       <c r="J19" s="5" t="inlineStr">
@@ -7855,7 +7855,7 @@
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=D / 4g=U; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>NÖTR: BIS genel kapanis: 3g=D / 4g=U; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -7935,7 +7935,7 @@
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=D / 4g=U; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>NÖTR: BIS genel kapanis: 3g=D / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -8015,7 +8015,7 @@
       </c>
       <c r="I22" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
@@ -8095,7 +8095,7 @@
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
         </is>
       </c>
       <c r="J23" s="5" t="inlineStr">
@@ -8175,7 +8175,7 @@
       </c>
       <c r="I24" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
@@ -8255,7 +8255,7 @@
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
@@ -8335,7 +8335,7 @@
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=U</t>
         </is>
       </c>
       <c r="J26" s="5" t="inlineStr">
@@ -8836,7 +8836,7 @@
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
         </is>
       </c>
       <c r="K2" s="4" t="inlineStr">
@@ -8923,7 +8923,7 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="K3" s="4" t="inlineStr">
@@ -9010,7 +9010,7 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="K4" s="5" t="inlineStr">
@@ -9097,7 +9097,7 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=U</t>
         </is>
       </c>
       <c r="K5" s="5" t="inlineStr">
@@ -9184,7 +9184,7 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr">
@@ -9271,7 +9271,7 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="K7" s="5" t="inlineStr">
@@ -9358,7 +9358,7 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="K8" s="5" t="inlineStr">
@@ -9445,7 +9445,7 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=D</t>
         </is>
       </c>
       <c r="K9" s="4" t="inlineStr">
@@ -9532,7 +9532,7 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=D</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr">
@@ -9619,7 +9619,7 @@
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=D; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=D; gun-kosullu: 3g=U / 4g=D</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
@@ -9706,7 +9706,7 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
         </is>
       </c>
       <c r="K12" s="5" t="inlineStr">
@@ -9793,7 +9793,7 @@
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="K13" s="5" t="inlineStr">
@@ -9880,7 +9880,7 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=U</t>
         </is>
       </c>
       <c r="K14" s="4" t="inlineStr">
@@ -9967,7 +9967,7 @@
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=D / 4g=U; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>NÖTR: BIS genel kapanis: 3g=D / 4g=U; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="K15" s="5" t="inlineStr">
@@ -10054,7 +10054,7 @@
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=D; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=D; gun-kosullu: 3g=U / 4g=U</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
@@ -10141,7 +10141,7 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
         </is>
       </c>
       <c r="K17" s="5" t="inlineStr">
@@ -10228,7 +10228,7 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=U</t>
         </is>
       </c>
       <c r="K18" s="5" t="inlineStr">
@@ -10315,7 +10315,7 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="K19" s="5" t="inlineStr">
@@ -10402,7 +10402,7 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=U</t>
         </is>
       </c>
       <c r="K20" s="5" t="inlineStr">
@@ -10489,7 +10489,7 @@
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=D / 4g=U; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>NÖTR: BIS genel kapanis: 3g=D / 4g=U; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
@@ -10576,7 +10576,7 @@
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=D / 4g=U; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>NÖTR: BIS genel kapanis: 3g=D / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
@@ -10663,7 +10663,7 @@
       </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="K23" s="4" t="inlineStr">
@@ -10750,7 +10750,7 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
         </is>
       </c>
       <c r="K24" s="5" t="inlineStr">
@@ -10837,7 +10837,7 @@
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="K25" s="4" t="inlineStr">
@@ -10924,7 +10924,7 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="K26" s="4" t="inlineStr">
@@ -11011,7 +11011,7 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=U</t>
         </is>
       </c>
       <c r="K27" s="5" t="inlineStr">
@@ -11098,7 +11098,7 @@
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=D; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=D; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="K28" s="5" t="inlineStr">
@@ -11185,7 +11185,7 @@
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=D; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=D; gun-kosullu: 3g=D / 4g=N</t>
         </is>
       </c>
       <c r="K29" s="4" t="inlineStr">
@@ -11272,7 +11272,7 @@
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=D / 4g=U; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>NÖTR: BIS genel kapanis: 3g=D / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
         </is>
       </c>
       <c r="K30" s="5" t="inlineStr">
@@ -11359,7 +11359,7 @@
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=N; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=N; gun-kosullu: 3g=N / 4g=D</t>
         </is>
       </c>
       <c r="K31" s="4" t="inlineStr">
@@ -11446,7 +11446,7 @@
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=D; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=D; gun-kosullu: 3g=N / 4g=D</t>
         </is>
       </c>
       <c r="K32" s="4" t="inlineStr">
@@ -11533,7 +11533,7 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=D</t>
         </is>
       </c>
       <c r="K33" s="4" t="inlineStr">
@@ -11620,7 +11620,7 @@
       </c>
       <c r="J34" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=D / 4g=U; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>NÖTR: BIS genel kapanis: 3g=D / 4g=U; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="K34" s="5" t="inlineStr">
@@ -11707,7 +11707,7 @@
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=D / 4g=U; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>NÖTR: BIS genel kapanis: 3g=D / 4g=U; gun-kosullu: 3g=D / 4g=U</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
@@ -11794,7 +11794,7 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
         </is>
       </c>
       <c r="K36" s="5" t="inlineStr">
@@ -11881,7 +11881,7 @@
       </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=D / 4g=U; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>NÖTR: BIS genel kapanis: 3g=D / 4g=U; gun-kosullu: 3g=D / 4g=U</t>
         </is>
       </c>
       <c r="K37" s="4" t="inlineStr">
@@ -11968,7 +11968,7 @@
       </c>
       <c r="J38" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="K38" s="5" t="inlineStr">
@@ -12055,7 +12055,7 @@
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=D / 4g=U</t>
         </is>
       </c>
       <c r="K39" s="5" t="inlineStr">
@@ -12142,7 +12142,7 @@
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=U</t>
         </is>
       </c>
       <c r="K40" s="4" t="inlineStr">
@@ -12229,7 +12229,7 @@
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=U / 4g=D</t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
@@ -12316,7 +12316,7 @@
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=N</t>
         </is>
       </c>
       <c r="K42" s="4" t="inlineStr">
@@ -12403,7 +12403,7 @@
       </c>
       <c r="J43" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="K43" s="5" t="inlineStr">
@@ -12490,7 +12490,7 @@
       </c>
       <c r="J44" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=U / 4g=D</t>
         </is>
       </c>
       <c r="K44" s="4" t="inlineStr">
@@ -12577,7 +12577,7 @@
       </c>
       <c r="J45" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=D / 4g=U</t>
         </is>
       </c>
       <c r="K45" s="5" t="inlineStr">
@@ -12664,7 +12664,7 @@
       </c>
       <c r="J46" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=D / 4g=U; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>NÖTR: BIS genel kapanis: 3g=D / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
         </is>
       </c>
       <c r="K46" s="5" t="inlineStr">
@@ -12751,7 +12751,7 @@
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=N / 4g=D</t>
         </is>
       </c>
       <c r="K47" s="5" t="inlineStr">
@@ -12838,7 +12838,7 @@
       </c>
       <c r="J48" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="K48" s="4" t="inlineStr">
@@ -12925,7 +12925,7 @@
       </c>
       <c r="J49" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=D / 4g=U</t>
         </is>
       </c>
       <c r="K49" s="4" t="inlineStr">
@@ -13012,7 +13012,7 @@
       </c>
       <c r="J50" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=D; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=D; gun-kosullu: 3g=U / 4g=U</t>
         </is>
       </c>
       <c r="K50" s="4" t="inlineStr">
@@ -13099,7 +13099,7 @@
       </c>
       <c r="J51" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=D / 4g=N</t>
         </is>
       </c>
       <c r="K51" s="5" t="inlineStr">
@@ -13186,7 +13186,7 @@
       </c>
       <c r="J52" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=U / 4g=D</t>
         </is>
       </c>
       <c r="K52" s="5" t="inlineStr">
@@ -13273,7 +13273,7 @@
       </c>
       <c r="J53" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=D / 4g=U; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>NÖTR: BIS genel kapanis: 3g=D / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
         </is>
       </c>
       <c r="K53" s="5" t="inlineStr">
@@ -13360,7 +13360,7 @@
       </c>
       <c r="J54" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=D / 4g=U; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>NÖTR: BIS genel kapanis: 3g=D / 4g=U; gun-kosullu: 3g=U / 4g=D</t>
         </is>
       </c>
       <c r="K54" s="4" t="inlineStr">
@@ -13447,7 +13447,7 @@
       </c>
       <c r="J55" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="K55" s="4" t="inlineStr">
@@ -13534,7 +13534,7 @@
       </c>
       <c r="J56" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=D / 4g=U; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>NÖTR: BIS genel kapanis: 3g=D / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
         </is>
       </c>
       <c r="K56" s="5" t="inlineStr">
@@ -13621,7 +13621,7 @@
       </c>
       <c r="J57" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=D; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=D; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="K57" s="5" t="inlineStr">
@@ -13708,7 +13708,7 @@
       </c>
       <c r="J58" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=D / 4g=U; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>NÖTR: BIS genel kapanis: 3g=D / 4g=U; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="K58" s="4" t="inlineStr">
@@ -13795,7 +13795,7 @@
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=U</t>
         </is>
       </c>
       <c r="K59" s="4" t="inlineStr">
@@ -13882,7 +13882,7 @@
       </c>
       <c r="J60" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=N; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=N; gun-kosullu: 3g=U / 4g=U</t>
         </is>
       </c>
       <c r="K60" s="4" t="inlineStr">
@@ -13969,7 +13969,7 @@
       </c>
       <c r="J61" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="K61" s="4" t="inlineStr">
@@ -14056,7 +14056,7 @@
       </c>
       <c r="J62" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=D; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=D; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="K62" s="5" t="inlineStr">
@@ -14143,7 +14143,7 @@
       </c>
       <c r="J63" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=D / 4g=U</t>
         </is>
       </c>
       <c r="K63" s="4" t="inlineStr">
@@ -14230,7 +14230,7 @@
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=U</t>
         </is>
       </c>
       <c r="K64" s="4" t="inlineStr">
@@ -14317,7 +14317,7 @@
       </c>
       <c r="J65" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="K65" s="5" t="inlineStr">
@@ -14404,7 +14404,7 @@
       </c>
       <c r="J66" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=U / 4g=D</t>
         </is>
       </c>
       <c r="K66" s="4" t="inlineStr">
@@ -14491,7 +14491,7 @@
       </c>
       <c r="J67" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="K67" s="5" t="inlineStr">
@@ -14578,7 +14578,7 @@
       </c>
       <c r="J68" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="K68" s="5" t="inlineStr">
@@ -14665,7 +14665,7 @@
       </c>
       <c r="J69" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="K69" s="4" t="inlineStr">
@@ -14752,7 +14752,7 @@
       </c>
       <c r="J70" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="K70" s="5" t="inlineStr">
@@ -14839,7 +14839,7 @@
       </c>
       <c r="J71" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=D; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=D; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="K71" s="5" t="inlineStr">
@@ -14926,7 +14926,7 @@
       </c>
       <c r="J72" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=YOK / 4g=YOK</t>
+          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=U / 4g=N</t>
         </is>
       </c>
       <c r="K72" s="5" t="inlineStr">

--- a/OZET_tr.xlsx
+++ b/OZET_tr.xlsx
@@ -1298,7 +1298,7 @@
       <c r="P10" s="2" t="inlineStr">
         <is>
           <t>SHORT - 32 - 10/3
-SHORT - 17 - 9/4
+SHORT - 17 - 8/4
 SHORT - 9 - 7/3</t>
         </is>
       </c>
@@ -1332,12 +1332,12 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: Action=LONG_WATCH | Trade_Action=LONG_WATCH | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now +5.1%, L +0.0%, H +5.1%, UD; Path=+17.6% → -9.9% | M Now=Now +5.1%, L +0.0%, H +5.1%, UD; Path=+6.6% → -8.4% | S Now=NA; Path=NA | WMA200=-2.5%, DOWN</t>
+          <t>OLUMLU: Action=LONG_WATCH | Trade_Action=LONG_WATCH | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now +5.2%, L +0.0%, H +5.2%, UD; Path=+17.6% → -9.9% | M Now=Now +5.2%, L +0.0%, H +5.2%, UD; Path=+6.6% → -8.4% | S Now=NA; Path=NA | WMA200=-2.5%, DOWN</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse +%5,1 / XU030 +%0,8 / Fark +%4,3 puan | M: Hisse +%5,1 / XU030 +%0,8 / Fark +%4,3 puan | S: VERİ YOK</t>
+          <t>Q: Hisse +%5,2 / XU030 +%0,8 / Fark +%4,4 puan | M: Hisse +%5,2 / XU030 +%0,8 / Fark +%4,4 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="I11" s="5" t="inlineStr">
@@ -1697,7 +1697,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>LONG - 2 - 10/0
+          <t>LONG - 2 - 10/1
 LONG - 97 - 13/8
 ALT -  - 29/5</t>
         </is>
@@ -2307,7 +2307,7 @@
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: Endeks=XU030 | Karar=ÇELİŞKİLİ_BEKLE | AL basari=52.63157894736842 n=38 | SAT basari=35.18518518518518 n=54</t>
+          <t>NÖTR: Endeks=XU030 | Karar=ÇELİŞKİLİ_BEKLE | AL basari=50 n=38 | SAT basari=35.18518518518518 n=54</t>
         </is>
       </c>
       <c r="K23" s="5" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: Endeks=XU030 | Karar=ÇELİŞKİLİ_BEKLE | AL basari=68.75 n=16 | SAT basari=40 n=50</t>
+          <t>NÖTR: Endeks=XU030 | Karar=ÇELİŞKİLİ_BEKLE | AL basari=68.75 n=16 | SAT basari=39.21568627450981 n=51</t>
         </is>
       </c>
       <c r="K30" s="4" t="inlineStr">
@@ -4052,12 +4052,12 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: Action=LONG_WATCH | Trade_Action=LONG_WATCH | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -2.1%, L -2.1%, H +0.3%, DU; Path=-5.9% → +19.2% | M Now=Now -2.1%, L -2.1%, H +0.3%, DU; Path=-2.6% → +10.3% | S Now=NA; Path=NA | WMA200=-23.3%, UP</t>
+          <t>OLUMLU: Action=LONG_WATCH | Trade_Action=LONG_WATCH | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -2.0%, L -2.0%, H +0.3%, DU; Path=-5.9% → +19.2% | M Now=Now -2.0%, L -2.0%, H +0.3%, DU; Path=-2.6% → +10.3% | S Now=NA; Path=NA | WMA200=-23.3%, UP</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%2,1 / XU030 +%0,8 / Fark -%2,9 puan | M: Hisse -%2,1 / XU030 +%0,8 / Fark -%2,9 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%2,0 / XU030 +%0,8 / Fark -%2,8 puan | M: Hisse -%2,0 / XU030 +%0,8 / Fark -%2,8 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="I45" s="5" t="inlineStr">
@@ -4132,7 +4132,7 @@
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: Action=NO_CLEAR_EDGE | Trade_Action=NO_CLEAR_EDGE | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now +1.5%, L -1.7%, H +2.1%, UD; Path=-11.5% → +20.6% | M Now=Now +1.5%, L -1.7%, H +2.1%, UD; Path=-7.4% → +8.1% | S Now=NA; Path=NA | WMA200=-0.2%, DOWN</t>
+          <t>NÖTR: Action=NO_CLEAR_EDGE | Trade_Action=NO_CLEAR_EDGE | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now +1.5%, L -1.7%, H +2.1%, UD; Path=-11.5% → +20.6% | M Now=Now +1.5%, L -1.7%, H +2.1%, UD; Path=-7.4% → +8.1% | S Now=NA; Path=NA | WMA200=-0.1%, DOWN</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -4147,7 +4147,7 @@
       </c>
       <c r="J46" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=SAT_BEKLE_EŞİK | AL basari=45 n=40 | SAT basari=52 n=25</t>
+          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=SAT_BEKLE_EŞİK | AL basari=45 n=40 | SAT basari=54.16666666666666 n=24</t>
         </is>
       </c>
       <c r="K46" s="4" t="inlineStr">
@@ -4387,7 +4387,7 @@
       </c>
       <c r="J49" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=AL_ADAYI | AL basari=57.89473684210526 n=19 | SAT basari=40 n=20</t>
+          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=AL_ADAYI | AL basari=55.55555555555556 n=18 | SAT basari=40 n=20</t>
         </is>
       </c>
       <c r="K49" s="4" t="inlineStr">
@@ -4577,7 +4577,7 @@
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>LONG - 4 - 11/1
+          <t>LONG - 4 - 11/2
 LONG - 11 - 7/4
 LONG - 4 - 11/2</t>
         </is>
@@ -5812,12 +5812,12 @@
       </c>
       <c r="G67" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: Action=NO_CLEAR_EDGE | Trade_Action=NO_CLEAR_EDGE | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now +0.1%, L -1.6%, H +0.1%, DU; Path=-13.7% → +28.9% | M Now=Now +0.1%, L -1.6%, H +0.1%, DU; Path=-7.1% → +10.0% | S Now=NA; Path=NA | WMA200=+2.4%, DOWN</t>
+          <t>NÖTR: Action=NO_CLEAR_EDGE | Trade_Action=NO_CLEAR_EDGE | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now +0.2%, L -1.6%, H +0.2%, DU; Path=-13.7% → +28.9% | M Now=Now +0.2%, L -1.6%, H +0.2%, DU; Path=-7.1% → +10.0% | S Now=NA; Path=NA | WMA200=+2.4%, DOWN</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse +%0,1 / XU030 +%0,8 / Fark -%0,7 puan | M: Hisse +%0,1 / XU030 +%0,8 / Fark -%0,7 puan | S: VERİ YOK</t>
+          <t>Q: Hisse +%0,2 / XU030 +%0,8 / Fark -%0,6 puan | M: Hisse +%0,2 / XU030 +%0,8 / Fark -%0,6 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="I67" s="4" t="inlineStr">
@@ -5987,7 +5987,7 @@
       </c>
       <c r="J69" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=SAT_ADAYI | AL basari=nan n=0 | SAT basari=52.94117647058823 n=17</t>
+          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=SAT_ADAYI | AL basari=nan n=0 | SAT basari=50 n=18</t>
         </is>
       </c>
       <c r="K69" s="4" t="inlineStr">
@@ -7091,7 +7091,7 @@
       <c r="P10" s="2" t="inlineStr">
         <is>
           <t>SHORT - 32 - 10/3
-SHORT - 17 - 9/4
+SHORT - 17 - 8/4
 SHORT - 9 - 7/3</t>
         </is>
       </c>
@@ -7125,12 +7125,12 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: Action=LONG_WATCH | Trade_Action=LONG_WATCH | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now +5.1%, L +0.0%, H +5.1%, UD; Path=+17.6% → -9.9% | M Now=Now +5.1%, L +0.0%, H +5.1%, UD; Path=+6.6% → -8.4% | S Now=NA; Path=NA | WMA200=-2.5%, DOWN</t>
+          <t>OLUMLU: Action=LONG_WATCH | Trade_Action=LONG_WATCH | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now +5.2%, L +0.0%, H +5.2%, UD; Path=+17.6% → -9.9% | M Now=Now +5.2%, L +0.0%, H +5.2%, UD; Path=+6.6% → -8.4% | S Now=NA; Path=NA | WMA200=-2.5%, DOWN</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse +%5,1 / XU030 +%0,8 / Fark +%4,3 puan | M: Hisse +%5,1 / XU030 +%0,8 / Fark +%4,3 puan | S: VERİ YOK</t>
+          <t>Q: Hisse +%5,2 / XU030 +%0,8 / Fark +%4,4 puan | M: Hisse +%5,2 / XU030 +%0,8 / Fark +%4,4 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="I11" s="5" t="inlineStr">
@@ -7490,7 +7490,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>LONG - 2 - 10/0
+          <t>LONG - 2 - 10/1
 LONG - 97 - 13/8
 ALT -  - 29/5</t>
         </is>
@@ -8100,7 +8100,7 @@
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: Endeks=XU030 | Karar=ÇELİŞKİLİ_BEKLE | AL basari=52.63157894736842 n=38 | SAT basari=35.18518518518518 n=54</t>
+          <t>NÖTR: Endeks=XU030 | Karar=ÇELİŞKİLİ_BEKLE | AL basari=50 n=38 | SAT basari=35.18518518518518 n=54</t>
         </is>
       </c>
       <c r="K23" s="5" t="inlineStr">
@@ -9735,7 +9735,7 @@
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>SHORT - 32 - 10/3
-SHORT - 17 - 9/4
+SHORT - 17 - 8/4
 SHORT - 9 - 7/3</t>
         </is>
       </c>
@@ -9776,12 +9776,12 @@
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: Action=LONG_WATCH | Trade_Action=LONG_WATCH | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now +5.1%, L +0.0%, H +5.1%, UD; Path=+17.6% → -9.9% | M Now=Now +5.1%, L +0.0%, H +5.1%, UD; Path=+6.6% → -8.4% | S Now=NA; Path=NA | WMA200=-2.5%, DOWN</t>
+          <t>OLUMLU: Action=LONG_WATCH | Trade_Action=LONG_WATCH | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now +5.2%, L +0.0%, H +5.2%, UD; Path=+17.6% → -9.9% | M Now=Now +5.2%, L +0.0%, H +5.2%, UD; Path=+6.6% → -8.4% | S Now=NA; Path=NA | WMA200=-2.5%, DOWN</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse +%5,1 / XU030 +%0,8 / Fark +%4,3 puan | M: Hisse +%5,1 / XU030 +%0,8 / Fark +%4,3 puan | S: VERİ YOK</t>
+          <t>Q: Hisse +%5,2 / XU030 +%0,8 / Fark +%4,4 puan | M: Hisse +%5,2 / XU030 +%0,8 / Fark +%4,4 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="J12" s="5" t="inlineStr">
@@ -10169,7 +10169,7 @@
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>LONG - 2 - 10/0
+          <t>LONG - 2 - 10/1
 LONG - 97 - 13/8
 ALT -  - 29/5</t>
         </is>
@@ -10835,7 +10835,7 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: Endeks=XU030 | Karar=ÇELİŞKİLİ_BEKLE | AL basari=52.63157894736842 n=38 | SAT basari=35.18518518518518 n=54</t>
+          <t>NÖTR: Endeks=XU030 | Karar=ÇELİŞKİLİ_BEKLE | AL basari=50 n=38 | SAT basari=35.18518518518518 n=54</t>
         </is>
       </c>
       <c r="L24" s="5" t="inlineStr">
@@ -11444,7 +11444,7 @@
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: Endeks=XU030 | Karar=ÇELİŞKİLİ_BEKLE | AL basari=68.75 n=16 | SAT basari=40 n=50</t>
+          <t>NÖTR: Endeks=XU030 | Karar=ÇELİŞKİLİ_BEKLE | AL basari=68.75 n=16 | SAT basari=39.21568627450981 n=51</t>
         </is>
       </c>
       <c r="L31" s="4" t="inlineStr">
@@ -12734,12 +12734,12 @@
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: Action=LONG_WATCH | Trade_Action=LONG_WATCH | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -2.1%, L -2.1%, H +0.3%, DU; Path=-5.9% → +19.2% | M Now=Now -2.1%, L -2.1%, H +0.3%, DU; Path=-2.6% → +10.3% | S Now=NA; Path=NA | WMA200=-23.3%, UP</t>
+          <t>OLUMLU: Action=LONG_WATCH | Trade_Action=LONG_WATCH | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now -2.0%, L -2.0%, H +0.3%, DU; Path=-5.9% → +19.2% | M Now=Now -2.0%, L -2.0%, H +0.3%, DU; Path=-2.6% → +10.3% | S Now=NA; Path=NA | WMA200=-23.3%, UP</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse -%2,1 / XU030 +%0,8 / Fark -%2,9 puan | M: Hisse -%2,1 / XU030 +%0,8 / Fark -%2,9 puan | S: VERİ YOK</t>
+          <t>Q: Hisse -%2,0 / XU030 +%0,8 / Fark -%2,8 puan | M: Hisse -%2,0 / XU030 +%0,8 / Fark -%2,8 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="J46" s="5" t="inlineStr">
@@ -12821,7 +12821,7 @@
       </c>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: Action=NO_CLEAR_EDGE | Trade_Action=NO_CLEAR_EDGE | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now +1.5%, L -1.7%, H +2.1%, UD; Path=-11.5% → +20.6% | M Now=Now +1.5%, L -1.7%, H +2.1%, UD; Path=-7.4% → +8.1% | S Now=NA; Path=NA | WMA200=-0.2%, DOWN</t>
+          <t>NÖTR: Action=NO_CLEAR_EDGE | Trade_Action=NO_CLEAR_EDGE | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now +1.5%, L -1.7%, H +2.1%, UD; Path=-11.5% → +20.6% | M Now=Now +1.5%, L -1.7%, H +2.1%, UD; Path=-7.4% → +8.1% | S Now=NA; Path=NA | WMA200=-0.1%, DOWN</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
@@ -12836,7 +12836,7 @@
       </c>
       <c r="K47" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=SAT_BEKLE_EŞİK | AL basari=45 n=40 | SAT basari=52 n=25</t>
+          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=SAT_BEKLE_EŞİK | AL basari=45 n=40 | SAT basari=54.16666666666666 n=24</t>
         </is>
       </c>
       <c r="L47" s="4" t="inlineStr">
@@ -13097,7 +13097,7 @@
       </c>
       <c r="K50" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=AL_ADAYI | AL basari=57.89473684210526 n=19 | SAT basari=40 n=20</t>
+          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=AL_ADAYI | AL basari=55.55555555555556 n=18 | SAT basari=40 n=20</t>
         </is>
       </c>
       <c r="L50" s="4" t="inlineStr">
@@ -13301,7 +13301,7 @@
       </c>
       <c r="Q52" s="2" t="inlineStr">
         <is>
-          <t>LONG - 4 - 11/1
+          <t>LONG - 4 - 11/2
 LONG - 11 - 7/4
 LONG - 4 - 11/2</t>
         </is>
@@ -14648,12 +14648,12 @@
       </c>
       <c r="H68" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: Action=NO_CLEAR_EDGE | Trade_Action=NO_CLEAR_EDGE | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now +0.1%, L -1.6%, H +0.1%, DU; Path=-13.7% → +28.9% | M Now=Now +0.1%, L -1.6%, H +0.1%, DU; Path=-7.1% → +10.0% | S Now=NA; Path=NA | WMA200=+2.4%, DOWN</t>
+          <t>NÖTR: Action=NO_CLEAR_EDGE | Trade_Action=NO_CLEAR_EDGE | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now +0.2%, L -1.6%, H +0.2%, DU; Path=-13.7% → +28.9% | M Now=Now +0.2%, L -1.6%, H +0.2%, DU; Path=-7.1% → +10.0% | S Now=NA; Path=NA | WMA200=+2.4%, DOWN</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>Q: Hisse +%0,1 / XU030 +%0,8 / Fark -%0,7 puan | M: Hisse +%0,1 / XU030 +%0,8 / Fark -%0,7 puan | S: VERİ YOK</t>
+          <t>Q: Hisse +%0,2 / XU030 +%0,8 / Fark -%0,6 puan | M: Hisse +%0,2 / XU030 +%0,8 / Fark -%0,6 puan | S: VERİ YOK</t>
         </is>
       </c>
       <c r="J68" s="4" t="inlineStr">
@@ -14837,7 +14837,7 @@
       </c>
       <c r="K70" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=SAT_ADAYI | AL basari=nan n=0 | SAT basari=52.94117647058823 n=17</t>
+          <t>OLUMSUZ / RİSK: Endeks=XU030 | Karar=SAT_ADAYI | AL basari=nan n=0 | SAT basari=50 n=18</t>
         </is>
       </c>
       <c r="L70" s="4" t="inlineStr">
